--- a/input_processing/reg_estimates_ES_toClean/reg_income_ES.xlsx
+++ b/input_processing/reg_estimates_ES_toClean/reg_income_ES.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="156" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="164" uniqueCount="64">
   <si>
     <t>Description:</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Categorical health variable modelled as continuous</t>
   </si>
   <si>
-    <t>Regions: ES1 =  Noroeste , ES2 = Noreste , ES3 = Madrid , ES4 =  Centro , ES5 = Este , ES5 =  Sur , ES5 = ,  Canarias.</t>
+    <t>Regions: ES1 =  Noroeste , ES2 = Noreste , ES3 = Madrid , ES4 =  Centro , ES5 = Este , ES6=  Sur , ES7 = ,  Canarias.</t>
   </si>
   <si>
     <t>Goodness of fit</t>
@@ -160,6 +160,12 @@
   </si>
   <si>
     <t>Year_transformed</t>
+  </si>
+  <si>
+    <t>Y2020</t>
+  </si>
+  <si>
+    <t>Y2021</t>
   </si>
   <si>
     <t>Constant</t>
@@ -500,56 +506,56 @@
     </row>
     <row r="5">
       <c r="A5" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B7">
-        <v>0.31876298588660379</v>
+        <v>0.32020493334424105</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F7">
-        <v>15028.617817897248</v>
+        <v>15106.424510469089</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B8">
         <v>139917</v>
       </c>
       <c r="E8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F8">
-        <v>-97623386.28692469</v>
+        <v>-97416839.566960737</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B13">
-        <v>0.63339424295572866</v>
+        <v>0.54353966627829697</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14">
-        <v>53223</v>
+        <v>52275</v>
       </c>
     </row>
   </sheetData>
@@ -558,7 +564,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AI33"/>
+  <dimension ref="A1:AK35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -667,109 +673,121 @@
       <c r="AI1" t="s">
         <v>49</v>
       </c>
+      <c r="AJ1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
       <c r="B2">
-        <v>-0.049454691310732921</v>
+        <v>-0.049047819627476584</v>
       </c>
       <c r="C2">
-        <v>0.00043173714771216039</v>
+        <v>0.00043189762075675279</v>
       </c>
       <c r="D2">
-        <v>-6.6266535941864502e-07</v>
+        <v>-7.1937156704148443e-07</v>
       </c>
       <c r="E2">
-        <v>3.3265319739136057e-08</v>
+        <v>3.3578253004639401e-08</v>
       </c>
       <c r="F2">
-        <v>-6.0959814604424941e-06</v>
+        <v>-8.241966738302059e-06</v>
       </c>
       <c r="G2">
-        <v>1.9222037769233948e-05</v>
+        <v>1.855934931981686e-05</v>
       </c>
       <c r="H2">
-        <v>3.3616512975651253e-07</v>
+        <v>-1.6690760842623853e-08</v>
       </c>
       <c r="I2">
-        <v>-9.4071768424800991e-07</v>
+        <v>-7.3914409938055097e-07</v>
       </c>
       <c r="J2">
-        <v>1.9342654812550678e-06</v>
+        <v>1.6071703646335672e-06</v>
       </c>
       <c r="K2">
-        <v>-5.7624821228866908e-05</v>
+        <v>-5.7547310330336932e-05</v>
       </c>
       <c r="L2">
-        <v>-5.718589117759293e-06</v>
+        <v>-5.6414867353351785e-06</v>
       </c>
       <c r="M2">
-        <v>-9.3407144047405155e-07</v>
+        <v>-8.3731349492827086e-07</v>
       </c>
       <c r="N2">
-        <v>-0.00042433242154412705</v>
+        <v>-0.00042477101755662413</v>
       </c>
       <c r="O2">
-        <v>9.1092695125573891e-08</v>
+        <v>9.0939883462974436e-08</v>
       </c>
       <c r="P2">
-        <v>-6.9630187884068893e-07</v>
+        <v>-5.5365494455151705e-07</v>
       </c>
       <c r="Q2">
-        <v>-4.4291088169017185e-06</v>
+        <v>-4.4643412823985004e-06</v>
       </c>
       <c r="R2">
-        <v>-0.00020488441457322765</v>
+        <v>-0.00020276970545396434</v>
       </c>
       <c r="S2">
-        <v>-0.00018583290833420433</v>
+        <v>-0.00018457906641151828</v>
       </c>
       <c r="T2">
-        <v>-0.0001437379964723695</v>
+        <v>-0.00014230107507940196</v>
       </c>
       <c r="U2">
-        <v>-0.00043025157219142519</v>
+        <v>-0.00042824173032764926</v>
       </c>
       <c r="V2">
-        <v>-0.00038948152581626505</v>
+        <v>-0.00038901432655613779</v>
       </c>
       <c r="W2">
-        <v>-0.00054368934856143479</v>
+        <v>-0.00054219627613523783</v>
       </c>
       <c r="X2">
-        <v>3.2875115851226283e-05</v>
+        <v>3.2606815590782098e-05</v>
       </c>
       <c r="Y2">
-        <v>1.2960937229377916e-05</v>
+        <v>1.2507353626023731e-05</v>
       </c>
       <c r="Z2">
-        <v>0.00010968366927055643</v>
+        <v>0.00010919930756859229</v>
       </c>
       <c r="AA2">
-        <v>2.2234755090753911e-05</v>
+        <v>2.008944525785602e-05</v>
       </c>
       <c r="AB2">
-        <v>3.2851493319003622e-05</v>
+        <v>3.0620277680629821e-05</v>
       </c>
       <c r="AC2">
-        <v>1.9518044904853678e-05</v>
+        <v>1.737095255270012e-05</v>
       </c>
       <c r="AD2">
-        <v>1.186426867075995e-05</v>
+        <v>9.9550358277092029e-06</v>
       </c>
       <c r="AE2">
-        <v>2.0848925512747659e-05</v>
+        <v>1.8740201872788885e-05</v>
       </c>
       <c r="AF2">
-        <v>1.8016048059746909e-05</v>
+        <v>1.6236824556625044e-05</v>
       </c>
       <c r="AG2">
-        <v>3.2427673415165035e-07</v>
+        <v>4.5706930769845149e-07</v>
       </c>
       <c r="AH2">
-        <v>0.00034613295039739823</v>
+        <v>-1.1395694809765368e-05</v>
+      </c>
+      <c r="AI2">
+        <v>7.7841352484640314e-07</v>
+      </c>
+      <c r="AJ2">
+        <v>0.00034627450460851311</v>
       </c>
     </row>
     <row r="3">
@@ -777,103 +795,109 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>-0.022431504360503968</v>
+        <v>-0.022291752349886996</v>
       </c>
       <c r="C3">
-        <v>-6.6266535941864502e-07</v>
+        <v>-7.1937156704148443e-07</v>
       </c>
       <c r="D3">
-        <v>1.8012752795665159e-05</v>
+        <v>1.8125442436254629e-05</v>
       </c>
       <c r="E3">
-        <v>-1.6785502349928611e-07</v>
+        <v>-1.6888010944626742e-07</v>
       </c>
       <c r="F3">
-        <v>3.8715113795570241e-06</v>
+        <v>3.7800642651957662e-06</v>
       </c>
       <c r="G3">
-        <v>-9.5020304315485756e-06</v>
+        <v>-9.4488630177101824e-06</v>
       </c>
       <c r="H3">
-        <v>-1.4180418073471551e-05</v>
+        <v>-1.4270496977472148e-05</v>
       </c>
       <c r="I3">
-        <v>-1.2255673480901987e-05</v>
+        <v>-1.2432825514939752e-05</v>
       </c>
       <c r="J3">
-        <v>-9.864825399419761e-07</v>
+        <v>-9.6927094243349794e-07</v>
       </c>
       <c r="K3">
-        <v>-1.0834928015026822e-06</v>
+        <v>-9.6672651619156798e-07</v>
       </c>
       <c r="L3">
-        <v>-2.6060318885225805e-06</v>
+        <v>-2.6211966690228471e-06</v>
       </c>
       <c r="M3">
-        <v>-3.1338989980077789e-07</v>
+        <v>-2.8019044137940674e-07</v>
       </c>
       <c r="N3">
-        <v>8.2333549944939496e-07</v>
+        <v>8.6552023993750523e-07</v>
       </c>
       <c r="O3">
-        <v>-2.8773079103080056e-07</v>
+        <v>-2.8893583893147131e-07</v>
       </c>
       <c r="P3">
-        <v>2.8529170781301794e-07</v>
+        <v>3.1809939197751243e-07</v>
       </c>
       <c r="Q3">
-        <v>-2.88184855673491e-08</v>
+        <v>-9.2049423138635105e-08</v>
       </c>
       <c r="R3">
-        <v>-0.00013289368719563159</v>
+        <v>-0.00013339923347572137</v>
       </c>
       <c r="S3">
-        <v>-0.00013909063257459549</v>
+        <v>-0.00013984982154221666</v>
       </c>
       <c r="T3">
-        <v>-0.00013915259142187336</v>
+        <v>-0.00013983667603342863</v>
       </c>
       <c r="U3">
-        <v>9.2835608810035983e-05</v>
+        <v>9.4556681224327444e-05</v>
       </c>
       <c r="V3">
-        <v>-1.8199907419089623e-05</v>
+        <v>-1.7461056325237417e-05</v>
       </c>
       <c r="W3">
-        <v>3.4184986662915199e-05</v>
+        <v>3.4993562997956667e-05</v>
       </c>
       <c r="X3">
-        <v>7.0596743197700326e-06</v>
+        <v>7.0259324899972927e-06</v>
       </c>
       <c r="Y3">
-        <v>3.3498853011830892e-05</v>
+        <v>3.3636494439989339e-05</v>
       </c>
       <c r="Z3">
-        <v>1.2459658143304568e-05</v>
+        <v>1.2068406259105221e-05</v>
       </c>
       <c r="AA3">
-        <v>-2.8963431150097192e-07</v>
+        <v>-5.6742895563629365e-08</v>
       </c>
       <c r="AB3">
-        <v>2.9920934160534854e-06</v>
+        <v>3.1955560987219204e-06</v>
       </c>
       <c r="AC3">
-        <v>-7.7616755457745891e-07</v>
+        <v>-6.8472474563408703e-07</v>
       </c>
       <c r="AD3">
-        <v>2.9705298366321492e-06</v>
+        <v>3.2431857514446849e-06</v>
       </c>
       <c r="AE3">
-        <v>-7.6108715431803884e-07</v>
+        <v>-8.2469178198846168e-07</v>
       </c>
       <c r="AF3">
-        <v>-9.9309227653372669e-07</v>
+        <v>-1.0605696990893357e-06</v>
       </c>
       <c r="AG3">
-        <v>-7.3688707800804895e-08</v>
+        <v>-1.2611444277851479e-08</v>
       </c>
       <c r="AH3">
-        <v>-0.00028780368450828913</v>
+        <v>-1.7413413081221549e-06</v>
+      </c>
+      <c r="AI3">
+        <v>-5.8608815061820762e-06</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.00029159833162855969</v>
       </c>
     </row>
     <row r="4">
@@ -881,103 +905,109 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>0.00022222907925898292</v>
+        <v>0.0002226663494288233</v>
       </c>
       <c r="C4">
-        <v>3.3265319739136057e-08</v>
+        <v>3.3578253004639401e-08</v>
       </c>
       <c r="D4">
-        <v>-1.6785502349928611e-07</v>
+        <v>-1.6888010944626742e-07</v>
       </c>
       <c r="E4">
-        <v>1.663087318900021e-09</v>
+        <v>1.6727282583411538e-09</v>
       </c>
       <c r="F4">
-        <v>-1.0846835246964713e-07</v>
+        <v>-1.070237855945143e-07</v>
       </c>
       <c r="G4">
-        <v>1.1824028152076093e-08</v>
+        <v>1.0273546572809171e-08</v>
       </c>
       <c r="H4">
-        <v>6.6593286774008528e-08</v>
+        <v>6.671136080329205e-08</v>
       </c>
       <c r="I4">
-        <v>8.9202116180281253e-08</v>
+        <v>9.081154328071772e-08</v>
       </c>
       <c r="J4">
-        <v>7.9365608593560513e-09</v>
+        <v>7.7275767180458687e-09</v>
       </c>
       <c r="K4">
-        <v>-1.3769748027964034e-08</v>
+        <v>-1.4816671349479194e-08</v>
       </c>
       <c r="L4">
-        <v>2.4353636414914117e-08</v>
+        <v>2.4445942903902144e-08</v>
       </c>
       <c r="M4">
-        <v>-4.1022173935000866e-10</v>
+        <v>-7.2624813416632366e-10</v>
       </c>
       <c r="N4">
-        <v>-3.9222811388244211e-08</v>
+        <v>-3.958036537029314e-08</v>
       </c>
       <c r="O4">
-        <v>2.6493330990526786e-09</v>
+        <v>2.6591359089132346e-09</v>
       </c>
       <c r="P4">
-        <v>-6.538111937488371e-10</v>
+        <v>-9.4327821682507526e-10</v>
       </c>
       <c r="Q4">
-        <v>2.275567861549283e-09</v>
+        <v>2.9432057953050599e-09</v>
       </c>
       <c r="R4">
-        <v>1.1737753706095371e-06</v>
+        <v>1.178256127163396e-06</v>
       </c>
       <c r="S4">
-        <v>1.2684298192710072e-06</v>
+        <v>1.2750902600667099e-06</v>
       </c>
       <c r="T4">
-        <v>1.2844227315813218e-06</v>
+        <v>1.2905328601471298e-06</v>
       </c>
       <c r="U4">
-        <v>-9.0644583065478604e-07</v>
+        <v>-9.2138299886223013e-07</v>
       </c>
       <c r="V4">
-        <v>-2.5301988561612497e-08</v>
+        <v>-3.196357144212363e-08</v>
       </c>
       <c r="W4">
-        <v>-7.94541009372632e-07</v>
+        <v>-8.0194097487419187e-07</v>
       </c>
       <c r="X4">
-        <v>1.9096019429329625e-09</v>
+        <v>2.4718955330417382e-09</v>
       </c>
       <c r="Y4">
-        <v>-2.6422740261230321e-07</v>
+        <v>-2.6520618624859582e-07</v>
       </c>
       <c r="Z4">
-        <v>-2.3703806077740918e-08</v>
+        <v>-2.019680137828838e-08</v>
       </c>
       <c r="AA4">
-        <v>-4.3415141386539307e-09</v>
+        <v>-6.8232360607243115e-09</v>
       </c>
       <c r="AB4">
-        <v>-3.2763529015902064e-08</v>
+        <v>-3.4670737634483481e-08</v>
       </c>
       <c r="AC4">
-        <v>-9.6861377565618268e-09</v>
+        <v>-1.0666190224700449e-08</v>
       </c>
       <c r="AD4">
-        <v>-3.5228759364842849e-08</v>
+        <v>-3.7838868997234808e-08</v>
       </c>
       <c r="AE4">
-        <v>4.83441720118436e-09</v>
+        <v>5.3965842930057215e-09</v>
       </c>
       <c r="AF4">
-        <v>-8.1460225145584858e-10</v>
+        <v>-7.9962469026845007e-10</v>
       </c>
       <c r="AG4">
-        <v>-1.7697718347875624e-09</v>
+        <v>-2.1088776176912062e-09</v>
       </c>
       <c r="AH4">
-        <v>2.7132771203039535e-06</v>
+        <v>2.52249146753247e-10</v>
+      </c>
+      <c r="AI4">
+        <v>5.1451634562556878e-08</v>
+      </c>
+      <c r="AJ4">
+        <v>2.7453203057273422e-06</v>
       </c>
     </row>
     <row r="5">
@@ -985,103 +1015,109 @@
         <v>20</v>
       </c>
       <c r="B5">
-        <v>-0.11894398478598062</v>
+        <v>-0.1272697368254139</v>
       </c>
       <c r="C5">
-        <v>-6.0959814604424941e-06</v>
+        <v>-8.241966738302059e-06</v>
       </c>
       <c r="D5">
-        <v>3.8715113795570241e-06</v>
+        <v>3.7800642651957662e-06</v>
       </c>
       <c r="E5">
-        <v>-1.0846835246964713e-07</v>
+        <v>-1.070237855945143e-07</v>
       </c>
       <c r="F5">
-        <v>0.0069030181106416464</v>
+        <v>0.0070011271870271284</v>
       </c>
       <c r="G5">
-        <v>0.00089303193385478796</v>
+        <v>0.00089594544329824652</v>
       </c>
       <c r="H5">
-        <v>0.00074938583118323615</v>
+        <v>0.00075579857920740439</v>
       </c>
       <c r="I5">
-        <v>0.00058724131331214192</v>
+        <v>0.00059028655789596291</v>
       </c>
       <c r="J5">
-        <v>5.9629134612511602e-06</v>
+        <v>6.0484794832162373e-06</v>
       </c>
       <c r="K5">
-        <v>1.8915300501936842e-06</v>
+        <v>4.7606042383823601e-06</v>
       </c>
       <c r="L5">
-        <v>7.2551501351288175e-07</v>
+        <v>3.9998818759418743e-07</v>
       </c>
       <c r="M5">
-        <v>-1.0193228779546308e-05</v>
+        <v>-1.1265379461933814e-05</v>
       </c>
       <c r="N5">
-        <v>7.9664515972540967e-05</v>
+        <v>8.3427250543406401e-05</v>
       </c>
       <c r="O5">
-        <v>-1.7589163526709101e-07</v>
+        <v>-1.9504447077157633e-07</v>
       </c>
       <c r="P5">
-        <v>-6.0548709677588065e-06</v>
+        <v>-7.6681099742058539e-06</v>
       </c>
       <c r="Q5">
-        <v>8.2143268312577867e-06</v>
+        <v>9.5385467637937026e-06</v>
       </c>
       <c r="R5">
-        <v>-8.4748861329416817e-05</v>
+        <v>-8.6934742314077697e-05</v>
       </c>
       <c r="S5">
-        <v>-8.4694143457047713e-05</v>
+        <v>-9.0659463184927195e-05</v>
       </c>
       <c r="T5">
-        <v>-3.2755991009762988e-05</v>
+        <v>-3.7183345565693071e-05</v>
       </c>
       <c r="U5">
-        <v>5.4172295235524297e-05</v>
+        <v>7.3814813121306189e-05</v>
       </c>
       <c r="V5">
-        <v>-8.1881973549052258e-05</v>
+        <v>-6.1034824572332952e-05</v>
       </c>
       <c r="W5">
-        <v>-8.626780096255036e-05</v>
+        <v>-7.2887149255579191e-05</v>
       </c>
       <c r="X5">
-        <v>4.0877533799368282e-05</v>
+        <v>4.4439057352386403e-05</v>
       </c>
       <c r="Y5">
-        <v>5.0404522487951546e-05</v>
+        <v>5.7182990474016758e-05</v>
       </c>
       <c r="Z5">
-        <v>2.6840814959948789e-06</v>
+        <v>7.3325191904736575e-06</v>
       </c>
       <c r="AA5">
-        <v>-0.00035665476068260933</v>
+        <v>-0.0003879657408031901</v>
       </c>
       <c r="AB5">
-        <v>-0.00031278162733416247</v>
+        <v>-0.0003438759676396907</v>
       </c>
       <c r="AC5">
-        <v>-0.00029149891908651052</v>
+        <v>-0.00032144368232211009</v>
       </c>
       <c r="AD5">
-        <v>-0.00030614056520443549</v>
+        <v>-0.00033621321242632862</v>
       </c>
       <c r="AE5">
-        <v>-0.00030570504301377589</v>
+        <v>-0.00033238896329270599</v>
       </c>
       <c r="AF5">
-        <v>-0.00030864186912341182</v>
+        <v>-0.00033821930018997277</v>
       </c>
       <c r="AG5">
-        <v>1.312790935562137e-06</v>
+        <v>-1.0847629299590987e-06</v>
       </c>
       <c r="AH5">
-        <v>-0.00015056543033221308</v>
+        <v>0.0001415248638067281</v>
+      </c>
+      <c r="AI5">
+        <v>9.6796122039921882e-05</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.00011587260424335971</v>
       </c>
     </row>
     <row r="6">
@@ -1089,103 +1125,109 @@
         <v>21</v>
       </c>
       <c r="B6">
-        <v>-0.15799272093562175</v>
+        <v>-0.1688379343589245</v>
       </c>
       <c r="C6">
-        <v>1.9222037769233948e-05</v>
+        <v>1.855934931981686e-05</v>
       </c>
       <c r="D6">
-        <v>-9.5020304315485756e-06</v>
+        <v>-9.4488630177101824e-06</v>
       </c>
       <c r="E6">
-        <v>1.1824028152076093e-08</v>
+        <v>1.0273546572809171e-08</v>
       </c>
       <c r="F6">
-        <v>0.00089303193385478796</v>
+        <v>0.00089594544329824652</v>
       </c>
       <c r="G6">
-        <v>0.0023015634132054329</v>
+        <v>0.0023041814130098995</v>
       </c>
       <c r="H6">
-        <v>0.00077781750078962937</v>
+        <v>0.00077996021318262672</v>
       </c>
       <c r="I6">
-        <v>0.0005934377547757696</v>
+        <v>0.0005952103883234025</v>
       </c>
       <c r="J6">
-        <v>8.796549220679139e-06</v>
+        <v>7.7739891524872083e-06</v>
       </c>
       <c r="K6">
-        <v>1.1849337779196809e-05</v>
+        <v>1.2262476722449255e-05</v>
       </c>
       <c r="L6">
-        <v>3.0704944980222247e-06</v>
+        <v>2.8329295447831688e-06</v>
       </c>
       <c r="M6">
-        <v>-9.9612791581779276e-06</v>
+        <v>-9.8463402691600676e-06</v>
       </c>
       <c r="N6">
-        <v>4.7684286516681535e-05</v>
+        <v>5.25249177570374e-05</v>
       </c>
       <c r="O6">
-        <v>1.0792745720968088e-07</v>
+        <v>1.002143807837706e-07</v>
       </c>
       <c r="P6">
-        <v>-8.5154949488814529e-06</v>
+        <v>-8.8487608585180564e-06</v>
       </c>
       <c r="Q6">
-        <v>1.1073215599314283e-05</v>
+        <v>1.159891588002625e-05</v>
       </c>
       <c r="R6">
-        <v>-1.2104100224375977e-05</v>
+        <v>-9.9597856857855599e-06</v>
       </c>
       <c r="S6">
-        <v>5.7740975907146489e-05</v>
+        <v>5.8883803869194855e-05</v>
       </c>
       <c r="T6">
-        <v>8.5622407482293853e-05</v>
+        <v>8.8132520044139427e-05</v>
       </c>
       <c r="U6">
-        <v>8.3036332029209447e-05</v>
+        <v>8.5320300293013223e-05</v>
       </c>
       <c r="V6">
-        <v>1.6375039565686615e-05</v>
+        <v>1.7200407890189924e-05</v>
       </c>
       <c r="W6">
-        <v>7.0723872223454209e-05</v>
+        <v>7.3103565255648747e-05</v>
       </c>
       <c r="X6">
-        <v>3.497730833551634e-05</v>
+        <v>3.3090857626206661e-05</v>
       </c>
       <c r="Y6">
-        <v>-1.8459387842582608e-06</v>
+        <v>-3.0687237558719e-06</v>
       </c>
       <c r="Z6">
-        <v>0.00010042887687203324</v>
+        <v>0.00010496985164197403</v>
       </c>
       <c r="AA6">
-        <v>-3.9753025021668992e-07</v>
+        <v>-7.4596915694141459e-06</v>
       </c>
       <c r="AB6">
-        <v>6.2341965845422702e-05</v>
+        <v>5.4673612840301764e-05</v>
       </c>
       <c r="AC6">
-        <v>5.4421947256034584e-05</v>
+        <v>4.9310795184917987e-05</v>
       </c>
       <c r="AD6">
-        <v>5.3714956046137257e-05</v>
+        <v>4.5919926953411143e-05</v>
       </c>
       <c r="AE6">
-        <v>6.5974288557758365e-05</v>
+        <v>6.1274752174575741e-05</v>
       </c>
       <c r="AF6">
-        <v>6.9240617735101252e-05</v>
+        <v>6.3162003885449379e-05</v>
       </c>
       <c r="AG6">
-        <v>-9.143016305353215e-07</v>
+        <v>-7.7394332615398398e-07</v>
       </c>
       <c r="AH6">
-        <v>-0.00034746826021087105</v>
+        <v>-2.2030612711127417e-05</v>
+      </c>
+      <c r="AI6">
+        <v>3.1578757810894997e-05</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.00034392369399797193</v>
       </c>
     </row>
     <row r="7">
@@ -1193,103 +1235,109 @@
         <v>22</v>
       </c>
       <c r="B7">
-        <v>-0.09000199343080241</v>
+        <v>-0.098748510927967229</v>
       </c>
       <c r="C7">
-        <v>3.3616512975651253e-07</v>
+        <v>-1.6690760842623853e-08</v>
       </c>
       <c r="D7">
-        <v>-1.4180418073471551e-05</v>
+        <v>-1.4270496977472148e-05</v>
       </c>
       <c r="E7">
-        <v>6.6593286774008528e-08</v>
+        <v>6.671136080329205e-08</v>
       </c>
       <c r="F7">
-        <v>0.00074938583118323615</v>
+        <v>0.00075579857920740439</v>
       </c>
       <c r="G7">
-        <v>0.00077781750078962937</v>
+        <v>0.00077996021318262672</v>
       </c>
       <c r="H7">
-        <v>0.0011315053642052654</v>
+        <v>0.0011315132796168752</v>
       </c>
       <c r="I7">
-        <v>0.0005878337582678391</v>
+        <v>0.00058888876881138085</v>
       </c>
       <c r="J7">
-        <v>4.2357679139632553e-06</v>
+        <v>3.2360955125311024e-06</v>
       </c>
       <c r="K7">
-        <v>2.0786111657702558e-05</v>
+        <v>2.0982357384107968e-05</v>
       </c>
       <c r="L7">
-        <v>2.0729995756803925e-06</v>
+        <v>1.9737877711997582e-06</v>
       </c>
       <c r="M7">
-        <v>-2.898844185125591e-06</v>
+        <v>-2.542223090869507e-06</v>
       </c>
       <c r="N7">
-        <v>6.7351037229235766e-05</v>
+        <v>7.054752164711747e-05</v>
       </c>
       <c r="O7">
-        <v>1.6384444896190105e-07</v>
+        <v>1.4424970242157938e-07</v>
       </c>
       <c r="P7">
-        <v>-6.5998867637764146e-06</v>
+        <v>-6.6178325936134106e-06</v>
       </c>
       <c r="Q7">
-        <v>5.9116496688289687e-06</v>
+        <v>6.7493930827819065e-06</v>
       </c>
       <c r="R7">
-        <v>5.4293659110573666e-05</v>
+        <v>5.1677075663596421e-05</v>
       </c>
       <c r="S7">
-        <v>7.7710050512130055e-05</v>
+        <v>7.3886624544214119e-05</v>
       </c>
       <c r="T7">
-        <v>0.00012302769918354166</v>
+        <v>0.00012020170536684142</v>
       </c>
       <c r="U7">
-        <v>0.00014629105508320726</v>
+        <v>0.00014718677037586051</v>
       </c>
       <c r="V7">
-        <v>0.00011471605355682865</v>
+        <v>0.00011459949982876333</v>
       </c>
       <c r="W7">
-        <v>0.00014042705096554026</v>
+        <v>0.00014111864591351823</v>
       </c>
       <c r="X7">
-        <v>2.7588099927021692e-05</v>
+        <v>2.723835413366407e-05</v>
       </c>
       <c r="Y7">
-        <v>-9.6900770293089894e-06</v>
+        <v>-9.4038118989487331e-06</v>
       </c>
       <c r="Z7">
-        <v>2.2871316319884326e-05</v>
+        <v>3.5154995881514023e-05</v>
       </c>
       <c r="AA7">
-        <v>1.1202492387732697e-05</v>
+        <v>-3.0570556696946517e-07</v>
       </c>
       <c r="AB7">
-        <v>4.0732752038115892e-05</v>
+        <v>2.9363457396843162e-05</v>
       </c>
       <c r="AC7">
-        <v>4.2613918864713538e-05</v>
+        <v>3.4039029180815849e-05</v>
       </c>
       <c r="AD7">
-        <v>4.362694109231747e-05</v>
+        <v>3.1579243025551076e-05</v>
       </c>
       <c r="AE7">
-        <v>6.1628326391954697e-05</v>
+        <v>5.5209910383559709e-05</v>
       </c>
       <c r="AF7">
-        <v>4.9979475708497805e-05</v>
+        <v>4.0949210002263745e-05</v>
       </c>
       <c r="AG7">
-        <v>-4.1721118033656768e-06</v>
+        <v>-3.6728508684652067e-06</v>
       </c>
       <c r="AH7">
-        <v>-0.0002912081307662889</v>
+        <v>-2.6350577141604002e-06</v>
+      </c>
+      <c r="AI7">
+        <v>1.7121646091136532e-05</v>
+      </c>
+      <c r="AJ7">
+        <v>-0.00028215220952928924</v>
       </c>
     </row>
     <row r="8">
@@ -1297,103 +1345,109 @@
         <v>23</v>
       </c>
       <c r="B8">
-        <v>-0.035237987944406982</v>
+        <v>-0.040879888998375774</v>
       </c>
       <c r="C8">
-        <v>-9.4071768424800991e-07</v>
+        <v>-7.3914409938055097e-07</v>
       </c>
       <c r="D8">
-        <v>-1.2255673480901987e-05</v>
+        <v>-1.2432825514939752e-05</v>
       </c>
       <c r="E8">
-        <v>8.9202116180281253e-08</v>
+        <v>9.081154328071772e-08</v>
       </c>
       <c r="F8">
-        <v>0.00058724131331214192</v>
+        <v>0.00059028655789596291</v>
       </c>
       <c r="G8">
-        <v>0.0005934377547757696</v>
+        <v>0.0005952103883234025</v>
       </c>
       <c r="H8">
-        <v>0.0005878337582678391</v>
+        <v>0.00058888876881138085</v>
       </c>
       <c r="I8">
-        <v>0.00068931284603347936</v>
+        <v>0.00069174820066388628</v>
       </c>
       <c r="J8">
-        <v>2.6417807943617867e-06</v>
+        <v>2.0368523341756255e-06</v>
       </c>
       <c r="K8">
-        <v>2.5238308197965248e-06</v>
+        <v>2.5789119911564537e-06</v>
       </c>
       <c r="L8">
-        <v>9.0660575383667505e-08</v>
+        <v>5.5289611406675109e-08</v>
       </c>
       <c r="M8">
-        <v>-4.7982660206105442e-06</v>
+        <v>-4.3570862052101599e-06</v>
       </c>
       <c r="N8">
-        <v>8.2170133663235178e-05</v>
+        <v>8.6852708167312485e-05</v>
       </c>
       <c r="O8">
-        <v>-3.469218407606828e-08</v>
+        <v>-3.5753092428886456e-08</v>
       </c>
       <c r="P8">
-        <v>-4.6355220483620501e-06</v>
+        <v>-5.4800625058765496e-06</v>
       </c>
       <c r="Q8">
-        <v>6.1050641238750348e-06</v>
+        <v>6.5896982252864441e-06</v>
       </c>
       <c r="R8">
-        <v>-1.370963977263276e-05</v>
+        <v>-9.9348736545875816e-06</v>
       </c>
       <c r="S8">
-        <v>-1.2827912515240126e-05</v>
+        <v>-1.0058234629685758e-05</v>
       </c>
       <c r="T8">
-        <v>1.6990177490073276e-05</v>
+        <v>2.1311724134353537e-05</v>
       </c>
       <c r="U8">
-        <v>1.0929610966390181e-05</v>
+        <v>1.1399888685241705e-05</v>
       </c>
       <c r="V8">
-        <v>1.3374220194669543e-05</v>
+        <v>1.307100996085454e-05</v>
       </c>
       <c r="W8">
-        <v>2.1542359730252847e-05</v>
+        <v>2.0899714964468818e-05</v>
       </c>
       <c r="X8">
-        <v>1.2382438929014677e-05</v>
+        <v>1.1635607613298661e-05</v>
       </c>
       <c r="Y8">
-        <v>7.2643634315007145e-06</v>
+        <v>7.0885674723720956e-06</v>
       </c>
       <c r="Z8">
-        <v>2.0656766935375653e-05</v>
+        <v>2.3598843092312557e-05</v>
       </c>
       <c r="AA8">
-        <v>-3.2349431402661517e-05</v>
+        <v>-3.490996641805142e-05</v>
       </c>
       <c r="AB8">
-        <v>-1.7887042008131091e-05</v>
+        <v>-2.0527092432584375e-05</v>
       </c>
       <c r="AC8">
-        <v>-5.894578668109681e-06</v>
+        <v>-7.3287296165411089e-06</v>
       </c>
       <c r="AD8">
-        <v>-1.3738714630288901e-05</v>
+        <v>-1.6400313896113033e-05</v>
       </c>
       <c r="AE8">
-        <v>1.6392407808113615e-06</v>
+        <v>7.8808003916201817e-07</v>
       </c>
       <c r="AF8">
-        <v>-7.9407637682717063e-06</v>
+        <v>-1.0023184592857515e-05</v>
       </c>
       <c r="AG8">
-        <v>-2.6956156767708938e-06</v>
+        <v>-2.2712442873387257e-06</v>
       </c>
       <c r="AH8">
-        <v>-0.00013817329010755008</v>
+        <v>-2.4612296879961913e-05</v>
+      </c>
+      <c r="AI8">
+        <v>3.2512755883705105e-06</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.00014186833008786152</v>
       </c>
     </row>
     <row r="9">
@@ -1401,103 +1455,109 @@
         <v>24</v>
       </c>
       <c r="B9">
-        <v>0.52094305766110649</v>
+        <v>0.52230224930162195</v>
       </c>
       <c r="C9">
-        <v>1.9342654812550678e-06</v>
+        <v>1.6071703646335672e-06</v>
       </c>
       <c r="D9">
-        <v>-9.864825399419761e-07</v>
+        <v>-9.6927094243349794e-07</v>
       </c>
       <c r="E9">
-        <v>7.9365608593560513e-09</v>
+        <v>7.7275767180458687e-09</v>
       </c>
       <c r="F9">
-        <v>5.9629134612511602e-06</v>
+        <v>6.0484794832162373e-06</v>
       </c>
       <c r="G9">
-        <v>8.796549220679139e-06</v>
+        <v>7.7739891524872083e-06</v>
       </c>
       <c r="H9">
-        <v>4.2357679139632553e-06</v>
+        <v>3.2360955125311024e-06</v>
       </c>
       <c r="I9">
-        <v>2.6417807943617867e-06</v>
+        <v>2.0368523341756255e-06</v>
       </c>
       <c r="J9">
-        <v>5.4298826176083947e-05</v>
+        <v>5.4637988424876221e-05</v>
       </c>
       <c r="K9">
-        <v>-6.2722499326892359e-06</v>
+        <v>-6.589703952821758e-06</v>
       </c>
       <c r="L9">
-        <v>6.517558633111074e-07</v>
+        <v>6.727853820748999e-07</v>
       </c>
       <c r="M9">
-        <v>-2.1006686263617072e-05</v>
+        <v>-2.1129394291012563e-05</v>
       </c>
       <c r="N9">
-        <v>-1.6125883602401086e-06</v>
+        <v>-1.5943984269933549e-06</v>
       </c>
       <c r="O9">
-        <v>1.5347041682199427e-08</v>
+        <v>1.3473076405657386e-08</v>
       </c>
       <c r="P9">
-        <v>-5.5559429458063994e-05</v>
+        <v>-5.5738154889283928e-05</v>
       </c>
       <c r="Q9">
-        <v>2.1856245634203768e-05</v>
+        <v>2.2172052801245286e-05</v>
       </c>
       <c r="R9">
-        <v>-1.4587525947807571e-05</v>
+        <v>-1.4521490597421205e-05</v>
       </c>
       <c r="S9">
-        <v>-1.5959082681540526e-05</v>
+        <v>-1.6105590771735326e-05</v>
       </c>
       <c r="T9">
-        <v>-1.8387298203976624e-05</v>
+        <v>-1.8653698068622268e-05</v>
       </c>
       <c r="U9">
-        <v>-5.0935754477921896e-05</v>
+        <v>-5.3257989886495712e-05</v>
       </c>
       <c r="V9">
-        <v>-4.9516874433796827e-05</v>
+        <v>-5.1986896564435784e-05</v>
       </c>
       <c r="W9">
-        <v>-5.6314680192282662e-05</v>
+        <v>-5.8470650969077207e-05</v>
       </c>
       <c r="X9">
-        <v>1.598184924259426e-06</v>
+        <v>1.9745750342813263e-06</v>
       </c>
       <c r="Y9">
-        <v>-5.5936669005860406e-07</v>
+        <v>-9.8666629231824524e-08</v>
       </c>
       <c r="Z9">
-        <v>1.0739068533409171e-05</v>
+        <v>1.1311372692250869e-05</v>
       </c>
       <c r="AA9">
-        <v>6.7777764299665312e-06</v>
+        <v>4.8588571204757222e-06</v>
       </c>
       <c r="AB9">
-        <v>7.7405084287827147e-06</v>
+        <v>5.9795931515586247e-06</v>
       </c>
       <c r="AC9">
-        <v>5.1500515317105544e-06</v>
+        <v>3.8411332852990127e-06</v>
       </c>
       <c r="AD9">
-        <v>2.1048768021260701e-06</v>
+        <v>3.582330656313413e-07</v>
       </c>
       <c r="AE9">
-        <v>7.0349394531768444e-06</v>
+        <v>5.711689207059639e-06</v>
       </c>
       <c r="AF9">
-        <v>1.4171980792534952e-05</v>
+        <v>1.2897999056349304e-05</v>
       </c>
       <c r="AG9">
-        <v>7.1113663786945166e-07</v>
+        <v>9.7116927496613578e-07</v>
       </c>
       <c r="AH9">
-        <v>3.8241408493853369e-05</v>
+        <v>-1.5609354672070172e-06</v>
+      </c>
+      <c r="AI9">
+        <v>-1.3730403899072507e-05</v>
+      </c>
+      <c r="AJ9">
+        <v>3.89467405004832e-05</v>
       </c>
     </row>
     <row r="10">
@@ -1505,103 +1565,109 @@
         <v>25</v>
       </c>
       <c r="B10">
-        <v>0.12169763432759727</v>
+        <v>0.11838812140458939</v>
       </c>
       <c r="C10">
-        <v>-5.7624821228866908e-05</v>
+        <v>-5.7547310330336932e-05</v>
       </c>
       <c r="D10">
-        <v>-1.0834928015026822e-06</v>
+        <v>-9.6672651619156798e-07</v>
       </c>
       <c r="E10">
-        <v>-1.3769748027964034e-08</v>
+        <v>-1.4816671349479194e-08</v>
       </c>
       <c r="F10">
-        <v>1.8915300501936842e-06</v>
+        <v>4.7606042383823601e-06</v>
       </c>
       <c r="G10">
-        <v>1.1849337779196809e-05</v>
+        <v>1.2262476722449255e-05</v>
       </c>
       <c r="H10">
-        <v>2.0786111657702558e-05</v>
+        <v>2.0982357384107968e-05</v>
       </c>
       <c r="I10">
-        <v>2.5238308197965248e-06</v>
+        <v>2.5789119911564537e-06</v>
       </c>
       <c r="J10">
-        <v>-6.2722499326892359e-06</v>
+        <v>-6.589703952821758e-06</v>
       </c>
       <c r="K10">
-        <v>0.00040318265792177037</v>
+        <v>0.00040416536467221626</v>
       </c>
       <c r="L10">
-        <v>-2.444351813277091e-05</v>
+        <v>-2.46725333418743e-05</v>
       </c>
       <c r="M10">
-        <v>-2.105745013406545e-07</v>
+        <v>-1.4549384709005733e-07</v>
       </c>
       <c r="N10">
-        <v>5.7188767927676616e-05</v>
+        <v>5.794569055239447e-05</v>
       </c>
       <c r="O10">
-        <v>-3.57267789138076e-08</v>
+        <v>-4.2195512494135536e-08</v>
       </c>
       <c r="P10">
-        <v>4.9742589554302227e-06</v>
+        <v>5.259438075629881e-06</v>
       </c>
       <c r="Q10">
-        <v>1.6116678415521154e-06</v>
+        <v>1.5325239321903013e-06</v>
       </c>
       <c r="R10">
-        <v>7.5268081404743865e-05</v>
+        <v>7.2942141221193967e-05</v>
       </c>
       <c r="S10">
-        <v>4.1560520250256858e-05</v>
+        <v>3.8903304867473406e-05</v>
       </c>
       <c r="T10">
-        <v>-4.0093540460861771e-05</v>
+        <v>-4.2076096725377865e-05</v>
       </c>
       <c r="U10">
-        <v>0.0029916827384938714</v>
+        <v>0.002999366440053402</v>
       </c>
       <c r="V10">
-        <v>0.003045095528134539</v>
+        <v>0.003052238522011635</v>
       </c>
       <c r="W10">
-        <v>0.0030868104116333612</v>
+        <v>0.0030930118556961434</v>
       </c>
       <c r="X10">
-        <v>-1.3878111332322801e-05</v>
+        <v>-1.42044052615582e-05</v>
       </c>
       <c r="Y10">
-        <v>1.4850935956310212e-05</v>
+        <v>1.5362234224736333e-05</v>
       </c>
       <c r="Z10">
-        <v>-2.7042754110714645e-05</v>
+        <v>-2.5286700238444392e-05</v>
       </c>
       <c r="AA10">
-        <v>-1.3495049181258111e-05</v>
+        <v>-1.2605071197613945e-05</v>
       </c>
       <c r="AB10">
-        <v>-4.968256124866983e-05</v>
+        <v>-4.8552193531725685e-05</v>
       </c>
       <c r="AC10">
-        <v>-6.5003285620603179e-05</v>
+        <v>-6.3493944229510251e-05</v>
       </c>
       <c r="AD10">
-        <v>-7.6640437867028875e-06</v>
+        <v>-6.7674234959375079e-06</v>
       </c>
       <c r="AE10">
-        <v>-3.3770335514039535e-05</v>
+        <v>-3.2184299087756286e-05</v>
       </c>
       <c r="AF10">
-        <v>-2.860533445252938e-05</v>
+        <v>-2.8043883466234308e-05</v>
       </c>
       <c r="AG10">
-        <v>-6.5742139252626447e-07</v>
+        <v>-5.0741236670478877e-07</v>
       </c>
       <c r="AH10">
-        <v>-0.0029148802844716684</v>
+        <v>-1.4728989282367707e-05</v>
+      </c>
+      <c r="AI10">
+        <v>6.3375947813017154e-06</v>
+      </c>
+      <c r="AJ10">
+        <v>-0.0029244195253660971</v>
       </c>
     </row>
     <row r="11">
@@ -1609,103 +1675,109 @@
         <v>26</v>
       </c>
       <c r="B11">
-        <v>0.013758111123401511</v>
+        <v>0.014659101291421114</v>
       </c>
       <c r="C11">
-        <v>-5.718589117759293e-06</v>
+        <v>-5.6414867353351785e-06</v>
       </c>
       <c r="D11">
-        <v>-2.6060318885225805e-06</v>
+        <v>-2.6211966690228471e-06</v>
       </c>
       <c r="E11">
-        <v>2.4353636414914117e-08</v>
+        <v>2.4445942903902144e-08</v>
       </c>
       <c r="F11">
-        <v>7.2551501351288175e-07</v>
+        <v>3.9998818759418743e-07</v>
       </c>
       <c r="G11">
-        <v>3.0704944980222247e-06</v>
+        <v>2.8329295447831688e-06</v>
       </c>
       <c r="H11">
-        <v>2.0729995756803925e-06</v>
+        <v>1.9737877711997582e-06</v>
       </c>
       <c r="I11">
-        <v>9.0660575383667505e-08</v>
+        <v>5.5289611406675109e-08</v>
       </c>
       <c r="J11">
-        <v>6.517558633111074e-07</v>
+        <v>6.727853820748999e-07</v>
       </c>
       <c r="K11">
-        <v>-2.444351813277091e-05</v>
+        <v>-2.46725333418743e-05</v>
       </c>
       <c r="L11">
-        <v>2.0606350761556701e-05</v>
+        <v>2.0645238593851432e-05</v>
       </c>
       <c r="M11">
-        <v>5.2446366371917843e-07</v>
+        <v>5.1357797594993791e-07</v>
       </c>
       <c r="N11">
-        <v>5.5681979030883015e-06</v>
+        <v>5.4187298588879362e-06</v>
       </c>
       <c r="O11">
-        <v>2.566161407327924e-08</v>
+        <v>2.5109967207929017e-08</v>
       </c>
       <c r="P11">
-        <v>-1.0836245148114824e-06</v>
+        <v>-1.0909205124439425e-06</v>
       </c>
       <c r="Q11">
-        <v>-2.3286269359875828e-07</v>
+        <v>-1.6022301973270842e-07</v>
       </c>
       <c r="R11">
-        <v>9.1571775018034444e-06</v>
+        <v>8.7873443139225703e-06</v>
       </c>
       <c r="S11">
-        <v>6.2764350888560335e-06</v>
+        <v>6.0585243863096099e-06</v>
       </c>
       <c r="T11">
-        <v>2.1260633326848366e-06</v>
+        <v>1.8206085427353066e-06</v>
       </c>
       <c r="U11">
-        <v>-7.5643521075182982e-05</v>
+        <v>-7.7503693165586649e-05</v>
       </c>
       <c r="V11">
-        <v>-7.7127714590427421e-05</v>
+        <v>-7.8663409873098978e-05</v>
       </c>
       <c r="W11">
-        <v>-6.4099077036030045e-05</v>
+        <v>-6.546711117600631e-05</v>
       </c>
       <c r="X11">
-        <v>-3.8179162124950021e-06</v>
+        <v>-3.9028183123111055e-06</v>
       </c>
       <c r="Y11">
-        <v>8.747500839220292e-08</v>
+        <v>1.4581552651866553e-07</v>
       </c>
       <c r="Z11">
-        <v>-1.3947854852402062e-05</v>
+        <v>-1.3796579052501655e-05</v>
       </c>
       <c r="AA11">
-        <v>4.0115925639870137e-06</v>
+        <v>3.617953627115794e-06</v>
       </c>
       <c r="AB11">
-        <v>3.056533745855855e-06</v>
+        <v>2.67415623426097e-06</v>
       </c>
       <c r="AC11">
-        <v>4.1252634444072315e-06</v>
+        <v>3.9441884765833681e-06</v>
       </c>
       <c r="AD11">
-        <v>3.8857613465943921e-06</v>
+        <v>3.5712211650880036e-06</v>
       </c>
       <c r="AE11">
-        <v>3.2539170285022785e-06</v>
+        <v>2.9579091092853315e-06</v>
       </c>
       <c r="AF11">
-        <v>3.3464814574087493e-06</v>
+        <v>3.1652168661934511e-06</v>
       </c>
       <c r="AG11">
-        <v>-2.7301158488969425e-07</v>
+        <v>-2.2299980491866647e-07</v>
       </c>
       <c r="AH11">
-        <v>0.00011060536569436742</v>
+        <v>-1.2428005193927032e-06</v>
+      </c>
+      <c r="AI11">
+        <v>-2.4194662693187976e-06</v>
+      </c>
+      <c r="AJ11">
+        <v>0.00011265633956514313</v>
       </c>
     </row>
     <row r="12">
@@ -1713,103 +1785,109 @@
         <v>27</v>
       </c>
       <c r="B12">
-        <v>0.29249082093949219</v>
+        <v>0.29268427736767672</v>
       </c>
       <c r="C12">
-        <v>-9.3407144047405155e-07</v>
+        <v>-8.3731349492827086e-07</v>
       </c>
       <c r="D12">
-        <v>-3.1338989980077789e-07</v>
+        <v>-2.8019044137940674e-07</v>
       </c>
       <c r="E12">
-        <v>-4.1022173935000866e-10</v>
+        <v>-7.2624813416632366e-10</v>
       </c>
       <c r="F12">
-        <v>-1.0193228779546308e-05</v>
+        <v>-1.1265379461933814e-05</v>
       </c>
       <c r="G12">
-        <v>-9.9612791581779276e-06</v>
+        <v>-9.8463402691600676e-06</v>
       </c>
       <c r="H12">
-        <v>-2.898844185125591e-06</v>
+        <v>-2.542223090869507e-06</v>
       </c>
       <c r="I12">
-        <v>-4.7982660206105442e-06</v>
+        <v>-4.3570862052101599e-06</v>
       </c>
       <c r="J12">
-        <v>-2.1006686263617072e-05</v>
+        <v>-2.1129394291012563e-05</v>
       </c>
       <c r="K12">
-        <v>-2.105745013406545e-07</v>
+        <v>-1.4549384709005733e-07</v>
       </c>
       <c r="L12">
-        <v>5.2446366371917843e-07</v>
+        <v>5.1357797594993791e-07</v>
       </c>
       <c r="M12">
-        <v>4.1543895088285499e-05</v>
+        <v>4.1741776084694758e-05</v>
       </c>
       <c r="N12">
-        <v>3.0348697276402229e-07</v>
+        <v>9.082504181894794e-08</v>
       </c>
       <c r="O12">
-        <v>6.4978665811687819e-09</v>
+        <v>5.6320424013921407e-09</v>
       </c>
       <c r="P12">
-        <v>2.4102036469438977e-05</v>
+        <v>2.4114701378240636e-05</v>
       </c>
       <c r="Q12">
-        <v>-4.2024789614385775e-05</v>
+        <v>-4.2136373622518569e-05</v>
       </c>
       <c r="R12">
-        <v>2.5659523892040982e-07</v>
+        <v>-2.2297393878621718e-07</v>
       </c>
       <c r="S12">
-        <v>-5.8629824426148105e-06</v>
+        <v>-6.248287619315995e-06</v>
       </c>
       <c r="T12">
-        <v>-9.9853199002744104e-06</v>
+        <v>-1.0596812772207388e-05</v>
       </c>
       <c r="U12">
-        <v>1.3244037329865431e-05</v>
+        <v>1.436465799518815e-05</v>
       </c>
       <c r="V12">
-        <v>-1.3895136511261135e-06</v>
+        <v>-9.063151714073773e-07</v>
       </c>
       <c r="W12">
-        <v>1.2131480104485105e-06</v>
+        <v>1.7803446417798033e-06</v>
       </c>
       <c r="X12">
-        <v>4.8353945859318536e-06</v>
+        <v>4.4989500669006581e-06</v>
       </c>
       <c r="Y12">
-        <v>-1.6592569004102378e-06</v>
+        <v>-1.9094483336881404e-06</v>
       </c>
       <c r="Z12">
-        <v>-2.6543288045339635e-05</v>
+        <v>-2.7157703428098845e-05</v>
       </c>
       <c r="AA12">
-        <v>-5.1284221121947723e-06</v>
+        <v>-3.6761612594367478e-06</v>
       </c>
       <c r="AB12">
-        <v>-8.2864567449780173e-06</v>
+        <v>-7.0413633157318348e-06</v>
       </c>
       <c r="AC12">
-        <v>-6.7021501247420185e-06</v>
+        <v>-5.5340363770648717e-06</v>
       </c>
       <c r="AD12">
-        <v>-6.0174381488210799e-06</v>
+        <v>-4.717933822105455e-06</v>
       </c>
       <c r="AE12">
-        <v>-7.3972617268349515e-06</v>
+        <v>-6.538428092497768e-06</v>
       </c>
       <c r="AF12">
-        <v>-3.929834504762094e-06</v>
+        <v>-2.9057213094194881e-06</v>
       </c>
       <c r="AG12">
-        <v>1.4314811093280512e-06</v>
+        <v>1.4247585618967477e-06</v>
       </c>
       <c r="AH12">
-        <v>-2.6282177451205223e-05</v>
+        <v>-2.2626364425119899e-06</v>
+      </c>
+      <c r="AI12">
+        <v>-2.5026242273638586e-06</v>
+      </c>
+      <c r="AJ12">
+        <v>-2.8201969746309123e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1817,103 +1895,109 @@
         <v>28</v>
       </c>
       <c r="B13">
-        <v>0.089268077716273264</v>
+        <v>0.089514165590736716</v>
       </c>
       <c r="C13">
-        <v>-0.00042433242154412705</v>
+        <v>-0.00042477101755662413</v>
       </c>
       <c r="D13">
-        <v>8.2333549944939496e-07</v>
+        <v>8.6552023993750523e-07</v>
       </c>
       <c r="E13">
-        <v>-3.9222811388244211e-08</v>
+        <v>-3.958036537029314e-08</v>
       </c>
       <c r="F13">
-        <v>7.9664515972540967e-05</v>
+        <v>8.3427250543406401e-05</v>
       </c>
       <c r="G13">
-        <v>4.7684286516681535e-05</v>
+        <v>5.25249177570374e-05</v>
       </c>
       <c r="H13">
-        <v>6.7351037229235766e-05</v>
+        <v>7.054752164711747e-05</v>
       </c>
       <c r="I13">
-        <v>8.2170133663235178e-05</v>
+        <v>8.6852708167312485e-05</v>
       </c>
       <c r="J13">
-        <v>-1.6125883602401086e-06</v>
+        <v>-1.5943984269933549e-06</v>
       </c>
       <c r="K13">
-        <v>5.7188767927676616e-05</v>
+        <v>5.794569055239447e-05</v>
       </c>
       <c r="L13">
-        <v>5.5681979030883015e-06</v>
+        <v>5.4187298588879362e-06</v>
       </c>
       <c r="M13">
-        <v>3.0348697276402229e-07</v>
+        <v>9.082504181894794e-08</v>
       </c>
       <c r="N13">
-        <v>0.0086194386277107776</v>
+        <v>0.0086560143558350976</v>
       </c>
       <c r="O13">
-        <v>1.6668655581624485e-06</v>
+        <v>1.5224934966399831e-06</v>
       </c>
       <c r="P13">
-        <v>-5.1067064288901992e-06</v>
+        <v>-1.2797378699486503e-05</v>
       </c>
       <c r="Q13">
-        <v>5.2569499553637474e-05</v>
+        <v>5.5769530201830141e-05</v>
       </c>
       <c r="R13">
-        <v>0.0050754832797341408</v>
+        <v>0.0050136053871246969</v>
       </c>
       <c r="S13">
-        <v>0.0050501878930057</v>
+        <v>0.0049888765242035709</v>
       </c>
       <c r="T13">
-        <v>0.0050232044529128564</v>
+        <v>0.0049611952792562239</v>
       </c>
       <c r="U13">
-        <v>0.00047562031389892546</v>
+        <v>0.00047718190255935291</v>
       </c>
       <c r="V13">
-        <v>0.00038695768746498235</v>
+        <v>0.0003922445210037314</v>
       </c>
       <c r="W13">
-        <v>0.00054069489522240097</v>
+        <v>0.00054544506682772985</v>
       </c>
       <c r="X13">
-        <v>-4.6782119701288202e-05</v>
+        <v>-4.7132921023004847e-05</v>
       </c>
       <c r="Y13">
-        <v>7.8108018194332453e-07</v>
+        <v>1.7089749209726239e-06</v>
       </c>
       <c r="Z13">
-        <v>-0.00019455881047950019</v>
+        <v>-0.00019790241739100958</v>
       </c>
       <c r="AA13">
-        <v>-8.2672830506223035e-05</v>
+        <v>-8.8766111784358784e-05</v>
       </c>
       <c r="AB13">
-        <v>-9.658300844157721e-05</v>
+        <v>-0.00010466159803707801</v>
       </c>
       <c r="AC13">
-        <v>-0.00010420801169911981</v>
+        <v>-0.00011200549554738826</v>
       </c>
       <c r="AD13">
-        <v>-8.2261303497731427e-05</v>
+        <v>-8.7585297829528234e-05</v>
       </c>
       <c r="AE13">
-        <v>-9.2899386823946158e-05</v>
+        <v>-0.0001014477349346528</v>
       </c>
       <c r="AF13">
-        <v>-0.0001177618979195913</v>
+        <v>-0.0001261852041956013</v>
       </c>
       <c r="AG13">
-        <v>9.1740824583342456e-09</v>
+        <v>-6.4342264269657049e-07</v>
       </c>
       <c r="AH13">
-        <v>-0.0052036650527938558</v>
+        <v>-2.2164138048162176e-05</v>
+      </c>
+      <c r="AI13">
+        <v>5.4763436536255702e-05</v>
+      </c>
+      <c r="AJ13">
+        <v>-0.0051345458324562228</v>
       </c>
     </row>
     <row r="14">
@@ -1921,103 +2005,109 @@
         <v>29</v>
       </c>
       <c r="B14">
-        <v>-0.0023059382147071722</v>
+        <v>-0.0022670456225304925</v>
       </c>
       <c r="C14">
-        <v>9.1092695125573891e-08</v>
+        <v>9.0939883462974436e-08</v>
       </c>
       <c r="D14">
-        <v>-2.8773079103080056e-07</v>
+        <v>-2.8893583893147131e-07</v>
       </c>
       <c r="E14">
-        <v>2.6493330990526786e-09</v>
+        <v>2.6591359089132346e-09</v>
       </c>
       <c r="F14">
-        <v>-1.7589163526709101e-07</v>
+        <v>-1.9504447077157633e-07</v>
       </c>
       <c r="G14">
-        <v>1.0792745720968088e-07</v>
+        <v>1.002143807837706e-07</v>
       </c>
       <c r="H14">
-        <v>1.6384444896190105e-07</v>
+        <v>1.4424970242157938e-07</v>
       </c>
       <c r="I14">
-        <v>-3.469218407606828e-08</v>
+        <v>-3.5753092428886456e-08</v>
       </c>
       <c r="J14">
-        <v>1.5347041682199427e-08</v>
+        <v>1.3473076405657386e-08</v>
       </c>
       <c r="K14">
-        <v>-3.57267789138076e-08</v>
+        <v>-4.2195512494135536e-08</v>
       </c>
       <c r="L14">
-        <v>2.566161407327924e-08</v>
+        <v>2.5109967207929017e-08</v>
       </c>
       <c r="M14">
-        <v>6.4978665811687819e-09</v>
+        <v>5.6320424013921407e-09</v>
       </c>
       <c r="N14">
-        <v>1.6668655581624485e-06</v>
+        <v>1.5224934966399831e-06</v>
       </c>
       <c r="O14">
-        <v>2.4546192782446342e-07</v>
+        <v>2.4443940829377713e-07</v>
       </c>
       <c r="P14">
-        <v>-5.7890526752315372e-07</v>
+        <v>-6.029852900389148e-07</v>
       </c>
       <c r="Q14">
-        <v>-6.3853998947432813e-06</v>
+        <v>-6.4103127571306589e-06</v>
       </c>
       <c r="R14">
-        <v>0.00010490065336710432</v>
+        <v>0.00010444461320091992</v>
       </c>
       <c r="S14">
-        <v>0.00010503408991854612</v>
+        <v>0.00010458397880891684</v>
       </c>
       <c r="T14">
-        <v>0.00010508634650764373</v>
+        <v>0.00010462847082416017</v>
       </c>
       <c r="U14">
-        <v>-1.6742524788768197e-06</v>
+        <v>-1.745433348129832e-06</v>
       </c>
       <c r="V14">
-        <v>-7.4810372965237711e-08</v>
+        <v>-1.2286863435495218e-07</v>
       </c>
       <c r="W14">
-        <v>-5.5811439303195666e-07</v>
+        <v>-6.0376742978289683e-07</v>
       </c>
       <c r="X14">
-        <v>5.0252007600607009e-07</v>
+        <v>5.0711547101110088e-07</v>
       </c>
       <c r="Y14">
-        <v>-1.2118360618791086e-06</v>
+        <v>-1.2194903045869823e-06</v>
       </c>
       <c r="Z14">
-        <v>2.0638426417259916e-06</v>
+        <v>2.1349448885148807e-06</v>
       </c>
       <c r="AA14">
-        <v>-1.6257769286366858e-07</v>
+        <v>-1.5685781831742667e-07</v>
       </c>
       <c r="AB14">
-        <v>-1.2290727439932272e-07</v>
+        <v>-1.1896263647887223e-07</v>
       </c>
       <c r="AC14">
-        <v>6.3858596175337177e-08</v>
+        <v>6.7224863809878748e-08</v>
       </c>
       <c r="AD14">
-        <v>-2.7688962830133273e-07</v>
+        <v>-2.8464340596502083e-07</v>
       </c>
       <c r="AE14">
-        <v>-2.33255875422019e-07</v>
+        <v>-2.2703670235616047e-07</v>
       </c>
       <c r="AF14">
-        <v>-3.9428947924147748e-08</v>
+        <v>-3.4574382276464022e-08</v>
       </c>
       <c r="AG14">
-        <v>-1.8458298843144048e-08</v>
+        <v>-1.2076834283234572e-08</v>
       </c>
       <c r="AH14">
-        <v>-9.7153524140074275e-05</v>
+        <v>-5.7196816117010857e-07</v>
+      </c>
+      <c r="AI14">
+        <v>8.8186565686442837e-08</v>
+      </c>
+      <c r="AJ14">
+        <v>-9.666866067589903e-05</v>
       </c>
     </row>
     <row r="15">
@@ -2025,103 +2115,109 @@
         <v>30</v>
       </c>
       <c r="B15">
-        <v>-0.020713206399528034</v>
+        <v>-0.019658465172190144</v>
       </c>
       <c r="C15">
-        <v>-6.9630187884068893e-07</v>
+        <v>-5.5365494455151705e-07</v>
       </c>
       <c r="D15">
-        <v>2.8529170781301794e-07</v>
+        <v>3.1809939197751243e-07</v>
       </c>
       <c r="E15">
-        <v>-6.538111937488371e-10</v>
+        <v>-9.4327821682507526e-10</v>
       </c>
       <c r="F15">
-        <v>-6.0548709677588065e-06</v>
+        <v>-7.6681099742058539e-06</v>
       </c>
       <c r="G15">
-        <v>-8.5154949488814529e-06</v>
+        <v>-8.8487608585180564e-06</v>
       </c>
       <c r="H15">
-        <v>-6.5998867637764146e-06</v>
+        <v>-6.6178325936134106e-06</v>
       </c>
       <c r="I15">
-        <v>-4.6355220483620501e-06</v>
+        <v>-5.4800625058765496e-06</v>
       </c>
       <c r="J15">
-        <v>-5.5559429458063994e-05</v>
+        <v>-5.5738154889283928e-05</v>
       </c>
       <c r="K15">
-        <v>4.9742589554302227e-06</v>
+        <v>5.259438075629881e-06</v>
       </c>
       <c r="L15">
-        <v>-1.0836245148114824e-06</v>
+        <v>-1.0909205124439425e-06</v>
       </c>
       <c r="M15">
-        <v>2.4102036469438977e-05</v>
+        <v>2.4114701378240636e-05</v>
       </c>
       <c r="N15">
-        <v>-5.1067064288901992e-06</v>
+        <v>-1.2797378699486503e-05</v>
       </c>
       <c r="O15">
-        <v>-5.7890526752315372e-07</v>
+        <v>-6.029852900389148e-07</v>
       </c>
       <c r="P15">
-        <v>0.0013576246192694482</v>
+        <v>0.0013651451892964612</v>
       </c>
       <c r="Q15">
-        <v>-0.00062591091523798547</v>
+        <v>-0.00063419603228546614</v>
       </c>
       <c r="R15">
-        <v>0.00044355264053986529</v>
+        <v>0.00041740945321769004</v>
       </c>
       <c r="S15">
-        <v>0.00044998494852252355</v>
+        <v>0.00042421826620405351</v>
       </c>
       <c r="T15">
-        <v>0.00045294408924998749</v>
+        <v>0.00042676338634160485</v>
       </c>
       <c r="U15">
-        <v>8.0740708856456541e-05</v>
+        <v>8.2891654328890742e-05</v>
       </c>
       <c r="V15">
-        <v>3.9429321252727875e-05</v>
+        <v>4.1725278152355042e-05</v>
       </c>
       <c r="W15">
-        <v>4.6554062546254012e-05</v>
+        <v>4.8772942484471204e-05</v>
       </c>
       <c r="X15">
-        <v>1.341921103619929e-05</v>
+        <v>1.2907688390869378e-05</v>
       </c>
       <c r="Y15">
-        <v>-1.2680170136373374e-05</v>
+        <v>-1.2909084500184344e-05</v>
       </c>
       <c r="Z15">
-        <v>-1.838557902013717e-05</v>
+        <v>-2.0661299500110961e-05</v>
       </c>
       <c r="AA15">
-        <v>2.1887496361575705e-05</v>
+        <v>2.4480863746305988e-05</v>
       </c>
       <c r="AB15">
-        <v>1.3711097321521899e-05</v>
+        <v>1.6708748131363219e-05</v>
       </c>
       <c r="AC15">
-        <v>4.623236220552477e-06</v>
+        <v>6.6184178924230008e-06</v>
       </c>
       <c r="AD15">
-        <v>2.2916275614285242e-05</v>
+        <v>2.4974489775260748e-05</v>
       </c>
       <c r="AE15">
-        <v>2.9564094892454399e-06</v>
+        <v>5.4294317632951387e-06</v>
       </c>
       <c r="AF15">
-        <v>2.5283624473737147e-05</v>
+        <v>2.8341475067845799e-05</v>
       </c>
       <c r="AG15">
-        <v>-8.6018516675320246e-08</v>
+        <v>-4.0507905806822829e-07</v>
       </c>
       <c r="AH15">
-        <v>-0.0004777439030639913</v>
+        <v>1.1604885549131006e-05</v>
+      </c>
+      <c r="AI15">
+        <v>1.0604849255206464e-05</v>
+      </c>
+      <c r="AJ15">
+        <v>-0.00045274442340696415</v>
       </c>
     </row>
     <row r="16">
@@ -2129,103 +2225,109 @@
         <v>31</v>
       </c>
       <c r="B16">
-        <v>-0.045136340172975312</v>
+        <v>-0.044450175980520895</v>
       </c>
       <c r="C16">
-        <v>-4.4291088169017185e-06</v>
+        <v>-4.4643412823985004e-06</v>
       </c>
       <c r="D16">
-        <v>-2.88184855673491e-08</v>
+        <v>-9.2049423138635105e-08</v>
       </c>
       <c r="E16">
-        <v>2.275567861549283e-09</v>
+        <v>2.9432057953050599e-09</v>
       </c>
       <c r="F16">
-        <v>8.2143268312577867e-06</v>
+        <v>9.5385467637937026e-06</v>
       </c>
       <c r="G16">
-        <v>1.1073215599314283e-05</v>
+        <v>1.159891588002625e-05</v>
       </c>
       <c r="H16">
-        <v>5.9116496688289687e-06</v>
+        <v>6.7493930827819065e-06</v>
       </c>
       <c r="I16">
-        <v>6.1050641238750348e-06</v>
+        <v>6.5896982252864441e-06</v>
       </c>
       <c r="J16">
-        <v>2.1856245634203768e-05</v>
+        <v>2.2172052801245286e-05</v>
       </c>
       <c r="K16">
-        <v>1.6116678415521154e-06</v>
+        <v>1.5325239321903013e-06</v>
       </c>
       <c r="L16">
-        <v>-2.3286269359875828e-07</v>
+        <v>-1.6022301973270842e-07</v>
       </c>
       <c r="M16">
-        <v>-4.2024789614385775e-05</v>
+        <v>-4.2136373622518569e-05</v>
       </c>
       <c r="N16">
-        <v>5.2569499553637474e-05</v>
+        <v>5.5769530201830141e-05</v>
       </c>
       <c r="O16">
-        <v>-6.3853998947432813e-06</v>
+        <v>-6.4103127571306589e-06</v>
       </c>
       <c r="P16">
-        <v>-0.00062591091523798547</v>
+        <v>-0.00063419603228546614</v>
       </c>
       <c r="Q16">
-        <v>0.0013212484691502418</v>
+        <v>0.0013462025470260754</v>
       </c>
       <c r="R16">
-        <v>-0.0023489461903688112</v>
+        <v>-0.0023462957784217017</v>
       </c>
       <c r="S16">
-        <v>-0.0023441016477040604</v>
+        <v>-0.0023413908993463526</v>
       </c>
       <c r="T16">
-        <v>-0.0023444653779455156</v>
+        <v>-0.0023412320237869298</v>
       </c>
       <c r="U16">
-        <v>-3.5055375999286376e-05</v>
+        <v>-3.5028199515943579e-05</v>
       </c>
       <c r="V16">
-        <v>1.2149533639442458e-05</v>
+        <v>1.1943944616648727e-05</v>
       </c>
       <c r="W16">
-        <v>1.0669507886652699e-05</v>
+        <v>1.0307649675155668e-05</v>
       </c>
       <c r="X16">
-        <v>-1.116506599004884e-05</v>
+        <v>-1.0743271145026477e-05</v>
       </c>
       <c r="Y16">
-        <v>4.9068335579272553e-06</v>
+        <v>4.7458392919060303e-06</v>
       </c>
       <c r="Z16">
-        <v>3.5383472222992205e-05</v>
+        <v>3.4096513352007232e-05</v>
       </c>
       <c r="AA16">
-        <v>-4.6053523644693905e-06</v>
+        <v>-4.8760279663096189e-06</v>
       </c>
       <c r="AB16">
-        <v>-5.5999208484619478e-06</v>
+        <v>-6.1243900260174889e-06</v>
       </c>
       <c r="AC16">
-        <v>1.0134508858396089e-05</v>
+        <v>1.1151586887880134e-05</v>
       </c>
       <c r="AD16">
-        <v>1.2856077569123976e-05</v>
+        <v>1.3065401879147837e-05</v>
       </c>
       <c r="AE16">
-        <v>2.6691720750643758e-05</v>
+        <v>2.6647312627876472e-05</v>
       </c>
       <c r="AF16">
-        <v>2.7645467661454508e-06</v>
+        <v>3.0591265652514424e-06</v>
       </c>
       <c r="AG16">
-        <v>-5.5269597205395856e-07</v>
+        <v>-5.597041323916139e-07</v>
       </c>
       <c r="AH16">
-        <v>0.0023588968083124527</v>
+        <v>1.9939508548757427e-05</v>
+      </c>
+      <c r="AI16">
+        <v>-2.0131342377696995e-05</v>
+      </c>
+      <c r="AJ16">
+        <v>0.0023562528910354447</v>
       </c>
     </row>
     <row r="17">
@@ -2233,103 +2335,109 @@
         <v>32</v>
       </c>
       <c r="B17">
-        <v>-1.2460470403433786</v>
+        <v>-1.2319510901957458</v>
       </c>
       <c r="C17">
-        <v>-0.00020488441457322765</v>
+        <v>-0.00020276970545396434</v>
       </c>
       <c r="D17">
-        <v>-0.00013289368719563159</v>
+        <v>-0.00013339923347572137</v>
       </c>
       <c r="E17">
-        <v>1.1737753706095371e-06</v>
+        <v>1.178256127163396e-06</v>
       </c>
       <c r="F17">
-        <v>-8.4748861329416817e-05</v>
+        <v>-8.6934742314077697e-05</v>
       </c>
       <c r="G17">
-        <v>-1.2104100224375977e-05</v>
+        <v>-9.9597856857855599e-06</v>
       </c>
       <c r="H17">
-        <v>5.4293659110573666e-05</v>
+        <v>5.1677075663596421e-05</v>
       </c>
       <c r="I17">
-        <v>-1.370963977263276e-05</v>
+        <v>-9.9348736545875816e-06</v>
       </c>
       <c r="J17">
-        <v>-1.4587525947807571e-05</v>
+        <v>-1.4521490597421205e-05</v>
       </c>
       <c r="K17">
-        <v>7.5268081404743865e-05</v>
+        <v>7.2942141221193967e-05</v>
       </c>
       <c r="L17">
-        <v>9.1571775018034444e-06</v>
+        <v>8.7873443139225703e-06</v>
       </c>
       <c r="M17">
-        <v>2.5659523892040982e-07</v>
+        <v>-2.2297393878621718e-07</v>
       </c>
       <c r="N17">
-        <v>0.0050754832797341408</v>
+        <v>0.0050136053871246969</v>
       </c>
       <c r="O17">
-        <v>0.00010490065336710432</v>
+        <v>0.00010444461320091992</v>
       </c>
       <c r="P17">
-        <v>0.00044355264053986529</v>
+        <v>0.00041740945321769004</v>
       </c>
       <c r="Q17">
-        <v>-0.0023489461903688112</v>
+        <v>-0.0023462957784217017</v>
       </c>
       <c r="R17">
-        <v>0.052272855574013025</v>
+        <v>0.052056543072756048</v>
       </c>
       <c r="S17">
-        <v>0.051978416640240541</v>
+        <v>0.051764222192104956</v>
       </c>
       <c r="T17">
-        <v>0.052023386175482661</v>
+        <v>0.051806231087411628</v>
       </c>
       <c r="U17">
-        <v>0.001985589458940229</v>
+        <v>0.0019554998409978403</v>
       </c>
       <c r="V17">
-        <v>0.00054863123020110205</v>
+        <v>0.00053031381109416853</v>
       </c>
       <c r="W17">
-        <v>0.00045183360194928079</v>
+        <v>0.00043258298256027006</v>
       </c>
       <c r="X17">
-        <v>0.00015405077340892217</v>
+        <v>0.00015721725389215889</v>
       </c>
       <c r="Y17">
-        <v>-0.0005141009245745046</v>
+        <v>-0.00051755826393656227</v>
       </c>
       <c r="Z17">
-        <v>0.00086808413924651176</v>
+        <v>0.00089127060186100504</v>
       </c>
       <c r="AA17">
-        <v>-0.00015970902141392712</v>
+        <v>-0.00014345429489732997</v>
       </c>
       <c r="AB17">
-        <v>-9.796613118667058e-05</v>
+        <v>-8.3691032520712139e-05</v>
       </c>
       <c r="AC17">
-        <v>6.68068666565165e-06</v>
+        <v>1.9830693334169786e-05</v>
       </c>
       <c r="AD17">
-        <v>-0.00022133172117906608</v>
+        <v>-0.00021070400319908589</v>
       </c>
       <c r="AE17">
-        <v>-0.00018486922394329863</v>
+        <v>-0.0001713867178525768</v>
       </c>
       <c r="AF17">
-        <v>-0.00011959226924120221</v>
+        <v>-0.00010334947615037171</v>
       </c>
       <c r="AG17">
-        <v>-6.1724273337825444e-06</v>
+        <v>-4.650223596836282e-06</v>
       </c>
       <c r="AH17">
-        <v>-0.048849629572997613</v>
+        <v>-0.0001895486371505592</v>
+      </c>
+      <c r="AI17">
+        <v>6.374556169201108e-05</v>
+      </c>
+      <c r="AJ17">
+        <v>-0.048628395941666985</v>
       </c>
     </row>
     <row r="18">
@@ -2337,103 +2445,109 @@
         <v>33</v>
       </c>
       <c r="B18">
-        <v>-1.1117121403700687</v>
+        <v>-1.0964251342103926</v>
       </c>
       <c r="C18">
-        <v>-0.00018583290833420433</v>
+        <v>-0.00018457906641151828</v>
       </c>
       <c r="D18">
-        <v>-0.00013909063257459549</v>
+        <v>-0.00013984982154221666</v>
       </c>
       <c r="E18">
-        <v>1.2684298192710072e-06</v>
+        <v>1.2750902600667099e-06</v>
       </c>
       <c r="F18">
-        <v>-8.4694143457047713e-05</v>
+        <v>-9.0659463184927195e-05</v>
       </c>
       <c r="G18">
-        <v>5.7740975907146489e-05</v>
+        <v>5.8883803869194855e-05</v>
       </c>
       <c r="H18">
-        <v>7.7710050512130055e-05</v>
+        <v>7.3886624544214119e-05</v>
       </c>
       <c r="I18">
-        <v>-1.2827912515240126e-05</v>
+        <v>-1.0058234629685758e-05</v>
       </c>
       <c r="J18">
-        <v>-1.5959082681540526e-05</v>
+        <v>-1.6105590771735326e-05</v>
       </c>
       <c r="K18">
-        <v>4.1560520250256858e-05</v>
+        <v>3.8903304867473406e-05</v>
       </c>
       <c r="L18">
-        <v>6.2764350888560335e-06</v>
+        <v>6.0585243863096099e-06</v>
       </c>
       <c r="M18">
-        <v>-5.8629824426148105e-06</v>
+        <v>-6.248287619315995e-06</v>
       </c>
       <c r="N18">
-        <v>0.0050501878930057</v>
+        <v>0.0049888765242035709</v>
       </c>
       <c r="O18">
-        <v>0.00010503408991854612</v>
+        <v>0.00010458397880891684</v>
       </c>
       <c r="P18">
-        <v>0.00044998494852252355</v>
+        <v>0.00042421826620405351</v>
       </c>
       <c r="Q18">
-        <v>-0.0023441016477040604</v>
+        <v>-0.0023413908993463526</v>
       </c>
       <c r="R18">
-        <v>0.051978416640240541</v>
+        <v>0.051764222192104956</v>
       </c>
       <c r="S18">
-        <v>0.052476921716346416</v>
+        <v>0.052266544011733578</v>
       </c>
       <c r="T18">
-        <v>0.052057240909184933</v>
+        <v>0.051843442062760696</v>
       </c>
       <c r="U18">
-        <v>0.0017096827572988318</v>
+        <v>0.0016759839972338569</v>
       </c>
       <c r="V18">
-        <v>0.00036524188115484579</v>
+        <v>0.00034556698589546103</v>
       </c>
       <c r="W18">
-        <v>0.00020940101278717205</v>
+        <v>0.00018994649714085265</v>
       </c>
       <c r="X18">
-        <v>0.00015085358617323392</v>
+        <v>0.00015391109031342217</v>
       </c>
       <c r="Y18">
-        <v>-0.00054109157998855984</v>
+        <v>-0.00054598826562006096</v>
       </c>
       <c r="Z18">
-        <v>0.001011832552426175</v>
+        <v>0.0010319563433645457</v>
       </c>
       <c r="AA18">
-        <v>-7.2127173569351555e-05</v>
+        <v>-5.4917603809427618e-05</v>
       </c>
       <c r="AB18">
-        <v>-4.3666801738166672e-05</v>
+        <v>-2.8529795788011236e-05</v>
       </c>
       <c r="AC18">
-        <v>7.0300032987269737e-05</v>
+        <v>8.3710665276034643e-05</v>
       </c>
       <c r="AD18">
-        <v>-0.0001012817213137257</v>
+        <v>-8.9978529541907826e-05</v>
       </c>
       <c r="AE18">
-        <v>-9.1629844759622686e-05</v>
+        <v>-7.7348360760081183e-05</v>
       </c>
       <c r="AF18">
-        <v>3.3619327642619989e-07</v>
+        <v>1.6882261361857685e-05</v>
       </c>
       <c r="AG18">
-        <v>-1.2741045310613259e-05</v>
+        <v>-1.1098044695567527e-05</v>
       </c>
       <c r="AH18">
-        <v>-0.048495498961884945</v>
+        <v>-0.00018796882303842577</v>
+      </c>
+      <c r="AI18">
+        <v>5.0209324960333659e-05</v>
+      </c>
+      <c r="AJ18">
+        <v>-0.048269432432185289</v>
       </c>
     </row>
     <row r="19">
@@ -2441,103 +2555,109 @@
         <v>34</v>
       </c>
       <c r="B19">
-        <v>-0.90411724415591754</v>
+        <v>-0.88586791670074161</v>
       </c>
       <c r="C19">
-        <v>-0.0001437379964723695</v>
+        <v>-0.00014230107507940196</v>
       </c>
       <c r="D19">
-        <v>-0.00013915259142187336</v>
+        <v>-0.00013983667603342863</v>
       </c>
       <c r="E19">
-        <v>1.2844227315813218e-06</v>
+        <v>1.2905328601471298e-06</v>
       </c>
       <c r="F19">
-        <v>-3.2755991009762988e-05</v>
+        <v>-3.7183345565693071e-05</v>
       </c>
       <c r="G19">
-        <v>8.5622407482293853e-05</v>
+        <v>8.8132520044139427e-05</v>
       </c>
       <c r="H19">
-        <v>0.00012302769918354166</v>
+        <v>0.00012020170536684142</v>
       </c>
       <c r="I19">
-        <v>1.6990177490073276e-05</v>
+        <v>2.1311724134353537e-05</v>
       </c>
       <c r="J19">
-        <v>-1.8387298203976624e-05</v>
+        <v>-1.8653698068622268e-05</v>
       </c>
       <c r="K19">
-        <v>-4.0093540460861771e-05</v>
+        <v>-4.2076096725377865e-05</v>
       </c>
       <c r="L19">
-        <v>2.1260633326848366e-06</v>
+        <v>1.8206085427353066e-06</v>
       </c>
       <c r="M19">
-        <v>-9.9853199002744104e-06</v>
+        <v>-1.0596812772207388e-05</v>
       </c>
       <c r="N19">
-        <v>0.0050232044529128564</v>
+        <v>0.0049611952792562239</v>
       </c>
       <c r="O19">
-        <v>0.00010508634650764373</v>
+        <v>0.00010462847082416017</v>
       </c>
       <c r="P19">
-        <v>0.00045294408924998749</v>
+        <v>0.00042676338634160485</v>
       </c>
       <c r="Q19">
-        <v>-0.0023444653779455156</v>
+        <v>-0.0023412320237869298</v>
       </c>
       <c r="R19">
-        <v>0.052023386175482661</v>
+        <v>0.051806231087411628</v>
       </c>
       <c r="S19">
-        <v>0.052057240909184933</v>
+        <v>0.051843442062760696</v>
       </c>
       <c r="T19">
-        <v>0.052508664302923336</v>
+        <v>0.052291670640890867</v>
       </c>
       <c r="U19">
-        <v>0.0011742653725614338</v>
+        <v>0.0011469699117394455</v>
       </c>
       <c r="V19">
-        <v>-0.0002292551065141632</v>
+        <v>-0.0002442016231819083</v>
       </c>
       <c r="W19">
-        <v>-0.00046594911132715605</v>
+        <v>-0.00048080279203675108</v>
       </c>
       <c r="X19">
-        <v>0.00013384724745219749</v>
+        <v>0.00013641980171128767</v>
       </c>
       <c r="Y19">
-        <v>-0.00055225352246418558</v>
+        <v>-0.0005569960839069397</v>
       </c>
       <c r="Z19">
-        <v>0.0010131884884441063</v>
+        <v>0.0010400001708056883</v>
       </c>
       <c r="AA19">
-        <v>-0.00012171966859791244</v>
+        <v>-0.00010644408694181207</v>
       </c>
       <c r="AB19">
-        <v>-8.6236695376440409e-05</v>
+        <v>-7.2881788181329565e-05</v>
       </c>
       <c r="AC19">
-        <v>1.6656544121773989e-05</v>
+        <v>2.9071147594358915e-05</v>
       </c>
       <c r="AD19">
-        <v>-0.00014398854076355661</v>
+        <v>-0.00013469766881531176</v>
       </c>
       <c r="AE19">
-        <v>-0.00013276447865572493</v>
+        <v>-0.00011938335773575316</v>
       </c>
       <c r="AF19">
-        <v>-5.0895615875704188e-05</v>
+        <v>-3.5312369631867666e-05</v>
       </c>
       <c r="AG19">
-        <v>-1.6854466762370466e-05</v>
+        <v>-1.5124170488833594e-05</v>
       </c>
       <c r="AH19">
-        <v>-0.047875562641307878</v>
+        <v>-0.0002140049657082671</v>
+      </c>
+      <c r="AI19">
+        <v>6.5692277114502359e-05</v>
+      </c>
+      <c r="AJ19">
+        <v>-0.047652712381011209</v>
       </c>
     </row>
     <row r="20">
@@ -2545,103 +2665,109 @@
         <v>35</v>
       </c>
       <c r="B20">
-        <v>1.5066066189594254</v>
+        <v>1.4880521478051685</v>
       </c>
       <c r="C20">
-        <v>-0.00043025157219142519</v>
+        <v>-0.00042824173032764926</v>
       </c>
       <c r="D20">
-        <v>9.2835608810035983e-05</v>
+        <v>9.4556681224327444e-05</v>
       </c>
       <c r="E20">
-        <v>-9.0644583065478604e-07</v>
+        <v>-9.2138299886223013e-07</v>
       </c>
       <c r="F20">
-        <v>5.4172295235524297e-05</v>
+        <v>7.3814813121306189e-05</v>
       </c>
       <c r="G20">
-        <v>8.3036332029209447e-05</v>
+        <v>8.5320300293013223e-05</v>
       </c>
       <c r="H20">
-        <v>0.00014629105508320726</v>
+        <v>0.00014718677037586051</v>
       </c>
       <c r="I20">
-        <v>1.0929610966390181e-05</v>
+        <v>1.1399888685241705e-05</v>
       </c>
       <c r="J20">
-        <v>-5.0935754477921896e-05</v>
+        <v>-5.3257989886495712e-05</v>
       </c>
       <c r="K20">
-        <v>0.0029916827384938714</v>
+        <v>0.002999366440053402</v>
       </c>
       <c r="L20">
-        <v>-7.5643521075182982e-05</v>
+        <v>-7.7503693165586649e-05</v>
       </c>
       <c r="M20">
-        <v>1.3244037329865431e-05</v>
+        <v>1.436465799518815e-05</v>
       </c>
       <c r="N20">
-        <v>0.00047562031389892546</v>
+        <v>0.00047718190255935291</v>
       </c>
       <c r="O20">
-        <v>-1.6742524788768197e-06</v>
+        <v>-1.745433348129832e-06</v>
       </c>
       <c r="P20">
-        <v>8.0740708856456541e-05</v>
+        <v>8.2891654328890742e-05</v>
       </c>
       <c r="Q20">
-        <v>-3.5055375999286376e-05</v>
+        <v>-3.5028199515943579e-05</v>
       </c>
       <c r="R20">
-        <v>0.001985589458940229</v>
+        <v>0.0019554998409978403</v>
       </c>
       <c r="S20">
-        <v>0.0017096827572988318</v>
+        <v>0.0016759839972338569</v>
       </c>
       <c r="T20">
-        <v>0.0011742653725614338</v>
+        <v>0.0011469699117394455</v>
       </c>
       <c r="U20">
-        <v>0.026360777242583861</v>
+        <v>0.026428338584982339</v>
       </c>
       <c r="V20">
-        <v>0.023467389480207147</v>
+        <v>0.023523019326517337</v>
       </c>
       <c r="W20">
-        <v>0.023790114967233808</v>
+        <v>0.023838768049555287</v>
       </c>
       <c r="X20">
-        <v>1.5854803337415945e-05</v>
+        <v>1.3214857350892211e-05</v>
       </c>
       <c r="Y20">
-        <v>0.00018059676259831532</v>
+        <v>0.00018415005674882927</v>
       </c>
       <c r="Z20">
-        <v>-0.00011025696117060967</v>
+        <v>-0.00010553482450312464</v>
       </c>
       <c r="AA20">
-        <v>-5.1728826957697649e-05</v>
+        <v>-3.3787078824263489e-05</v>
       </c>
       <c r="AB20">
-        <v>-0.00030443045987598588</v>
+        <v>-0.00028615808145876498</v>
       </c>
       <c r="AC20">
-        <v>-0.00044775772178987441</v>
+        <v>-0.00042684280750269425</v>
       </c>
       <c r="AD20">
-        <v>1.2339985309965662e-05</v>
+        <v>3.0242113666888171e-05</v>
       </c>
       <c r="AE20">
-        <v>-0.00020949657855305528</v>
+        <v>-0.00018854380716434079</v>
       </c>
       <c r="AF20">
-        <v>-0.00021687740502025462</v>
+        <v>-0.00020352959101305667</v>
       </c>
       <c r="AG20">
-        <v>-1.4329823761891102e-05</v>
+        <v>-1.2037901713926298e-05</v>
       </c>
       <c r="AH20">
-        <v>-0.026834991417646989</v>
+        <v>-0.0001512338373518933</v>
+      </c>
+      <c r="AI20">
+        <v>-3.2714931552187479e-05</v>
+      </c>
+      <c r="AJ20">
+        <v>-0.026942780966095696</v>
       </c>
     </row>
     <row r="21">
@@ -2649,103 +2775,109 @@
         <v>36</v>
       </c>
       <c r="B21">
-        <v>0.84366115382410967</v>
+        <v>0.82493796010081688</v>
       </c>
       <c r="C21">
-        <v>-0.00038948152581626505</v>
+        <v>-0.00038901432655613779</v>
       </c>
       <c r="D21">
-        <v>-1.8199907419089623e-05</v>
+        <v>-1.7461056325237417e-05</v>
       </c>
       <c r="E21">
-        <v>-2.5301988561612497e-08</v>
+        <v>-3.196357144212363e-08</v>
       </c>
       <c r="F21">
-        <v>-8.1881973549052258e-05</v>
+        <v>-6.1034824572332952e-05</v>
       </c>
       <c r="G21">
-        <v>1.6375039565686615e-05</v>
+        <v>1.7200407890189924e-05</v>
       </c>
       <c r="H21">
-        <v>0.00011471605355682865</v>
+        <v>0.00011459949982876333</v>
       </c>
       <c r="I21">
-        <v>1.3374220194669543e-05</v>
+        <v>1.307100996085454e-05</v>
       </c>
       <c r="J21">
-        <v>-4.9516874433796827e-05</v>
+        <v>-5.1986896564435784e-05</v>
       </c>
       <c r="K21">
-        <v>0.003045095528134539</v>
+        <v>0.003052238522011635</v>
       </c>
       <c r="L21">
-        <v>-7.7127714590427421e-05</v>
+        <v>-7.8663409873098978e-05</v>
       </c>
       <c r="M21">
-        <v>-1.3895136511261135e-06</v>
+        <v>-9.063151714073773e-07</v>
       </c>
       <c r="N21">
-        <v>0.00038695768746498235</v>
+        <v>0.0003922445210037314</v>
       </c>
       <c r="O21">
-        <v>-7.4810372965237711e-08</v>
+        <v>-1.2286863435495218e-07</v>
       </c>
       <c r="P21">
-        <v>3.9429321252727875e-05</v>
+        <v>4.1725278152355042e-05</v>
       </c>
       <c r="Q21">
-        <v>1.2149533639442458e-05</v>
+        <v>1.1943944616648727e-05</v>
       </c>
       <c r="R21">
-        <v>0.00054863123020110205</v>
+        <v>0.00053031381109416853</v>
       </c>
       <c r="S21">
-        <v>0.00036524188115484579</v>
+        <v>0.00034556698589546103</v>
       </c>
       <c r="T21">
-        <v>-0.0002292551065141632</v>
+        <v>-0.0002442016231819083</v>
       </c>
       <c r="U21">
-        <v>0.023467389480207147</v>
+        <v>0.023523019326517337</v>
       </c>
       <c r="V21">
-        <v>0.024321556860214814</v>
+        <v>0.024375367836511022</v>
       </c>
       <c r="W21">
-        <v>0.024393488754375074</v>
+        <v>0.024440359640698399</v>
       </c>
       <c r="X21">
-        <v>-5.555277000671632e-05</v>
+        <v>-5.9221490715636346e-05</v>
       </c>
       <c r="Y21">
-        <v>0.00011173847754391533</v>
+        <v>0.00011512955434016779</v>
       </c>
       <c r="Z21">
-        <v>-0.0002512294983747854</v>
+        <v>-0.00023861001404968957</v>
       </c>
       <c r="AA21">
-        <v>-3.404242622366202e-05</v>
+        <v>-2.7087647779604554e-05</v>
       </c>
       <c r="AB21">
-        <v>-0.00031135122940891512</v>
+        <v>-0.00030288158819016808</v>
       </c>
       <c r="AC21">
-        <v>-0.00044875602882456667</v>
+        <v>-0.0004365576943273974</v>
       </c>
       <c r="AD21">
-        <v>2.7765915279077264e-06</v>
+        <v>1.0262788959360114e-05</v>
       </c>
       <c r="AE21">
-        <v>-0.00019752927270313796</v>
+        <v>-0.00018557136633158295</v>
       </c>
       <c r="AF21">
-        <v>-0.0002152364161605992</v>
+        <v>-0.00021021413701004374</v>
       </c>
       <c r="AG21">
-        <v>-1.3631811037048344e-06</v>
+        <v>3.298568482878279e-07</v>
       </c>
       <c r="AH21">
-        <v>-0.022908844474863507</v>
+        <v>-0.0001359753622682848</v>
+      </c>
+      <c r="AI21">
+        <v>1.7109776470275624e-05</v>
+      </c>
+      <c r="AJ21">
+        <v>-0.022981610082609877</v>
       </c>
     </row>
     <row r="22">
@@ -2753,103 +2885,109 @@
         <v>37</v>
       </c>
       <c r="B22">
-        <v>0.91182492845814567</v>
+        <v>0.89043197007938524</v>
       </c>
       <c r="C22">
-        <v>-0.00054368934856143479</v>
+        <v>-0.00054219627613523783</v>
       </c>
       <c r="D22">
-        <v>3.4184986662915199e-05</v>
+        <v>3.4993562997956667e-05</v>
       </c>
       <c r="E22">
-        <v>-7.94541009372632e-07</v>
+        <v>-8.0194097487419187e-07</v>
       </c>
       <c r="F22">
-        <v>-8.626780096255036e-05</v>
+        <v>-7.2887149255579191e-05</v>
       </c>
       <c r="G22">
-        <v>7.0723872223454209e-05</v>
+        <v>7.3103565255648747e-05</v>
       </c>
       <c r="H22">
-        <v>0.00014042705096554026</v>
+        <v>0.00014111864591351823</v>
       </c>
       <c r="I22">
-        <v>2.1542359730252847e-05</v>
+        <v>2.0899714964468818e-05</v>
       </c>
       <c r="J22">
-        <v>-5.6314680192282662e-05</v>
+        <v>-5.8470650969077207e-05</v>
       </c>
       <c r="K22">
-        <v>0.0030868104116333612</v>
+        <v>0.0030930118556961434</v>
       </c>
       <c r="L22">
-        <v>-6.4099077036030045e-05</v>
+        <v>-6.546711117600631e-05</v>
       </c>
       <c r="M22">
-        <v>1.2131480104485105e-06</v>
+        <v>1.7803446417798033e-06</v>
       </c>
       <c r="N22">
-        <v>0.00054069489522240097</v>
+        <v>0.00054544506682772985</v>
       </c>
       <c r="O22">
-        <v>-5.5811439303195666e-07</v>
+        <v>-6.0376742978289683e-07</v>
       </c>
       <c r="P22">
-        <v>4.6554062546254012e-05</v>
+        <v>4.8772942484471204e-05</v>
       </c>
       <c r="Q22">
-        <v>1.0669507886652699e-05</v>
+        <v>1.0307649675155668e-05</v>
       </c>
       <c r="R22">
-        <v>0.00045183360194928079</v>
+        <v>0.00043258298256027006</v>
       </c>
       <c r="S22">
-        <v>0.00020940101278717205</v>
+        <v>0.00018994649714085265</v>
       </c>
       <c r="T22">
-        <v>-0.00046594911132715605</v>
+        <v>-0.00048080279203675108</v>
       </c>
       <c r="U22">
-        <v>0.023790114967233808</v>
+        <v>0.023838768049555287</v>
       </c>
       <c r="V22">
-        <v>0.024393488754375074</v>
+        <v>0.024440359640698399</v>
       </c>
       <c r="W22">
-        <v>0.026307490526385265</v>
+        <v>0.026347387477073592</v>
       </c>
       <c r="X22">
-        <v>-9.3825783574827491e-05</v>
+        <v>-9.6692698841411608e-05</v>
       </c>
       <c r="Y22">
-        <v>9.6961116737285429e-05</v>
+        <v>0.00010094760406168727</v>
       </c>
       <c r="Z22">
-        <v>-0.00029189933431725788</v>
+        <v>-0.00027720321106184959</v>
       </c>
       <c r="AA22">
-        <v>-4.5536644832460532e-05</v>
+        <v>-3.492590841396373e-05</v>
       </c>
       <c r="AB22">
-        <v>-0.00033727564414217162</v>
+        <v>-0.00032499519214412506</v>
       </c>
       <c r="AC22">
-        <v>-0.00043109935112108739</v>
+        <v>-0.00041555000174634937</v>
       </c>
       <c r="AD22">
-        <v>2.9091084384758048e-05</v>
+        <v>4.0257242717714123e-05</v>
       </c>
       <c r="AE22">
-        <v>-0.0002142572191855454</v>
+        <v>-0.00019909139433911278</v>
       </c>
       <c r="AF22">
-        <v>-0.00016989106295890819</v>
+        <v>-0.00015975550368417177</v>
       </c>
       <c r="AG22">
-        <v>-1.2259196194089328e-06</v>
+        <v>3.6350820467926336e-07</v>
       </c>
       <c r="AH22">
-        <v>-0.02377072641085777</v>
+        <v>-0.00011810315069277558</v>
+      </c>
+      <c r="AI22">
+        <v>4.4973636718738733e-06</v>
+      </c>
+      <c r="AJ22">
+        <v>-0.023842405045704632</v>
       </c>
     </row>
     <row r="23">
@@ -2857,103 +2995,109 @@
         <v>38</v>
       </c>
       <c r="B23">
-        <v>-0.16443818382971401</v>
+        <v>-0.16562418677036875</v>
       </c>
       <c r="C23">
-        <v>3.2875115851226283e-05</v>
+        <v>3.2606815590782098e-05</v>
       </c>
       <c r="D23">
-        <v>7.0596743197700326e-06</v>
+        <v>7.0259324899972927e-06</v>
       </c>
       <c r="E23">
-        <v>1.9096019429329625e-09</v>
+        <v>2.4718955330417382e-09</v>
       </c>
       <c r="F23">
-        <v>4.0877533799368282e-05</v>
+        <v>4.4439057352386403e-05</v>
       </c>
       <c r="G23">
-        <v>3.497730833551634e-05</v>
+        <v>3.3090857626206661e-05</v>
       </c>
       <c r="H23">
-        <v>2.7588099927021692e-05</v>
+        <v>2.723835413366407e-05</v>
       </c>
       <c r="I23">
-        <v>1.2382438929014677e-05</v>
+        <v>1.1635607613298661e-05</v>
       </c>
       <c r="J23">
-        <v>1.598184924259426e-06</v>
+        <v>1.9745750342813263e-06</v>
       </c>
       <c r="K23">
-        <v>-1.3878111332322801e-05</v>
+        <v>-1.42044052615582e-05</v>
       </c>
       <c r="L23">
-        <v>-3.8179162124950021e-06</v>
+        <v>-3.9028183123111055e-06</v>
       </c>
       <c r="M23">
-        <v>4.8353945859318536e-06</v>
+        <v>4.4989500669006581e-06</v>
       </c>
       <c r="N23">
-        <v>-4.6782119701288202e-05</v>
+        <v>-4.7132921023004847e-05</v>
       </c>
       <c r="O23">
-        <v>5.0252007600607009e-07</v>
+        <v>5.0711547101110088e-07</v>
       </c>
       <c r="P23">
-        <v>1.341921103619929e-05</v>
+        <v>1.2907688390869378e-05</v>
       </c>
       <c r="Q23">
-        <v>-1.116506599004884e-05</v>
+        <v>-1.0743271145026477e-05</v>
       </c>
       <c r="R23">
-        <v>0.00015405077340892217</v>
+        <v>0.00015721725389215889</v>
       </c>
       <c r="S23">
-        <v>0.00015085358617323392</v>
+        <v>0.00015391109031342217</v>
       </c>
       <c r="T23">
-        <v>0.00013384724745219749</v>
+        <v>0.00013641980171128767</v>
       </c>
       <c r="U23">
-        <v>1.5854803337415945e-05</v>
+        <v>1.3214857350892211e-05</v>
       </c>
       <c r="V23">
-        <v>-5.555277000671632e-05</v>
+        <v>-5.9221490715636346e-05</v>
       </c>
       <c r="W23">
-        <v>-9.3825783574827491e-05</v>
+        <v>-9.6692698841411608e-05</v>
       </c>
       <c r="X23">
-        <v>0.00073698992053537304</v>
+        <v>0.00073781342126298644</v>
       </c>
       <c r="Y23">
-        <v>0.00031819015943353488</v>
+        <v>0.00031916678969476977</v>
       </c>
       <c r="Z23">
-        <v>0.00039641171952480795</v>
+        <v>0.00039799076756211443</v>
       </c>
       <c r="AA23">
-        <v>-6.8691764685141227e-05</v>
+        <v>-6.6280645229651496e-05</v>
       </c>
       <c r="AB23">
-        <v>-9.1119440751068204e-05</v>
+        <v>-8.8778427547365536e-05</v>
       </c>
       <c r="AC23">
-        <v>-0.00010638648922825083</v>
+        <v>-0.0001025623456676171</v>
       </c>
       <c r="AD23">
-        <v>-8.4685032830998479e-05</v>
+        <v>-8.1845277992750713e-05</v>
       </c>
       <c r="AE23">
-        <v>-8.1631800335603351e-05</v>
+        <v>-7.9303566415632899e-05</v>
       </c>
       <c r="AF23">
-        <v>-9.5426843787421178e-05</v>
+        <v>-9.2811942185132366e-05</v>
       </c>
       <c r="AG23">
-        <v>3.0921685381445773e-06</v>
+        <v>2.8892275891271729e-06</v>
       </c>
       <c r="AH23">
-        <v>-0.00074744863532919524</v>
+        <v>2.3279697372624348e-05</v>
+      </c>
+      <c r="AI23">
+        <v>-4.8265097263521076e-06</v>
+      </c>
+      <c r="AJ23">
+        <v>-0.00074773814662214711</v>
       </c>
     </row>
     <row r="24">
@@ -2961,103 +3105,109 @@
         <v>39</v>
       </c>
       <c r="B24">
-        <v>-0.32946729787556228</v>
+        <v>-0.33038245343777334</v>
       </c>
       <c r="C24">
-        <v>1.2960937229377916e-05</v>
+        <v>1.2507353626023731e-05</v>
       </c>
       <c r="D24">
-        <v>3.3498853011830892e-05</v>
+        <v>3.3636494439989339e-05</v>
       </c>
       <c r="E24">
-        <v>-2.6422740261230321e-07</v>
+        <v>-2.6520618624859582e-07</v>
       </c>
       <c r="F24">
-        <v>5.0404522487951546e-05</v>
+        <v>5.7182990474016758e-05</v>
       </c>
       <c r="G24">
-        <v>-1.8459387842582608e-06</v>
+        <v>-3.0687237558719e-06</v>
       </c>
       <c r="H24">
-        <v>-9.6900770293089894e-06</v>
+        <v>-9.4038118989487331e-06</v>
       </c>
       <c r="I24">
-        <v>7.2643634315007145e-06</v>
+        <v>7.0885674723720956e-06</v>
       </c>
       <c r="J24">
-        <v>-5.5936669005860406e-07</v>
+        <v>-9.8666629231824524e-08</v>
       </c>
       <c r="K24">
-        <v>1.4850935956310212e-05</v>
+        <v>1.5362234224736333e-05</v>
       </c>
       <c r="L24">
-        <v>8.747500839220292e-08</v>
+        <v>1.4581552651866553e-07</v>
       </c>
       <c r="M24">
-        <v>-1.6592569004102378e-06</v>
+        <v>-1.9094483336881404e-06</v>
       </c>
       <c r="N24">
-        <v>7.8108018194332453e-07</v>
+        <v>1.7089749209726239e-06</v>
       </c>
       <c r="O24">
-        <v>-1.2118360618791086e-06</v>
+        <v>-1.2194903045869823e-06</v>
       </c>
       <c r="P24">
-        <v>-1.2680170136373374e-05</v>
+        <v>-1.2909084500184344e-05</v>
       </c>
       <c r="Q24">
-        <v>4.9068335579272553e-06</v>
+        <v>4.7458392919060303e-06</v>
       </c>
       <c r="R24">
-        <v>-0.0005141009245745046</v>
+        <v>-0.00051755826393656227</v>
       </c>
       <c r="S24">
-        <v>-0.00054109157998855984</v>
+        <v>-0.00054598826562006096</v>
       </c>
       <c r="T24">
-        <v>-0.00055225352246418558</v>
+        <v>-0.0005569960839069397</v>
       </c>
       <c r="U24">
-        <v>0.00018059676259831532</v>
+        <v>0.00018415005674882927</v>
       </c>
       <c r="V24">
-        <v>0.00011173847754391533</v>
+        <v>0.00011512955434016779</v>
       </c>
       <c r="W24">
-        <v>9.6961116737285429e-05</v>
+        <v>0.00010094760406168727</v>
       </c>
       <c r="X24">
-        <v>0.00031819015943353488</v>
+        <v>0.00031916678969476977</v>
       </c>
       <c r="Y24">
-        <v>0.00068367781747988375</v>
+        <v>0.00068688782566452694</v>
       </c>
       <c r="Z24">
-        <v>0.00034773189747253736</v>
+        <v>0.00034754770859169825</v>
       </c>
       <c r="AA24">
-        <v>-4.6965734606338699e-05</v>
+        <v>-4.7904968243904088e-05</v>
       </c>
       <c r="AB24">
-        <v>-2.923279558224919e-05</v>
+        <v>-2.9352671216799006e-05</v>
       </c>
       <c r="AC24">
-        <v>-6.6007459642419537e-05</v>
+        <v>-6.6569343664000434e-05</v>
       </c>
       <c r="AD24">
-        <v>-3.5135767100815426e-05</v>
+        <v>-3.4827249257180079e-05</v>
       </c>
       <c r="AE24">
-        <v>-2.9396846011165123e-05</v>
+        <v>-2.9747572854813415e-05</v>
       </c>
       <c r="AF24">
-        <v>-4.1457980832742397e-05</v>
+        <v>-4.2999107983410516e-05</v>
       </c>
       <c r="AG24">
-        <v>1.3405765647571658e-06</v>
+        <v>7.0353498413279949e-07</v>
       </c>
       <c r="AH24">
-        <v>-0.00082986178935164729</v>
+        <v>4.3654792742303509e-05</v>
+      </c>
+      <c r="AI24">
+        <v>8.7640245386980315e-06</v>
+      </c>
+      <c r="AJ24">
+        <v>-0.00082784343779009561</v>
       </c>
     </row>
     <row r="25">
@@ -3065,103 +3215,109 @@
         <v>40</v>
       </c>
       <c r="B25">
-        <v>-0.24660487780964813</v>
+        <v>-0.25057095185008144</v>
       </c>
       <c r="C25">
-        <v>0.00010968366927055643</v>
+        <v>0.00010919930756859229</v>
       </c>
       <c r="D25">
-        <v>1.2459658143304568e-05</v>
+        <v>1.2068406259105221e-05</v>
       </c>
       <c r="E25">
-        <v>-2.3703806077740918e-08</v>
+        <v>-2.019680137828838e-08</v>
       </c>
       <c r="F25">
-        <v>2.6840814959948789e-06</v>
+        <v>7.3325191904736575e-06</v>
       </c>
       <c r="G25">
-        <v>0.00010042887687203324</v>
+        <v>0.00010496985164197403</v>
       </c>
       <c r="H25">
-        <v>2.2871316319884326e-05</v>
+        <v>3.5154995881514023e-05</v>
       </c>
       <c r="I25">
-        <v>2.0656766935375653e-05</v>
+        <v>2.3598843092312557e-05</v>
       </c>
       <c r="J25">
-        <v>1.0739068533409171e-05</v>
+        <v>1.1311372692250869e-05</v>
       </c>
       <c r="K25">
-        <v>-2.7042754110714645e-05</v>
+        <v>-2.5286700238444392e-05</v>
       </c>
       <c r="L25">
-        <v>-1.3947854852402062e-05</v>
+        <v>-1.3796579052501655e-05</v>
       </c>
       <c r="M25">
-        <v>-2.6543288045339635e-05</v>
+        <v>-2.7157703428098845e-05</v>
       </c>
       <c r="N25">
-        <v>-0.00019455881047950019</v>
+        <v>-0.00019790241739100958</v>
       </c>
       <c r="O25">
-        <v>2.0638426417259916e-06</v>
+        <v>2.1349448885148807e-06</v>
       </c>
       <c r="P25">
-        <v>-1.838557902013717e-05</v>
+        <v>-2.0661299500110961e-05</v>
       </c>
       <c r="Q25">
-        <v>3.5383472222992205e-05</v>
+        <v>3.4096513352007232e-05</v>
       </c>
       <c r="R25">
-        <v>0.00086808413924651176</v>
+        <v>0.00089127060186100504</v>
       </c>
       <c r="S25">
-        <v>0.001011832552426175</v>
+        <v>0.0010319563433645457</v>
       </c>
       <c r="T25">
-        <v>0.0010131884884441063</v>
+        <v>0.0010400001708056883</v>
       </c>
       <c r="U25">
-        <v>-0.00011025696117060967</v>
+        <v>-0.00010553482450312464</v>
       </c>
       <c r="V25">
-        <v>-0.0002512294983747854</v>
+        <v>-0.00023861001404968957</v>
       </c>
       <c r="W25">
-        <v>-0.00029189933431725788</v>
+        <v>-0.00027720321106184959</v>
       </c>
       <c r="X25">
-        <v>0.00039641171952480795</v>
+        <v>0.00039799076756211443</v>
       </c>
       <c r="Y25">
-        <v>0.00034773189747253736</v>
+        <v>0.00034754770859169825</v>
       </c>
       <c r="Z25">
-        <v>0.0070342460774750837</v>
+        <v>0.007084741218361292</v>
       </c>
       <c r="AA25">
-        <v>-0.0001154367134606442</v>
+        <v>-0.00012305285941720484</v>
       </c>
       <c r="AB25">
-        <v>-7.3780374970814234e-05</v>
+        <v>-8.1863036665034993e-05</v>
       </c>
       <c r="AC25">
-        <v>-8.4013493835154434e-05</v>
+        <v>-9.7050776052944943e-05</v>
       </c>
       <c r="AD25">
-        <v>-6.8095470249913991e-05</v>
+        <v>-7.5280938311871721e-05</v>
       </c>
       <c r="AE25">
-        <v>-6.4623941889244884e-05</v>
+        <v>-7.5616856199937069e-05</v>
       </c>
       <c r="AF25">
-        <v>-0.00015215740231570534</v>
+        <v>-0.00016097100158499842</v>
       </c>
       <c r="AG25">
-        <v>-7.2766051630554189e-07</v>
+        <v>-4.461270944023758e-06</v>
       </c>
       <c r="AH25">
-        <v>-0.0015053921370662363</v>
+        <v>0.00018554183225410093</v>
+      </c>
+      <c r="AI25">
+        <v>8.7218874822208697e-05</v>
+      </c>
+      <c r="AJ25">
+        <v>-0.0014865553221428342</v>
       </c>
     </row>
     <row r="26">
@@ -3169,103 +3325,109 @@
         <v>41</v>
       </c>
       <c r="B26">
-        <v>0.24869216178533521</v>
+        <v>0.24989273312437241</v>
       </c>
       <c r="C26">
-        <v>2.2234755090753911e-05</v>
+        <v>2.008944525785602e-05</v>
       </c>
       <c r="D26">
-        <v>-2.8963431150097192e-07</v>
+        <v>-5.6742895563629365e-08</v>
       </c>
       <c r="E26">
-        <v>-4.3415141386539307e-09</v>
+        <v>-6.8232360607243115e-09</v>
       </c>
       <c r="F26">
-        <v>-0.00035665476068260933</v>
+        <v>-0.0003879657408031901</v>
       </c>
       <c r="G26">
-        <v>-3.9753025021668992e-07</v>
+        <v>-7.4596915694141459e-06</v>
       </c>
       <c r="H26">
-        <v>1.1202492387732697e-05</v>
+        <v>-3.0570556696946517e-07</v>
       </c>
       <c r="I26">
-        <v>-3.2349431402661517e-05</v>
+        <v>-3.490996641805142e-05</v>
       </c>
       <c r="J26">
-        <v>6.7777764299665312e-06</v>
+        <v>4.8588571204757222e-06</v>
       </c>
       <c r="K26">
-        <v>-1.3495049181258111e-05</v>
+        <v>-1.2605071197613945e-05</v>
       </c>
       <c r="L26">
-        <v>4.0115925639870137e-06</v>
+        <v>3.617953627115794e-06</v>
       </c>
       <c r="M26">
-        <v>-5.1284221121947723e-06</v>
+        <v>-3.6761612594367478e-06</v>
       </c>
       <c r="N26">
-        <v>-8.2672830506223035e-05</v>
+        <v>-8.8766111784358784e-05</v>
       </c>
       <c r="O26">
-        <v>-1.6257769286366858e-07</v>
+        <v>-1.5685781831742667e-07</v>
       </c>
       <c r="P26">
-        <v>2.1887496361575705e-05</v>
+        <v>2.4480863746305988e-05</v>
       </c>
       <c r="Q26">
-        <v>-4.6053523644693905e-06</v>
+        <v>-4.8760279663096189e-06</v>
       </c>
       <c r="R26">
-        <v>-0.00015970902141392712</v>
+        <v>-0.00014345429489732997</v>
       </c>
       <c r="S26">
-        <v>-7.2127173569351555e-05</v>
+        <v>-5.4917603809427618e-05</v>
       </c>
       <c r="T26">
-        <v>-0.00012171966859791244</v>
+        <v>-0.00010644408694181207</v>
       </c>
       <c r="U26">
-        <v>-5.1728826957697649e-05</v>
+        <v>-3.3787078824263489e-05</v>
       </c>
       <c r="V26">
-        <v>-3.404242622366202e-05</v>
+        <v>-2.7087647779604554e-05</v>
       </c>
       <c r="W26">
-        <v>-4.5536644832460532e-05</v>
+        <v>-3.492590841396373e-05</v>
       </c>
       <c r="X26">
-        <v>-6.8691764685141227e-05</v>
+        <v>-6.6280645229651496e-05</v>
       </c>
       <c r="Y26">
-        <v>-4.6965734606338699e-05</v>
+        <v>-4.7904968243904088e-05</v>
       </c>
       <c r="Z26">
-        <v>-0.0001154367134606442</v>
+        <v>-0.00012305285941720484</v>
       </c>
       <c r="AA26">
-        <v>0.0034634679795363253</v>
+        <v>0.0034619170763470239</v>
       </c>
       <c r="AB26">
-        <v>0.0029053006524198378</v>
+        <v>0.0029029759032347894</v>
       </c>
       <c r="AC26">
-        <v>0.0029095023967118509</v>
+        <v>0.0029085033857017997</v>
       </c>
       <c r="AD26">
-        <v>0.0029086551719373537</v>
+        <v>0.0029060405772065173</v>
       </c>
       <c r="AE26">
-        <v>0.0029087270204631562</v>
+        <v>0.0029087243273573822</v>
       </c>
       <c r="AF26">
-        <v>0.0029091359848835499</v>
+        <v>0.0029070270264578901</v>
       </c>
       <c r="AG26">
-        <v>-6.0430964146783003e-06</v>
+        <v>-1.4313372219291668e-06</v>
       </c>
       <c r="AH26">
-        <v>-0.0025364980888062374</v>
+        <v>-0.00023490624061426506</v>
+      </c>
+      <c r="AI26">
+        <v>-0.00010769817196022084</v>
+      </c>
+      <c r="AJ26">
+        <v>-0.0026099034608096233</v>
       </c>
     </row>
     <row r="27">
@@ -3273,103 +3435,109 @@
         <v>42</v>
       </c>
       <c r="B27">
-        <v>0.1186014202943803</v>
+        <v>0.12004958849408647</v>
       </c>
       <c r="C27">
-        <v>3.2851493319003622e-05</v>
+        <v>3.0620277680629821e-05</v>
       </c>
       <c r="D27">
-        <v>2.9920934160534854e-06</v>
+        <v>3.1955560987219204e-06</v>
       </c>
       <c r="E27">
-        <v>-3.2763529015902064e-08</v>
+        <v>-3.4670737634483481e-08</v>
       </c>
       <c r="F27">
-        <v>-0.00031278162733416247</v>
+        <v>-0.0003438759676396907</v>
       </c>
       <c r="G27">
-        <v>6.2341965845422702e-05</v>
+        <v>5.4673612840301764e-05</v>
       </c>
       <c r="H27">
-        <v>4.0732752038115892e-05</v>
+        <v>2.9363457396843162e-05</v>
       </c>
       <c r="I27">
-        <v>-1.7887042008131091e-05</v>
+        <v>-2.0527092432584375e-05</v>
       </c>
       <c r="J27">
-        <v>7.7405084287827147e-06</v>
+        <v>5.9795931515586247e-06</v>
       </c>
       <c r="K27">
-        <v>-4.968256124866983e-05</v>
+        <v>-4.8552193531725685e-05</v>
       </c>
       <c r="L27">
-        <v>3.056533745855855e-06</v>
+        <v>2.67415623426097e-06</v>
       </c>
       <c r="M27">
-        <v>-8.2864567449780173e-06</v>
+        <v>-7.0413633157318348e-06</v>
       </c>
       <c r="N27">
-        <v>-9.658300844157721e-05</v>
+        <v>-0.00010466159803707801</v>
       </c>
       <c r="O27">
-        <v>-1.2290727439932272e-07</v>
+        <v>-1.1896263647887223e-07</v>
       </c>
       <c r="P27">
-        <v>1.3711097321521899e-05</v>
+        <v>1.6708748131363219e-05</v>
       </c>
       <c r="Q27">
-        <v>-5.5999208484619478e-06</v>
+        <v>-6.1243900260174889e-06</v>
       </c>
       <c r="R27">
-        <v>-9.796613118667058e-05</v>
+        <v>-8.3691032520712139e-05</v>
       </c>
       <c r="S27">
-        <v>-4.3666801738166672e-05</v>
+        <v>-2.8529795788011236e-05</v>
       </c>
       <c r="T27">
-        <v>-8.6236695376440409e-05</v>
+        <v>-7.2881788181329565e-05</v>
       </c>
       <c r="U27">
-        <v>-0.00030443045987598588</v>
+        <v>-0.00028615808145876498</v>
       </c>
       <c r="V27">
-        <v>-0.00031135122940891512</v>
+        <v>-0.00030288158819016808</v>
       </c>
       <c r="W27">
-        <v>-0.00033727564414217162</v>
+        <v>-0.00032499519214412506</v>
       </c>
       <c r="X27">
-        <v>-9.1119440751068204e-05</v>
+        <v>-8.8778427547365536e-05</v>
       </c>
       <c r="Y27">
-        <v>-2.923279558224919e-05</v>
+        <v>-2.9352671216799006e-05</v>
       </c>
       <c r="Z27">
-        <v>-7.3780374970814234e-05</v>
+        <v>-8.1863036665034993e-05</v>
       </c>
       <c r="AA27">
-        <v>0.0029053006524198378</v>
+        <v>0.0029029759032347894</v>
       </c>
       <c r="AB27">
-        <v>0.0035366481164324105</v>
+        <v>0.0035373462453600541</v>
       </c>
       <c r="AC27">
-        <v>0.0029229124848833415</v>
+        <v>0.0029216686038496913</v>
       </c>
       <c r="AD27">
-        <v>0.0029076877790324696</v>
+        <v>0.0029052706475953551</v>
       </c>
       <c r="AE27">
-        <v>0.0029156119435319676</v>
+        <v>0.0029154973797012431</v>
       </c>
       <c r="AF27">
-        <v>0.0029094981720951718</v>
+        <v>0.0029077053027501297</v>
       </c>
       <c r="AG27">
-        <v>-5.0869656480458478e-06</v>
+        <v>-1.0244352968129001e-06</v>
       </c>
       <c r="AH27">
-        <v>-0.0024201521414660811</v>
+        <v>-0.00021127524913756943</v>
+      </c>
+      <c r="AI27">
+        <v>-8.7048774519841922e-05</v>
+      </c>
+      <c r="AJ27">
+        <v>-0.0024873590331442085</v>
       </c>
     </row>
     <row r="28">
@@ -3377,103 +3545,109 @@
         <v>43</v>
       </c>
       <c r="B28">
-        <v>0.37575415649523608</v>
+        <v>0.37943915130448625</v>
       </c>
       <c r="C28">
-        <v>1.9518044904853678e-05</v>
+        <v>1.737095255270012e-05</v>
       </c>
       <c r="D28">
-        <v>-7.7616755457745891e-07</v>
+        <v>-6.8472474563408703e-07</v>
       </c>
       <c r="E28">
-        <v>-9.6861377565618268e-09</v>
+        <v>-1.0666190224700449e-08</v>
       </c>
       <c r="F28">
-        <v>-0.00029149891908651052</v>
+        <v>-0.00032144368232211009</v>
       </c>
       <c r="G28">
-        <v>5.4421947256034584e-05</v>
+        <v>4.9310795184917987e-05</v>
       </c>
       <c r="H28">
-        <v>4.2613918864713538e-05</v>
+        <v>3.4039029180815849e-05</v>
       </c>
       <c r="I28">
-        <v>-5.894578668109681e-06</v>
+        <v>-7.3287296165411089e-06</v>
       </c>
       <c r="J28">
-        <v>5.1500515317105544e-06</v>
+        <v>3.8411332852990127e-06</v>
       </c>
       <c r="K28">
-        <v>-6.5003285620603179e-05</v>
+        <v>-6.3493944229510251e-05</v>
       </c>
       <c r="L28">
-        <v>4.1252634444072315e-06</v>
+        <v>3.9441884765833681e-06</v>
       </c>
       <c r="M28">
-        <v>-6.7021501247420185e-06</v>
+        <v>-5.5340363770648717e-06</v>
       </c>
       <c r="N28">
-        <v>-0.00010420801169911981</v>
+        <v>-0.00011200549554738826</v>
       </c>
       <c r="O28">
-        <v>6.3858596175337177e-08</v>
+        <v>6.7224863809878748e-08</v>
       </c>
       <c r="P28">
-        <v>4.623236220552477e-06</v>
+        <v>6.6184178924230008e-06</v>
       </c>
       <c r="Q28">
-        <v>1.0134508858396089e-05</v>
+        <v>1.1151586887880134e-05</v>
       </c>
       <c r="R28">
-        <v>6.68068666565165e-06</v>
+        <v>1.9830693334169786e-05</v>
       </c>
       <c r="S28">
-        <v>7.0300032987269737e-05</v>
+        <v>8.3710665276034643e-05</v>
       </c>
       <c r="T28">
-        <v>1.6656544121773989e-05</v>
+        <v>2.9071147594358915e-05</v>
       </c>
       <c r="U28">
-        <v>-0.00044775772178987441</v>
+        <v>-0.00042684280750269425</v>
       </c>
       <c r="V28">
-        <v>-0.00044875602882456667</v>
+        <v>-0.0004365576943273974</v>
       </c>
       <c r="W28">
-        <v>-0.00043109935112108739</v>
+        <v>-0.00041555000174634937</v>
       </c>
       <c r="X28">
-        <v>-0.00010638648922825083</v>
+        <v>-0.0001025623456676171</v>
       </c>
       <c r="Y28">
-        <v>-6.6007459642419537e-05</v>
+        <v>-6.6569343664000434e-05</v>
       </c>
       <c r="Z28">
-        <v>-8.4013493835154434e-05</v>
+        <v>-9.7050776052944943e-05</v>
       </c>
       <c r="AA28">
-        <v>0.0029095023967118509</v>
+        <v>0.0029085033857017997</v>
       </c>
       <c r="AB28">
-        <v>0.0029229124848833415</v>
+        <v>0.0029216686038496913</v>
       </c>
       <c r="AC28">
-        <v>0.00376612821519206</v>
+        <v>0.0037686949155632948</v>
       </c>
       <c r="AD28">
-        <v>0.0029111451942414671</v>
+        <v>0.0029101001154186691</v>
       </c>
       <c r="AE28">
-        <v>0.0029178433517936205</v>
+        <v>0.0029185591438347729</v>
       </c>
       <c r="AF28">
-        <v>0.0029120563030947755</v>
+        <v>0.0029115119018080456</v>
       </c>
       <c r="AG28">
-        <v>-1.0045971589327611e-05</v>
+        <v>-6.639213141441388e-06</v>
       </c>
       <c r="AH28">
-        <v>-0.0021825387384951708</v>
+        <v>-0.00015229613577247584</v>
+      </c>
+      <c r="AI28">
+        <v>-0.00010316146593031673</v>
+      </c>
+      <c r="AJ28">
+        <v>-0.0022453718805205509</v>
       </c>
     </row>
     <row r="29">
@@ -3481,103 +3655,109 @@
         <v>44</v>
       </c>
       <c r="B29">
-        <v>0.1967553746893452</v>
+        <v>0.19953268158107076</v>
       </c>
       <c r="C29">
-        <v>1.186426867075995e-05</v>
+        <v>9.9550358277092029e-06</v>
       </c>
       <c r="D29">
-        <v>2.9705298366321492e-06</v>
+        <v>3.2431857514446849e-06</v>
       </c>
       <c r="E29">
-        <v>-3.5228759364842849e-08</v>
+        <v>-3.7838868997234808e-08</v>
       </c>
       <c r="F29">
-        <v>-0.00030614056520443549</v>
+        <v>-0.00033621321242632862</v>
       </c>
       <c r="G29">
-        <v>5.3714956046137257e-05</v>
+        <v>4.5919926953411143e-05</v>
       </c>
       <c r="H29">
-        <v>4.362694109231747e-05</v>
+        <v>3.1579243025551076e-05</v>
       </c>
       <c r="I29">
-        <v>-1.3738714630288901e-05</v>
+        <v>-1.6400313896113033e-05</v>
       </c>
       <c r="J29">
-        <v>2.1048768021260701e-06</v>
+        <v>3.582330656313413e-07</v>
       </c>
       <c r="K29">
-        <v>-7.6640437867028875e-06</v>
+        <v>-6.7674234959375079e-06</v>
       </c>
       <c r="L29">
-        <v>3.8857613465943921e-06</v>
+        <v>3.5712211650880036e-06</v>
       </c>
       <c r="M29">
-        <v>-6.0174381488210799e-06</v>
+        <v>-4.717933822105455e-06</v>
       </c>
       <c r="N29">
-        <v>-8.2261303497731427e-05</v>
+        <v>-8.7585297829528234e-05</v>
       </c>
       <c r="O29">
-        <v>-2.7688962830133273e-07</v>
+        <v>-2.8464340596502083e-07</v>
       </c>
       <c r="P29">
-        <v>2.2916275614285242e-05</v>
+        <v>2.4974489775260748e-05</v>
       </c>
       <c r="Q29">
-        <v>1.2856077569123976e-05</v>
+        <v>1.3065401879147837e-05</v>
       </c>
       <c r="R29">
-        <v>-0.00022133172117906608</v>
+        <v>-0.00021070400319908589</v>
       </c>
       <c r="S29">
-        <v>-0.0001012817213137257</v>
+        <v>-8.9978529541907826e-05</v>
       </c>
       <c r="T29">
-        <v>-0.00014398854076355661</v>
+        <v>-0.00013469766881531176</v>
       </c>
       <c r="U29">
-        <v>1.2339985309965662e-05</v>
+        <v>3.0242113666888171e-05</v>
       </c>
       <c r="V29">
-        <v>2.7765915279077264e-06</v>
+        <v>1.0262788959360114e-05</v>
       </c>
       <c r="W29">
-        <v>2.9091084384758048e-05</v>
+        <v>4.0257242717714123e-05</v>
       </c>
       <c r="X29">
-        <v>-8.4685032830998479e-05</v>
+        <v>-8.1845277992750713e-05</v>
       </c>
       <c r="Y29">
-        <v>-3.5135767100815426e-05</v>
+        <v>-3.4827249257180079e-05</v>
       </c>
       <c r="Z29">
-        <v>-6.8095470249913991e-05</v>
+        <v>-7.5280938311871721e-05</v>
       </c>
       <c r="AA29">
-        <v>0.0029086551719373537</v>
+        <v>0.0029060405772065173</v>
       </c>
       <c r="AB29">
-        <v>0.0029076877790324696</v>
+        <v>0.0029052706475953551</v>
       </c>
       <c r="AC29">
-        <v>0.0029111451942414671</v>
+        <v>0.0029101001154186691</v>
       </c>
       <c r="AD29">
-        <v>0.0033894969917529208</v>
+        <v>0.0033873501817333592</v>
       </c>
       <c r="AE29">
-        <v>0.002914499956872132</v>
+        <v>0.0029144264479919156</v>
       </c>
       <c r="AF29">
-        <v>0.0029166080225927161</v>
+        <v>0.0029144657171838707</v>
       </c>
       <c r="AG29">
-        <v>-6.7784716042879382e-06</v>
+        <v>-2.4475277782291051e-06</v>
       </c>
       <c r="AH29">
-        <v>-0.0026229523256446809</v>
+        <v>-0.0002167506171987469</v>
+      </c>
+      <c r="AI29">
+        <v>-0.00010420829566168258</v>
+      </c>
+      <c r="AJ29">
+        <v>-0.0026899104053870653</v>
       </c>
     </row>
     <row r="30">
@@ -3585,103 +3765,109 @@
         <v>45</v>
       </c>
       <c r="B30">
-        <v>0.28713881263283192</v>
+        <v>0.28878556231026104</v>
       </c>
       <c r="C30">
-        <v>2.0848925512747659e-05</v>
+        <v>1.8740201872788885e-05</v>
       </c>
       <c r="D30">
-        <v>-7.6108715431803884e-07</v>
+        <v>-8.2469178198846168e-07</v>
       </c>
       <c r="E30">
-        <v>4.83441720118436e-09</v>
+        <v>5.3965842930057215e-09</v>
       </c>
       <c r="F30">
-        <v>-0.00030570504301377589</v>
+        <v>-0.00033238896329270599</v>
       </c>
       <c r="G30">
-        <v>6.5974288557758365e-05</v>
+        <v>6.1274752174575741e-05</v>
       </c>
       <c r="H30">
-        <v>6.1628326391954697e-05</v>
+        <v>5.5209910383559709e-05</v>
       </c>
       <c r="I30">
-        <v>1.6392407808113615e-06</v>
+        <v>7.8808003916201817e-07</v>
       </c>
       <c r="J30">
-        <v>7.0349394531768444e-06</v>
+        <v>5.711689207059639e-06</v>
       </c>
       <c r="K30">
-        <v>-3.3770335514039535e-05</v>
+        <v>-3.2184299087756286e-05</v>
       </c>
       <c r="L30">
-        <v>3.2539170285022785e-06</v>
+        <v>2.9579091092853315e-06</v>
       </c>
       <c r="M30">
-        <v>-7.3972617268349515e-06</v>
+        <v>-6.538428092497768e-06</v>
       </c>
       <c r="N30">
-        <v>-9.2899386823946158e-05</v>
+        <v>-0.0001014477349346528</v>
       </c>
       <c r="O30">
-        <v>-2.33255875422019e-07</v>
+        <v>-2.2703670235616047e-07</v>
       </c>
       <c r="P30">
-        <v>2.9564094892454399e-06</v>
+        <v>5.4294317632951387e-06</v>
       </c>
       <c r="Q30">
-        <v>2.6691720750643758e-05</v>
+        <v>2.6647312627876472e-05</v>
       </c>
       <c r="R30">
-        <v>-0.00018486922394329863</v>
+        <v>-0.0001713867178525768</v>
       </c>
       <c r="S30">
-        <v>-9.1629844759622686e-05</v>
+        <v>-7.7348360760081183e-05</v>
       </c>
       <c r="T30">
-        <v>-0.00013276447865572493</v>
+        <v>-0.00011938335773575316</v>
       </c>
       <c r="U30">
-        <v>-0.00020949657855305528</v>
+        <v>-0.00018854380716434079</v>
       </c>
       <c r="V30">
-        <v>-0.00019752927270313796</v>
+        <v>-0.00018557136633158295</v>
       </c>
       <c r="W30">
-        <v>-0.0002142572191855454</v>
+        <v>-0.00019909139433911278</v>
       </c>
       <c r="X30">
-        <v>-8.1631800335603351e-05</v>
+        <v>-7.9303566415632899e-05</v>
       </c>
       <c r="Y30">
-        <v>-2.9396846011165123e-05</v>
+        <v>-2.9747572854813415e-05</v>
       </c>
       <c r="Z30">
-        <v>-6.4623941889244884e-05</v>
+        <v>-7.5616856199937069e-05</v>
       </c>
       <c r="AA30">
-        <v>0.0029087270204631562</v>
+        <v>0.0029087243273573822</v>
       </c>
       <c r="AB30">
-        <v>0.0029156119435319676</v>
+        <v>0.0029154973797012431</v>
       </c>
       <c r="AC30">
-        <v>0.0029178433517936205</v>
+        <v>0.0029185591438347729</v>
       </c>
       <c r="AD30">
-        <v>0.002914499956872132</v>
+        <v>0.0029144264479919156</v>
       </c>
       <c r="AE30">
-        <v>0.0033107890975492861</v>
+        <v>0.003313065612739129</v>
       </c>
       <c r="AF30">
-        <v>0.0029149635045843175</v>
+        <v>0.0029152380562523788</v>
       </c>
       <c r="AG30">
-        <v>-6.8396461337696168e-06</v>
+        <v>-4.2143116683275095e-06</v>
       </c>
       <c r="AH30">
-        <v>-0.0023799265555945462</v>
+        <v>-0.00013314379931529544</v>
+      </c>
+      <c r="AI30">
+        <v>-6.5950887269362532e-05</v>
+      </c>
+      <c r="AJ30">
+        <v>-0.0024311174448058094</v>
       </c>
     </row>
     <row r="31">
@@ -3689,103 +3875,109 @@
         <v>46</v>
       </c>
       <c r="B31">
-        <v>0.16186216833390327</v>
+        <v>0.16224224554125677</v>
       </c>
       <c r="C31">
-        <v>1.8016048059746909e-05</v>
+        <v>1.6236824556625044e-05</v>
       </c>
       <c r="D31">
-        <v>-9.9309227653372669e-07</v>
+        <v>-1.0605696990893357e-06</v>
       </c>
       <c r="E31">
-        <v>-8.1460225145584858e-10</v>
+        <v>-7.9962469026845007e-10</v>
       </c>
       <c r="F31">
-        <v>-0.00030864186912341182</v>
+        <v>-0.00033821930018997277</v>
       </c>
       <c r="G31">
-        <v>6.9240617735101252e-05</v>
+        <v>6.3162003885449379e-05</v>
       </c>
       <c r="H31">
-        <v>4.9979475708497805e-05</v>
+        <v>4.0949210002263745e-05</v>
       </c>
       <c r="I31">
-        <v>-7.9407637682717063e-06</v>
+        <v>-1.0023184592857515e-05</v>
       </c>
       <c r="J31">
-        <v>1.4171980792534952e-05</v>
+        <v>1.2897999056349304e-05</v>
       </c>
       <c r="K31">
-        <v>-2.860533445252938e-05</v>
+        <v>-2.8043883466234308e-05</v>
       </c>
       <c r="L31">
-        <v>3.3464814574087493e-06</v>
+        <v>3.1652168661934511e-06</v>
       </c>
       <c r="M31">
-        <v>-3.929834504762094e-06</v>
+        <v>-2.9057213094194881e-06</v>
       </c>
       <c r="N31">
-        <v>-0.0001177618979195913</v>
+        <v>-0.0001261852041956013</v>
       </c>
       <c r="O31">
-        <v>-3.9428947924147748e-08</v>
+        <v>-3.4574382276464022e-08</v>
       </c>
       <c r="P31">
-        <v>2.5283624473737147e-05</v>
+        <v>2.8341475067845799e-05</v>
       </c>
       <c r="Q31">
-        <v>2.7645467661454508e-06</v>
+        <v>3.0591265652514424e-06</v>
       </c>
       <c r="R31">
-        <v>-0.00011959226924120221</v>
+        <v>-0.00010334947615037171</v>
       </c>
       <c r="S31">
-        <v>3.3619327642619989e-07</v>
+        <v>1.6882261361857685e-05</v>
       </c>
       <c r="T31">
-        <v>-5.0895615875704188e-05</v>
+        <v>-3.5312369631867666e-05</v>
       </c>
       <c r="U31">
-        <v>-0.00021687740502025462</v>
+        <v>-0.00020352959101305667</v>
       </c>
       <c r="V31">
-        <v>-0.0002152364161605992</v>
+        <v>-0.00021021413701004374</v>
       </c>
       <c r="W31">
-        <v>-0.00016989106295890819</v>
+        <v>-0.00015975550368417177</v>
       </c>
       <c r="X31">
-        <v>-9.5426843787421178e-05</v>
+        <v>-9.2811942185132366e-05</v>
       </c>
       <c r="Y31">
-        <v>-4.1457980832742397e-05</v>
+        <v>-4.2999107983410516e-05</v>
       </c>
       <c r="Z31">
-        <v>-0.00015215740231570534</v>
+        <v>-0.00016097100158499842</v>
       </c>
       <c r="AA31">
-        <v>0.0029091359848835499</v>
+        <v>0.0029070270264578901</v>
       </c>
       <c r="AB31">
-        <v>0.0029094981720951718</v>
+        <v>0.0029077053027501297</v>
       </c>
       <c r="AC31">
-        <v>0.0029120563030947755</v>
+        <v>0.0029115119018080456</v>
       </c>
       <c r="AD31">
-        <v>0.0029166080225927161</v>
+        <v>0.0029144657171838707</v>
       </c>
       <c r="AE31">
-        <v>0.0029149635045843175</v>
+        <v>0.0029152380562523788</v>
       </c>
       <c r="AF31">
-        <v>0.0034404797885385281</v>
+        <v>0.0034389348138001174</v>
       </c>
       <c r="AG31">
-        <v>-6.5205985603400242e-06</v>
+        <v>-2.9793961509160124e-06</v>
       </c>
       <c r="AH31">
-        <v>-0.0024522664016238174</v>
+        <v>-0.00016166259147393789</v>
+      </c>
+      <c r="AI31">
+        <v>-9.908780070286982e-05</v>
+      </c>
+      <c r="AJ31">
+        <v>-0.0025057044599426648</v>
       </c>
     </row>
     <row r="32">
@@ -3793,103 +3985,109 @@
         <v>47</v>
       </c>
       <c r="B32">
-        <v>-0.054980541675969698</v>
+        <v>-0.048669337576933626</v>
       </c>
       <c r="C32">
-        <v>3.2427673415165035e-07</v>
+        <v>4.5706930769845149e-07</v>
       </c>
       <c r="D32">
-        <v>-7.3688707800804895e-08</v>
+        <v>-1.2611444277851479e-08</v>
       </c>
       <c r="E32">
-        <v>-1.7697718347875624e-09</v>
+        <v>-2.1088776176912062e-09</v>
       </c>
       <c r="F32">
-        <v>1.312790935562137e-06</v>
+        <v>-1.0847629299590987e-06</v>
       </c>
       <c r="G32">
-        <v>-9.143016305353215e-07</v>
+        <v>-7.7394332615398398e-07</v>
       </c>
       <c r="H32">
-        <v>-4.1721118033656768e-06</v>
+        <v>-3.6728508684652067e-06</v>
       </c>
       <c r="I32">
-        <v>-2.6956156767708938e-06</v>
+        <v>-2.2712442873387257e-06</v>
       </c>
       <c r="J32">
-        <v>7.1113663786945166e-07</v>
+        <v>9.7116927496613578e-07</v>
       </c>
       <c r="K32">
-        <v>-6.5742139252626447e-07</v>
+        <v>-5.0741236670478877e-07</v>
       </c>
       <c r="L32">
-        <v>-2.7301158488969425e-07</v>
+        <v>-2.2299980491866647e-07</v>
       </c>
       <c r="M32">
-        <v>1.4314811093280512e-06</v>
+        <v>1.4247585618967477e-06</v>
       </c>
       <c r="N32">
-        <v>9.1740824583342456e-09</v>
+        <v>-6.4342264269657049e-07</v>
       </c>
       <c r="O32">
-        <v>-1.8458298843144048e-08</v>
+        <v>-1.2076834283234572e-08</v>
       </c>
       <c r="P32">
-        <v>-8.6018516675320246e-08</v>
+        <v>-4.0507905806822829e-07</v>
       </c>
       <c r="Q32">
-        <v>-5.5269597205395856e-07</v>
+        <v>-5.597041323916139e-07</v>
       </c>
       <c r="R32">
-        <v>-6.1724273337825444e-06</v>
+        <v>-4.650223596836282e-06</v>
       </c>
       <c r="S32">
-        <v>-1.2741045310613259e-05</v>
+        <v>-1.1098044695567527e-05</v>
       </c>
       <c r="T32">
-        <v>-1.6854466762370466e-05</v>
+        <v>-1.5124170488833594e-05</v>
       </c>
       <c r="U32">
-        <v>-1.4329823761891102e-05</v>
+        <v>-1.2037901713926298e-05</v>
       </c>
       <c r="V32">
-        <v>-1.3631811037048344e-06</v>
+        <v>3.298568482878279e-07</v>
       </c>
       <c r="W32">
-        <v>-1.2259196194089328e-06</v>
+        <v>3.6350820467926336e-07</v>
       </c>
       <c r="X32">
-        <v>3.0921685381445773e-06</v>
+        <v>2.8892275891271729e-06</v>
       </c>
       <c r="Y32">
-        <v>1.3405765647571658e-06</v>
+        <v>7.0353498413279949e-07</v>
       </c>
       <c r="Z32">
-        <v>-7.2766051630554189e-07</v>
+        <v>-4.461270944023758e-06</v>
       </c>
       <c r="AA32">
-        <v>-6.0430964146783003e-06</v>
+        <v>-1.4313372219291668e-06</v>
       </c>
       <c r="AB32">
-        <v>-5.0869656480458478e-06</v>
+        <v>-1.0244352968129001e-06</v>
       </c>
       <c r="AC32">
-        <v>-1.0045971589327611e-05</v>
+        <v>-6.639213141441388e-06</v>
       </c>
       <c r="AD32">
-        <v>-6.7784716042879382e-06</v>
+        <v>-2.4475277782291051e-06</v>
       </c>
       <c r="AE32">
-        <v>-6.8396461337696168e-06</v>
+        <v>-4.2143116683275095e-06</v>
       </c>
       <c r="AF32">
-        <v>-6.5205985603400242e-06</v>
+        <v>-2.9793961509160124e-06</v>
       </c>
       <c r="AG32">
-        <v>5.8071372461245838e-06</v>
+        <v>5.6533435071966701e-06</v>
       </c>
       <c r="AH32">
-        <v>-7.7171881835745929e-05</v>
+        <v>-5.997998105176366e-06</v>
+      </c>
+      <c r="AI32">
+        <v>-1.2444182098481972e-05</v>
+      </c>
+      <c r="AJ32">
+        <v>-8.371642391915619e-05</v>
       </c>
     </row>
     <row r="33">
@@ -3897,103 +4095,329 @@
         <v>48</v>
       </c>
       <c r="B33">
-        <v>0.39018980515380575</v>
+        <v>0.0015405392933348944</v>
       </c>
       <c r="C33">
-        <v>0.00034613295039739823</v>
+        <v>-1.1395694809765368e-05</v>
       </c>
       <c r="D33">
-        <v>-0.00028780368450828913</v>
+        <v>-1.7413413081221549e-06</v>
       </c>
       <c r="E33">
-        <v>2.7132771203039535e-06</v>
+        <v>2.52249146753247e-10</v>
       </c>
       <c r="F33">
-        <v>-0.00015056543033221308</v>
+        <v>0.0001415248638067281</v>
       </c>
       <c r="G33">
-        <v>-0.00034746826021087105</v>
+        <v>-2.2030612711127417e-05</v>
       </c>
       <c r="H33">
-        <v>-0.0002912081307662889</v>
+        <v>-2.6350577141604002e-06</v>
       </c>
       <c r="I33">
-        <v>-0.00013817329010755008</v>
+        <v>-2.4612296879961913e-05</v>
       </c>
       <c r="J33">
-        <v>3.8241408493853369e-05</v>
+        <v>-1.5609354672070172e-06</v>
       </c>
       <c r="K33">
-        <v>-0.0029148802844716684</v>
+        <v>-1.4728989282367707e-05</v>
       </c>
       <c r="L33">
-        <v>0.00011060536569436742</v>
+        <v>-1.2428005193927032e-06</v>
       </c>
       <c r="M33">
-        <v>-2.6282177451205223e-05</v>
+        <v>-2.2626364425119899e-06</v>
       </c>
       <c r="N33">
-        <v>-0.0052036650527938558</v>
+        <v>-2.2164138048162176e-05</v>
       </c>
       <c r="O33">
-        <v>-9.7153524140074275e-05</v>
+        <v>-5.7196816117010857e-07</v>
       </c>
       <c r="P33">
-        <v>-0.0004777439030639913</v>
+        <v>1.1604885549131006e-05</v>
       </c>
       <c r="Q33">
-        <v>0.0023588968083124527</v>
+        <v>1.9939508548757427e-05</v>
       </c>
       <c r="R33">
-        <v>-0.048849629572997613</v>
+        <v>-0.0001895486371505592</v>
       </c>
       <c r="S33">
-        <v>-0.048495498961884945</v>
+        <v>-0.00018796882303842577</v>
       </c>
       <c r="T33">
-        <v>-0.047875562641307878</v>
+        <v>-0.0002140049657082671</v>
       </c>
       <c r="U33">
-        <v>-0.026834991417646989</v>
+        <v>-0.0001512338373518933</v>
       </c>
       <c r="V33">
-        <v>-0.022908844474863507</v>
+        <v>-0.0001359753622682848</v>
       </c>
       <c r="W33">
-        <v>-0.02377072641085777</v>
+        <v>-0.00011810315069277558</v>
       </c>
       <c r="X33">
-        <v>-0.00074744863532919524</v>
+        <v>2.3279697372624348e-05</v>
       </c>
       <c r="Y33">
-        <v>-0.00082986178935164729</v>
+        <v>4.3654792742303509e-05</v>
       </c>
       <c r="Z33">
-        <v>-0.0015053921370662363</v>
+        <v>0.00018554183225410093</v>
       </c>
       <c r="AA33">
-        <v>-0.0025364980888062374</v>
+        <v>-0.00023490624061426506</v>
       </c>
       <c r="AB33">
-        <v>-0.0024201521414660811</v>
+        <v>-0.00021127524913756943</v>
       </c>
       <c r="AC33">
-        <v>-0.0021825387384951708</v>
+        <v>-0.00015229613577247584</v>
       </c>
       <c r="AD33">
-        <v>-0.0026229523256446809</v>
+        <v>-0.0002167506171987469</v>
       </c>
       <c r="AE33">
-        <v>-0.0023799265555945462</v>
+        <v>-0.00013314379931529544</v>
       </c>
       <c r="AF33">
-        <v>-0.0024522664016238174</v>
+        <v>-0.00016166259147393789</v>
       </c>
       <c r="AG33">
-        <v>-7.7171881835745929e-05</v>
+        <v>-5.997998105176366e-06</v>
       </c>
       <c r="AH33">
-        <v>0.082637151128951647</v>
+        <v>0.001799609755040728</v>
+      </c>
+      <c r="AI33">
+        <v>0.00019303518533604131</v>
+      </c>
+      <c r="AJ33">
+        <v>0.00060398840478209724</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34">
+        <v>-0.46934929547261428</v>
+      </c>
+      <c r="C34">
+        <v>7.7841352484640314e-07</v>
+      </c>
+      <c r="D34">
+        <v>-5.8608815061820762e-06</v>
+      </c>
+      <c r="E34">
+        <v>5.1451634562556878e-08</v>
+      </c>
+      <c r="F34">
+        <v>9.6796122039921882e-05</v>
+      </c>
+      <c r="G34">
+        <v>3.1578757810894997e-05</v>
+      </c>
+      <c r="H34">
+        <v>1.7121646091136532e-05</v>
+      </c>
+      <c r="I34">
+        <v>3.2512755883705105e-06</v>
+      </c>
+      <c r="J34">
+        <v>-1.3730403899072507e-05</v>
+      </c>
+      <c r="K34">
+        <v>6.3375947813017154e-06</v>
+      </c>
+      <c r="L34">
+        <v>-2.4194662693187976e-06</v>
+      </c>
+      <c r="M34">
+        <v>-2.5026242273638586e-06</v>
+      </c>
+      <c r="N34">
+        <v>5.4763436536255702e-05</v>
+      </c>
+      <c r="O34">
+        <v>8.8186565686442837e-08</v>
+      </c>
+      <c r="P34">
+        <v>1.0604849255206464e-05</v>
+      </c>
+      <c r="Q34">
+        <v>-2.0131342377696995e-05</v>
+      </c>
+      <c r="R34">
+        <v>6.374556169201108e-05</v>
+      </c>
+      <c r="S34">
+        <v>5.0209324960333659e-05</v>
+      </c>
+      <c r="T34">
+        <v>6.5692277114502359e-05</v>
+      </c>
+      <c r="U34">
+        <v>-3.2714931552187479e-05</v>
+      </c>
+      <c r="V34">
+        <v>1.7109776470275624e-05</v>
+      </c>
+      <c r="W34">
+        <v>4.4973636718738733e-06</v>
+      </c>
+      <c r="X34">
+        <v>-4.8265097263521076e-06</v>
+      </c>
+      <c r="Y34">
+        <v>8.7640245386980315e-06</v>
+      </c>
+      <c r="Z34">
+        <v>8.7218874822208697e-05</v>
+      </c>
+      <c r="AA34">
+        <v>-0.00010769817196022084</v>
+      </c>
+      <c r="AB34">
+        <v>-8.7048774519841922e-05</v>
+      </c>
+      <c r="AC34">
+        <v>-0.00010316146593031673</v>
+      </c>
+      <c r="AD34">
+        <v>-0.00010420829566168258</v>
+      </c>
+      <c r="AE34">
+        <v>-6.5950887269362532e-05</v>
+      </c>
+      <c r="AF34">
+        <v>-9.908780070286982e-05</v>
+      </c>
+      <c r="AG34">
+        <v>-1.2444182098481972e-05</v>
+      </c>
+      <c r="AH34">
+        <v>0.00019303518533604131</v>
+      </c>
+      <c r="AI34">
+        <v>0.0013755066770988658</v>
+      </c>
+      <c r="AJ34">
+        <v>0.00029855710082384284</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35">
+        <v>0.30558455146641017</v>
+      </c>
+      <c r="C35">
+        <v>0.00034627450460851311</v>
+      </c>
+      <c r="D35">
+        <v>-0.00029159833162855969</v>
+      </c>
+      <c r="E35">
+        <v>2.7453203057273422e-06</v>
+      </c>
+      <c r="F35">
+        <v>-0.00011587260424335971</v>
+      </c>
+      <c r="G35">
+        <v>-0.00034392369399797193</v>
+      </c>
+      <c r="H35">
+        <v>-0.00028215220952928924</v>
+      </c>
+      <c r="I35">
+        <v>-0.00014186833008786152</v>
+      </c>
+      <c r="J35">
+        <v>3.89467405004832e-05</v>
+      </c>
+      <c r="K35">
+        <v>-0.0029244195253660971</v>
+      </c>
+      <c r="L35">
+        <v>0.00011265633956514313</v>
+      </c>
+      <c r="M35">
+        <v>-2.8201969746309123e-05</v>
+      </c>
+      <c r="N35">
+        <v>-0.0051345458324562228</v>
+      </c>
+      <c r="O35">
+        <v>-9.666866067589903e-05</v>
+      </c>
+      <c r="P35">
+        <v>-0.00045274442340696415</v>
+      </c>
+      <c r="Q35">
+        <v>0.0023562528910354447</v>
+      </c>
+      <c r="R35">
+        <v>-0.048628395941666985</v>
+      </c>
+      <c r="S35">
+        <v>-0.048269432432185289</v>
+      </c>
+      <c r="T35">
+        <v>-0.047652712381011209</v>
+      </c>
+      <c r="U35">
+        <v>-0.026942780966095696</v>
+      </c>
+      <c r="V35">
+        <v>-0.022981610082609877</v>
+      </c>
+      <c r="W35">
+        <v>-0.023842405045704632</v>
+      </c>
+      <c r="X35">
+        <v>-0.00074773814662214711</v>
+      </c>
+      <c r="Y35">
+        <v>-0.00082784343779009561</v>
+      </c>
+      <c r="Z35">
+        <v>-0.0014865553221428342</v>
+      </c>
+      <c r="AA35">
+        <v>-0.0026099034608096233</v>
+      </c>
+      <c r="AB35">
+        <v>-0.0024873590331442085</v>
+      </c>
+      <c r="AC35">
+        <v>-0.0022453718805205509</v>
+      </c>
+      <c r="AD35">
+        <v>-0.0026899104053870653</v>
+      </c>
+      <c r="AE35">
+        <v>-0.0024311174448058094</v>
+      </c>
+      <c r="AF35">
+        <v>-0.0025057044599426648</v>
+      </c>
+      <c r="AG35">
+        <v>-8.371642391915619e-05</v>
+      </c>
+      <c r="AH35">
+        <v>0.00060398840478209724</v>
+      </c>
+      <c r="AI35">
+        <v>0.00029855710082384284</v>
+      </c>
+      <c r="AJ35">
+        <v>0.082699131413959515</v>
       </c>
     </row>
   </sheetData>
@@ -4002,7 +4426,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AH32"/>
+  <dimension ref="A1:AJ34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4031,10 +4455,10 @@
         <v>23</v>
       </c>
       <c r="I1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K1" t="s">
         <v>25</v>
@@ -4043,16 +4467,16 @@
         <v>26</v>
       </c>
       <c r="M1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N1" t="s">
         <v>28</v>
       </c>
       <c r="O1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q1" t="s">
         <v>32</v>
@@ -4107,6 +4531,12 @@
       </c>
       <c r="AH1" t="s">
         <v>49</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="2">
@@ -4114,100 +4544,106 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>-0.010260375686786991</v>
+        <v>-0.017140229570873192</v>
       </c>
       <c r="C2">
-        <v>0.00024387016420996554</v>
+        <v>0.00033806938097501703</v>
       </c>
       <c r="D2">
-        <v>-1.2346889182066968e-06</v>
+        <v>-1.1778298065185433e-06</v>
       </c>
       <c r="E2">
-        <v>2.5907712733071444e-08</v>
+        <v>3.3006838742514826e-08</v>
       </c>
       <c r="F2">
-        <v>1.6182934861110855e-05</v>
+        <v>2.3502177242822334e-05</v>
       </c>
       <c r="G2">
-        <v>-1.5298460107365573e-05</v>
+        <v>-2.1957961697634844e-05</v>
       </c>
       <c r="H2">
-        <v>-4.2808229553902553e-06</v>
+        <v>-1.4483117365472833e-05</v>
       </c>
       <c r="I2">
-        <v>-4.625680081441417e-05</v>
+        <v>-6.721971269187937e-05</v>
       </c>
       <c r="J2">
-        <v>7.673705623548462e-06</v>
+        <v>4.1213408368018641e-05</v>
       </c>
       <c r="K2">
-        <v>-1.5474481394921801e-05</v>
+        <v>-2.226764468905269e-05</v>
       </c>
       <c r="L2">
-        <v>-6.1491109097676031e-07</v>
+        <v>-5.8287437428686758e-07</v>
       </c>
       <c r="M2">
-        <v>-4.3113017440064528e-06</v>
+        <v>-3.1723494920810533e-05</v>
       </c>
       <c r="N2">
-        <v>-0.00024019820742180766</v>
+        <v>-0.00032721101553160996</v>
       </c>
       <c r="O2">
-        <v>-1.0288408450762515e-05</v>
+        <v>-5.2190345536982111e-05</v>
       </c>
       <c r="P2">
-        <v>4.6918486669518108e-06</v>
+        <v>3.3053013638421755e-05</v>
       </c>
       <c r="Q2">
-        <v>-0.00018588921021277688</v>
+        <v>-0.0002335383041085244</v>
       </c>
       <c r="R2">
-        <v>-0.00018033001386842074</v>
+        <v>-0.0002303058251058735</v>
       </c>
       <c r="S2">
-        <v>-0.00015615417739911936</v>
+        <v>-0.00019378965804275452</v>
       </c>
       <c r="T2">
-        <v>-0.00010149179620665957</v>
+        <v>-0.00011173905231292986</v>
       </c>
       <c r="U2">
-        <v>-3.5238291414956995e-05</v>
+        <v>-6.1625668049730789e-05</v>
       </c>
       <c r="V2">
-        <v>-0.00014666270436385764</v>
+        <v>-0.00021239483960761732</v>
       </c>
       <c r="W2">
-        <v>2.8452502558465828e-05</v>
+        <v>3.9564821483017843e-05</v>
       </c>
       <c r="X2">
-        <v>6.5652393812434846e-06</v>
+        <v>-8.9443228905280233e-07</v>
       </c>
       <c r="Y2">
-        <v>0.000102507548319959</v>
+        <v>0.00013778405085550639</v>
       </c>
       <c r="Z2">
-        <v>-8.877803668276503e-06</v>
+        <v>5.7221913230602833e-06</v>
       </c>
       <c r="AA2">
-        <v>-5.8973248747452438e-06</v>
+        <v>1.0577578694776009e-05</v>
       </c>
       <c r="AB2">
-        <v>-9.8714966054679304e-06</v>
+        <v>7.2822143498292637e-06</v>
       </c>
       <c r="AC2">
-        <v>-9.2243777165275349e-06</v>
+        <v>4.2572345110106642e-06</v>
       </c>
       <c r="AD2">
-        <v>-2.4221781435151366e-05</v>
+        <v>-1.8895805004206254e-05</v>
       </c>
       <c r="AE2">
-        <v>-3.0923984250093275e-06</v>
+        <v>9.3130314107987875e-06</v>
       </c>
       <c r="AF2">
-        <v>-1.0539886173293146e-06</v>
+        <v>-1.1801453572122004e-07</v>
       </c>
       <c r="AG2">
-        <v>0.00017151388028960356</v>
+        <v>-7.8303737241919042e-05</v>
+      </c>
+      <c r="AH2">
+        <v>-2.8586673719581114e-05</v>
+      </c>
+      <c r="AI2">
+        <v>0.00018030146354133222</v>
       </c>
     </row>
     <row r="3">
@@ -4215,100 +4651,106 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>0.0079645408854857203</v>
+        <v>0.016935458362687471</v>
       </c>
       <c r="C3">
-        <v>-1.2346889182066968e-06</v>
+        <v>-1.1778298065185433e-06</v>
       </c>
       <c r="D3">
-        <v>1.187891504660902e-05</v>
+        <v>1.6416486361387738e-05</v>
       </c>
       <c r="E3">
-        <v>-1.0212374728358824e-07</v>
+        <v>-1.4363105323651625e-07</v>
       </c>
       <c r="F3">
-        <v>-4.6992045521010335e-06</v>
+        <v>-1.112691849875408e-05</v>
       </c>
       <c r="G3">
-        <v>-4.7609444038821897e-06</v>
+        <v>-1.049610769144287e-05</v>
       </c>
       <c r="H3">
-        <v>-7.9329939238223531e-06</v>
+        <v>-1.2277270060586291e-05</v>
       </c>
       <c r="I3">
-        <v>8.1183592218770902e-06</v>
+        <v>5.0313548365215613e-06</v>
       </c>
       <c r="J3">
-        <v>-6.1481107264909062e-07</v>
+        <v>-4.5307554241174784e-06</v>
       </c>
       <c r="K3">
-        <v>-2.3805408801780891e-06</v>
+        <v>-3.0609639437874859e-06</v>
       </c>
       <c r="L3">
-        <v>-8.6606786674804546e-07</v>
+        <v>-6.4280215891314599e-07</v>
       </c>
       <c r="M3">
-        <v>-2.7555205775670662e-07</v>
+        <v>1.6638624846267825e-06</v>
       </c>
       <c r="N3">
-        <v>8.1266654860760729e-08</v>
+        <v>1.6105749166989508e-06</v>
       </c>
       <c r="O3">
-        <v>1.3278797462765355e-07</v>
+        <v>4.7435608756717042e-06</v>
       </c>
       <c r="P3">
-        <v>1.1797481650982711e-07</v>
+        <v>-2.2758995772888545e-06</v>
       </c>
       <c r="Q3">
-        <v>-2.1407780739264993e-05</v>
+        <v>-2.4673197894813532e-05</v>
       </c>
       <c r="R3">
-        <v>-2.9710612782519373e-05</v>
+        <v>-3.6716647217242154e-05</v>
       </c>
       <c r="S3">
-        <v>-2.1951774781963339e-05</v>
+        <v>-2.7617825972556318e-05</v>
       </c>
       <c r="T3">
-        <v>3.8033274340980888e-05</v>
+        <v>5.5278619335626046e-05</v>
       </c>
       <c r="U3">
-        <v>-2.6751340245998614e-05</v>
+        <v>-2.9886890183150925e-05</v>
       </c>
       <c r="V3">
-        <v>-1.0460529573620136e-05</v>
+        <v>-4.4623759993101366e-06</v>
       </c>
       <c r="W3">
-        <v>1.0216310574711063e-05</v>
+        <v>8.9429306130692885e-06</v>
       </c>
       <c r="X3">
-        <v>2.6522687314115122e-05</v>
+        <v>3.4881524734780984e-05</v>
       </c>
       <c r="Y3">
-        <v>1.0112087376620995e-05</v>
+        <v>1.0546391990252503e-05</v>
       </c>
       <c r="Z3">
-        <v>1.156960100076414e-06</v>
+        <v>-3.5955745998582085e-07</v>
       </c>
       <c r="AA3">
-        <v>3.7377401114815629e-06</v>
+        <v>2.7308923763493925e-06</v>
       </c>
       <c r="AB3">
-        <v>4.6265665702065824e-06</v>
+        <v>2.697070694620193e-06</v>
       </c>
       <c r="AC3">
-        <v>3.9144467829741868e-06</v>
+        <v>3.3111745535957895e-06</v>
       </c>
       <c r="AD3">
-        <v>3.8214061891865504e-06</v>
+        <v>2.7098451452058439e-06</v>
       </c>
       <c r="AE3">
-        <v>-3.9748307806056623e-06</v>
+        <v>-3.7182472273433852e-06</v>
       </c>
       <c r="AF3">
-        <v>-1.0164325202820428e-07</v>
+        <v>-1.0517234437267577e-07</v>
       </c>
       <c r="AG3">
-        <v>-0.00027447695095998183</v>
+        <v>6.7792657439162902e-07</v>
+      </c>
+      <c r="AH3">
+        <v>-2.1025786509196349e-06</v>
+      </c>
+      <c r="AI3">
+        <v>-0.00037727989086930693</v>
       </c>
     </row>
     <row r="4">
@@ -4316,100 +4758,106 @@
         <v>19</v>
       </c>
       <c r="B4">
-        <v>-7.1609550370957872e-05</v>
+        <v>-0.00013172557719345085</v>
       </c>
       <c r="C4">
-        <v>2.5907712733071444e-08</v>
+        <v>3.3006838742514826e-08</v>
       </c>
       <c r="D4">
-        <v>-1.0212374728358824e-07</v>
+        <v>-1.4363105323651625e-07</v>
       </c>
       <c r="E4">
-        <v>9.3019968586059136e-10</v>
+        <v>1.329093588220942e-09</v>
       </c>
       <c r="F4">
-        <v>5.2774573006136682e-08</v>
+        <v>1.3257966234866214e-07</v>
       </c>
       <c r="G4">
-        <v>4.9637533590616021e-08</v>
+        <v>1.1876124015754986e-07</v>
       </c>
       <c r="H4">
-        <v>1.0129699688830441e-07</v>
+        <v>1.6483488710737124e-07</v>
       </c>
       <c r="I4">
-        <v>-2.2084939021040794e-08</v>
+        <v>3.1801700551144731e-08</v>
       </c>
       <c r="J4">
-        <v>4.1122901093325748e-09</v>
+        <v>3.9366403143661224e-08</v>
       </c>
       <c r="K4">
-        <v>5.3157982944807594e-09</v>
+        <v>6.937684904624332e-09</v>
       </c>
       <c r="L4">
-        <v>9.5353104650458061e-09</v>
+        <v>8.3378763345040892e-09</v>
       </c>
       <c r="M4">
-        <v>1.8071073194478636e-09</v>
+        <v>-2.1655739911599938e-08</v>
       </c>
       <c r="N4">
-        <v>-1.5654567780587191e-08</v>
+        <v>-3.5207519034754194e-08</v>
       </c>
       <c r="O4">
-        <v>8.3366516590246226e-10</v>
+        <v>-3.8195828957995975e-08</v>
       </c>
       <c r="P4">
-        <v>-8.7617767856733949e-10</v>
+        <v>2.457048710279807e-08</v>
       </c>
       <c r="Q4">
-        <v>1.4119886020460961e-07</v>
+        <v>1.5643170299260902e-07</v>
       </c>
       <c r="R4">
-        <v>2.3314111540483845e-07</v>
+        <v>2.9063490963525747e-07</v>
       </c>
       <c r="S4">
-        <v>1.8096306399121193e-07</v>
+        <v>2.294840276284424e-07</v>
       </c>
       <c r="T4">
-        <v>-3.6361981013645856e-07</v>
+        <v>-5.2139548909216559e-07</v>
       </c>
       <c r="U4">
-        <v>1.0661295843582858e-07</v>
+        <v>1.0555085868033711e-07</v>
       </c>
       <c r="V4">
-        <v>-1.6168915785791999e-07</v>
+        <v>-2.9672922183350712e-07</v>
       </c>
       <c r="W4">
-        <v>-4.7657272907616299e-08</v>
+        <v>-2.5885828971758204e-08</v>
       </c>
       <c r="X4">
-        <v>-2.0691183931877857e-07</v>
+        <v>-2.8117749342473678e-07</v>
       </c>
       <c r="Y4">
-        <v>-3.8040347883048606e-08</v>
+        <v>-1.9302764471890355e-08</v>
       </c>
       <c r="Z4">
-        <v>-3.7501710989713656e-08</v>
+        <v>-5.5699364489547746e-09</v>
       </c>
       <c r="AA4">
-        <v>-6.8936656713701994e-08</v>
+        <v>-4.0956090897983854e-08</v>
       </c>
       <c r="AB4">
-        <v>-7.5057046272668922e-08</v>
+        <v>-4.0279910068181208e-08</v>
       </c>
       <c r="AC4">
-        <v>-6.8818484765936329e-08</v>
+        <v>-4.6066599677972516e-08</v>
       </c>
       <c r="AD4">
-        <v>-6.2548400488715465e-08</v>
+        <v>-3.3901780022848824e-08</v>
       </c>
       <c r="AE4">
-        <v>-1.9607169780295065e-10</v>
+        <v>1.8326230847159117e-08</v>
       </c>
       <c r="AF4">
-        <v>-6.9834347979371075e-10</v>
+        <v>-7.9769449682427677e-10</v>
       </c>
       <c r="AG4">
-        <v>2.3688879857051789e-06</v>
+        <v>-2.0616752399827562e-08</v>
+      </c>
+      <c r="AH4">
+        <v>9.7628222075587755e-09</v>
+      </c>
+      <c r="AI4">
+        <v>3.2579248682791623e-06</v>
       </c>
     </row>
     <row r="5">
@@ -4417,100 +4865,106 @@
         <v>21</v>
       </c>
       <c r="B5">
-        <v>0.014957040159856867</v>
+        <v>0.035394831601462694</v>
       </c>
       <c r="C5">
-        <v>1.6182934861110855e-05</v>
+        <v>2.3502177242822334e-05</v>
       </c>
       <c r="D5">
-        <v>-4.6992045521010335e-06</v>
+        <v>-1.112691849875408e-05</v>
       </c>
       <c r="E5">
-        <v>5.2774573006136682e-08</v>
+        <v>1.3257966234866214e-07</v>
       </c>
       <c r="F5">
-        <v>0.0032503569473464325</v>
+        <v>0.0043205698248378628</v>
       </c>
       <c r="G5">
-        <v>0.0024858624394528467</v>
+        <v>0.003331974742639575</v>
       </c>
       <c r="H5">
-        <v>0.0024981933059437566</v>
+        <v>0.0033508516809490014</v>
       </c>
       <c r="I5">
-        <v>0.0024902366818681408</v>
+        <v>0.0033348456927829056</v>
       </c>
       <c r="J5">
-        <v>9.5626898841416359e-06</v>
+        <v>5.4545645044529537e-06</v>
       </c>
       <c r="K5">
-        <v>1.3152490895937884e-05</v>
+        <v>1.9796338654559292e-05</v>
       </c>
       <c r="L5">
-        <v>-4.1695182500271283e-06</v>
+        <v>-5.7405188505130732e-06</v>
       </c>
       <c r="M5">
-        <v>-1.6138216965445515e-05</v>
+        <v>-6.8646367053233843e-05</v>
       </c>
       <c r="N5">
-        <v>-1.6269787054758731e-05</v>
+        <v>-2.2211741921381923e-05</v>
       </c>
       <c r="O5">
-        <v>-9.8142529099163418e-06</v>
+        <v>-2.542835841340494e-06</v>
       </c>
       <c r="P5">
-        <v>1.5416105629659563e-05</v>
+        <v>6.2499291838728137e-05</v>
       </c>
       <c r="Q5">
-        <v>-1.1249784006980932e-05</v>
+        <v>3.4178594085720882e-05</v>
       </c>
       <c r="R5">
-        <v>3.0418839046161047e-05</v>
+        <v>9.2978855768374204e-05</v>
       </c>
       <c r="S5">
-        <v>1.7181464922683912e-05</v>
+        <v>7.2527720131985041e-05</v>
       </c>
       <c r="T5">
-        <v>7.4266916942861833e-05</v>
+        <v>0.0001052124654547246</v>
       </c>
       <c r="U5">
-        <v>8.8792500542317961e-05</v>
+        <v>0.00013217582648960798</v>
       </c>
       <c r="V5">
-        <v>4.6188856845626094e-05</v>
+        <v>3.4050800023753395e-05</v>
       </c>
       <c r="W5">
-        <v>-2.2435390006407253e-05</v>
+        <v>2.3762492316839416e-06</v>
       </c>
       <c r="X5">
-        <v>-3.2441540281280242e-05</v>
+        <v>-1.119198441620786e-05</v>
       </c>
       <c r="Y5">
-        <v>3.1618796387728734e-05</v>
+        <v>5.7622309281317365e-05</v>
       </c>
       <c r="Z5">
-        <v>-5.0134462642295857e-05</v>
+        <v>-5.5970222525287064e-05</v>
       </c>
       <c r="AA5">
-        <v>-3.5659616485143918e-05</v>
+        <v>-3.256235592747638e-05</v>
       </c>
       <c r="AB5">
-        <v>-3.9655761580559994e-05</v>
+        <v>-4.3692492921836609e-05</v>
       </c>
       <c r="AC5">
-        <v>-7.446299160707116e-05</v>
+        <v>-9.425875026856283e-05</v>
       </c>
       <c r="AD5">
-        <v>1.3809560856642422e-06</v>
+        <v>1.0258616395554358e-05</v>
       </c>
       <c r="AE5">
-        <v>-1.5600412780258758e-05</v>
+        <v>-5.2922973063558609e-06</v>
       </c>
       <c r="AF5">
-        <v>-1.4390174210012711e-07</v>
+        <v>-2.1242813873393685e-06</v>
       </c>
       <c r="AG5">
-        <v>-0.0024249514036422341</v>
+        <v>1.3254611324652228e-05</v>
+      </c>
+      <c r="AH5">
+        <v>-8.3220067583281154e-07</v>
+      </c>
+      <c r="AI5">
+        <v>-0.0031909959915158394</v>
       </c>
     </row>
     <row r="6">
@@ -4518,100 +4972,106 @@
         <v>22</v>
       </c>
       <c r="B6">
-        <v>0.022640611421299608</v>
+        <v>0.075078818242933027</v>
       </c>
       <c r="C6">
-        <v>-1.5298460107365573e-05</v>
+        <v>-2.1957961697634844e-05</v>
       </c>
       <c r="D6">
-        <v>-4.7609444038821897e-06</v>
+        <v>-1.049610769144287e-05</v>
       </c>
       <c r="E6">
-        <v>4.9637533590616021e-08</v>
+        <v>1.1876124015754986e-07</v>
       </c>
       <c r="F6">
-        <v>0.0024858624394528467</v>
+        <v>0.003331974742639575</v>
       </c>
       <c r="G6">
-        <v>0.0027552631783213091</v>
+        <v>0.0036920244587947296</v>
       </c>
       <c r="H6">
-        <v>0.0025610166528776232</v>
+        <v>0.0034464926035572812</v>
       </c>
       <c r="I6">
-        <v>0.0025647591301565321</v>
+        <v>0.0034460096641565387</v>
       </c>
       <c r="J6">
-        <v>-7.9474593351957579e-06</v>
+        <v>-3.8075677654614542e-05</v>
       </c>
       <c r="K6">
-        <v>1.2494003102702088e-05</v>
+        <v>1.6986230532526804e-05</v>
       </c>
       <c r="L6">
-        <v>-4.2522590666086596e-06</v>
+        <v>-6.3799710366713535e-06</v>
       </c>
       <c r="M6">
-        <v>4.7714268274553096e-08</v>
+        <v>-2.4006494258163938e-05</v>
       </c>
       <c r="N6">
-        <v>9.601122841489129e-06</v>
+        <v>1.2710445295975419e-05</v>
       </c>
       <c r="O6">
-        <v>4.8722524336313475e-06</v>
+        <v>2.7578659373188319e-05</v>
       </c>
       <c r="P6">
-        <v>1.6045205627177083e-06</v>
+        <v>3.0300963965835246e-05</v>
       </c>
       <c r="Q6">
-        <v>4.9168630931017109e-05</v>
+        <v>0.00011240303205274291</v>
       </c>
       <c r="R6">
-        <v>3.9121108881171041e-05</v>
+        <v>0.00010714980149372465</v>
       </c>
       <c r="S6">
-        <v>4.5106865196108386e-05</v>
+        <v>0.00010556458696630135</v>
       </c>
       <c r="T6">
-        <v>6.2197105422482322e-05</v>
+        <v>7.074332874305346e-05</v>
       </c>
       <c r="U6">
-        <v>0.000101760397985971</v>
+        <v>0.0001212270011351161</v>
       </c>
       <c r="V6">
-        <v>8.7680816693028012e-05</v>
+        <v>7.4130549102363239e-05</v>
       </c>
       <c r="W6">
-        <v>7.5493809545012125e-06</v>
+        <v>2.933742301836893e-05</v>
       </c>
       <c r="X6">
-        <v>1.0432826523100718e-05</v>
+        <v>3.5010963706506772e-05</v>
       </c>
       <c r="Y6">
-        <v>8.1664137176609653e-05</v>
+        <v>0.00011082359073710498</v>
       </c>
       <c r="Z6">
-        <v>-2.5102434169491962e-05</v>
+        <v>-3.2237887984472476e-05</v>
       </c>
       <c r="AA6">
-        <v>-2.7779003373911088e-05</v>
+        <v>-3.3365374743733918e-05</v>
       </c>
       <c r="AB6">
-        <v>-2.4704014749193145e-05</v>
+        <v>-3.4721204415569468e-05</v>
       </c>
       <c r="AC6">
-        <v>-7.2821221714079645e-05</v>
+        <v>-9.5267496664021333e-05</v>
       </c>
       <c r="AD6">
-        <v>-1.4506514775377449e-05</v>
+        <v>-3.6770110894328648e-07</v>
       </c>
       <c r="AE6">
-        <v>-4.9130978743581392e-06</v>
+        <v>1.7840588211187744e-06</v>
       </c>
       <c r="AF6">
-        <v>-1.9204040409130673e-06</v>
+        <v>-4.9769320234327978e-06</v>
       </c>
       <c r="AG6">
-        <v>-0.0024963187450407738</v>
+        <v>2.3653988487843877e-05</v>
+      </c>
+      <c r="AH6">
+        <v>5.0810295743719102e-05</v>
+      </c>
+      <c r="AI6">
+        <v>-0.003270466191866302</v>
       </c>
     </row>
     <row r="7">
@@ -4619,302 +5079,320 @@
         <v>23</v>
       </c>
       <c r="B7">
-        <v>0.039952871423114392</v>
+        <v>0.09944830669733494</v>
       </c>
       <c r="C7">
-        <v>-4.2808229553902553e-06</v>
+        <v>-1.4483117365472833e-05</v>
       </c>
       <c r="D7">
-        <v>-7.9329939238223531e-06</v>
+        <v>-1.2277270060586291e-05</v>
       </c>
       <c r="E7">
-        <v>1.0129699688830441e-07</v>
+        <v>1.6483488710737124e-07</v>
       </c>
       <c r="F7">
-        <v>0.0024981933059437566</v>
+        <v>0.0033508516809490014</v>
       </c>
       <c r="G7">
-        <v>0.0025610166528776232</v>
+        <v>0.0034464926035572812</v>
       </c>
       <c r="H7">
-        <v>0.0027185615057805481</v>
+        <v>0.0036653828547718171</v>
       </c>
       <c r="I7">
-        <v>0.0026524611622677679</v>
+        <v>0.0035791111171026052</v>
       </c>
       <c r="J7">
-        <v>-1.6101206548960472e-05</v>
+        <v>-4.4592238851128528e-05</v>
       </c>
       <c r="K7">
-        <v>6.8715091231081563e-06</v>
+        <v>1.3464568744444205e-05</v>
       </c>
       <c r="L7">
-        <v>-2.4508328212608259e-06</v>
+        <v>-4.661062151143344e-06</v>
       </c>
       <c r="M7">
-        <v>7.4801339880340226e-06</v>
+        <v>-5.4427010099697242e-06</v>
       </c>
       <c r="N7">
-        <v>5.3468363539406244e-06</v>
+        <v>1.7016537144485373e-05</v>
       </c>
       <c r="O7">
-        <v>2.1096058993988801e-05</v>
+        <v>5.8140799589011683e-05</v>
       </c>
       <c r="P7">
-        <v>-1.0385885076641036e-05</v>
+        <v>-6.9123038476550216e-06</v>
       </c>
       <c r="Q7">
-        <v>7.3815426198823707e-05</v>
+        <v>0.00012205513947016397</v>
       </c>
       <c r="R7">
-        <v>4.8715742661558075e-05</v>
+        <v>9.5082755675074404e-05</v>
       </c>
       <c r="S7">
-        <v>4.0443525073821044e-05</v>
+        <v>7.4378963457746687e-05</v>
       </c>
       <c r="T7">
-        <v>1.8095212749575859e-05</v>
+        <v>6.3200722583111636e-05</v>
       </c>
       <c r="U7">
-        <v>0.00010180836593608428</v>
+        <v>0.0001504576395539274</v>
       </c>
       <c r="V7">
-        <v>4.3515158044219685e-05</v>
+        <v>6.15511025975745e-05</v>
       </c>
       <c r="W7">
-        <v>-9.1081904446003515e-06</v>
+        <v>1.1349132512395238e-05</v>
       </c>
       <c r="X7">
-        <v>7.7039305647939134e-06</v>
+        <v>2.826723158468286e-05</v>
       </c>
       <c r="Y7">
-        <v>0.00010051261800222392</v>
+        <v>0.00014103812543211003</v>
       </c>
       <c r="Z7">
-        <v>-7.3997089550669956e-05</v>
+        <v>-7.1696895795612167e-05</v>
       </c>
       <c r="AA7">
-        <v>-8.9198778641227635e-05</v>
+        <v>-8.9513114637770463e-05</v>
       </c>
       <c r="AB7">
-        <v>-8.7012589759390331e-05</v>
+        <v>-9.6464399529598956e-05</v>
       </c>
       <c r="AC7">
-        <v>-0.0001299171678492226</v>
+        <v>-0.00014677624567278631</v>
       </c>
       <c r="AD7">
-        <v>-6.1442403194493837e-05</v>
+        <v>-5.7995603966465303e-05</v>
       </c>
       <c r="AE7">
-        <v>-4.4432150647458278e-05</v>
+        <v>-4.1755144483655708e-05</v>
       </c>
       <c r="AF7">
-        <v>-1.8707608751687319e-06</v>
+        <v>-3.812822218944009e-06</v>
       </c>
       <c r="AG7">
-        <v>-0.0024842963424730052</v>
+        <v>-9.4182418717767002e-07</v>
+      </c>
+      <c r="AH7">
+        <v>1.1790754280966483e-05</v>
+      </c>
+      <c r="AI7">
+        <v>-0.003381134787782597</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B8">
-        <v>0.041356645977558108</v>
+        <v>0.10173563395839548</v>
       </c>
       <c r="C8">
-        <v>-4.625680081441417e-05</v>
+        <v>-6.721971269187937e-05</v>
       </c>
       <c r="D8">
-        <v>8.1183592218770902e-06</v>
+        <v>5.0313548365215613e-06</v>
       </c>
       <c r="E8">
-        <v>-2.2084939021040794e-08</v>
+        <v>3.1801700551144731e-08</v>
       </c>
       <c r="F8">
-        <v>0.0024902366818681408</v>
+        <v>0.0033348456927829056</v>
       </c>
       <c r="G8">
-        <v>0.0025647591301565321</v>
+        <v>0.0034460096641565387</v>
       </c>
       <c r="H8">
-        <v>0.0026524611622677679</v>
+        <v>0.0035791111171026052</v>
       </c>
       <c r="I8">
-        <v>0.0031002817989955996</v>
+        <v>0.0041393192982061922</v>
       </c>
       <c r="J8">
-        <v>-4.1798859174149152e-05</v>
+        <v>-0.00015800051402928067</v>
       </c>
       <c r="K8">
-        <v>1.7038615665442437e-06</v>
+        <v>6.5553985238626469e-06</v>
       </c>
       <c r="L8">
-        <v>-1.0334265039564832e-05</v>
+        <v>-1.7084432362418025e-05</v>
       </c>
       <c r="M8">
-        <v>2.3447892628289651e-05</v>
+        <v>8.2796029395649866e-05</v>
       </c>
       <c r="N8">
-        <v>4.1048973395538615e-05</v>
+        <v>6.0961084983034175e-05</v>
       </c>
       <c r="O8">
-        <v>3.9245238564457829e-05</v>
+        <v>0.00019340393619652913</v>
       </c>
       <c r="P8">
-        <v>-2.3651249507488585e-05</v>
+        <v>-0.00010385536595319497</v>
       </c>
       <c r="Q8">
-        <v>0.0001408563208576412</v>
+        <v>0.00022570642505646658</v>
       </c>
       <c r="R8">
-        <v>0.00013397533207149329</v>
+        <v>0.00022836685530649645</v>
       </c>
       <c r="S8">
-        <v>7.3717243789573218e-05</v>
+        <v>0.0001324128404685404</v>
       </c>
       <c r="T8">
-        <v>-7.7953591892699747e-05</v>
+        <v>-0.00012814723418749568</v>
       </c>
       <c r="U8">
-        <v>-4.5988627532732654e-05</v>
+        <v>-5.159543964531753e-05</v>
       </c>
       <c r="V8">
-        <v>-8.2820324649471311e-05</v>
+        <v>-0.00011983592278242523</v>
       </c>
       <c r="W8">
-        <v>-1.0276551325011395e-05</v>
+        <v>-1.2675792881725387e-07</v>
       </c>
       <c r="X8">
-        <v>4.7409652537944678e-05</v>
+        <v>7.4293942289223444e-05</v>
       </c>
       <c r="Y8">
-        <v>0.00010989618229234458</v>
+        <v>0.00013772907671989266</v>
       </c>
       <c r="Z8">
-        <v>1.4588222487678729e-05</v>
+        <v>-5.7447948003091359e-06</v>
       </c>
       <c r="AA8">
-        <v>-2.7344143241462854e-05</v>
+        <v>-5.5462795353136696e-05</v>
       </c>
       <c r="AB8">
-        <v>-3.5443741443949334e-05</v>
+        <v>-7.5872728060489116e-05</v>
       </c>
       <c r="AC8">
-        <v>-5.0452409494885792e-05</v>
+        <v>-9.1320964737238216e-05</v>
       </c>
       <c r="AD8">
-        <v>5.679111209082083e-05</v>
+        <v>4.7570217411091985e-05</v>
       </c>
       <c r="AE8">
-        <v>1.0067916064749119e-05</v>
+        <v>-1.0998181087716835e-05</v>
       </c>
       <c r="AF8">
-        <v>2.3481140046250883e-06</v>
+        <v>-1.5225029826202927e-06</v>
       </c>
       <c r="AG8">
-        <v>-0.0030329053243088669</v>
+        <v>0.00017677745986703283</v>
+      </c>
+      <c r="AH8">
+        <v>6.4729527955960983e-05</v>
+      </c>
+      <c r="AI8">
+        <v>-0.0039087046616684516</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B9">
-        <v>0.62539999132686031</v>
+        <v>1.5183111231000272</v>
       </c>
       <c r="C9">
-        <v>7.673705623548462e-06</v>
+        <v>4.1213408368018641e-05</v>
       </c>
       <c r="D9">
-        <v>-6.1481107264909062e-07</v>
+        <v>-4.5307554241174784e-06</v>
       </c>
       <c r="E9">
-        <v>4.1122901093325748e-09</v>
+        <v>3.9366403143661224e-08</v>
       </c>
       <c r="F9">
-        <v>9.5626898841416359e-06</v>
+        <v>5.4545645044529537e-06</v>
       </c>
       <c r="G9">
-        <v>-7.9474593351957579e-06</v>
+        <v>-3.8075677654614542e-05</v>
       </c>
       <c r="H9">
-        <v>-1.6101206548960472e-05</v>
+        <v>-4.4592238851128528e-05</v>
       </c>
       <c r="I9">
-        <v>-4.1798859174149152e-05</v>
+        <v>-0.00015800051402928067</v>
       </c>
       <c r="J9">
-        <v>7.6929278623924193e-05</v>
+        <v>0.00064210866217899898</v>
       </c>
       <c r="K9">
-        <v>-2.932310522463555e-06</v>
+        <v>-2.2350172380330125e-05</v>
       </c>
       <c r="L9">
-        <v>-1.008236735213733e-06</v>
+        <v>7.4984738807742944e-06</v>
       </c>
       <c r="M9">
-        <v>-6.4742447803613077e-05</v>
+        <v>-0.00045996963522548811</v>
       </c>
       <c r="N9">
-        <v>-3.225826560839141e-06</v>
+        <v>-2.2946718541055334e-05</v>
       </c>
       <c r="O9">
-        <v>-7.5867268212224915e-05</v>
+        <v>-0.00063948629735780839</v>
       </c>
       <c r="P9">
-        <v>6.3154889599536246e-05</v>
+        <v>0.00044001378139978126</v>
       </c>
       <c r="Q9">
-        <v>-4.6086554464684485e-05</v>
+        <v>-0.00028142695421273859</v>
       </c>
       <c r="R9">
-        <v>-4.5781852662590803e-05</v>
+        <v>-0.00028114959275801315</v>
       </c>
       <c r="S9">
-        <v>-4.4132819116729377e-05</v>
+        <v>-0.00024195772820361438</v>
       </c>
       <c r="T9">
-        <v>-1.6236028211765117e-05</v>
+        <v>-5.427711514046656e-05</v>
       </c>
       <c r="U9">
-        <v>-2.9049290787453615e-05</v>
+        <v>-8.684763448134892e-05</v>
       </c>
       <c r="V9">
-        <v>-2.9113971377562904e-05</v>
+        <v>-0.00011456626608425207</v>
       </c>
       <c r="W9">
-        <v>3.9206455833612448e-07</v>
+        <v>1.8842634774256128e-05</v>
       </c>
       <c r="X9">
-        <v>-1.8946519835451321e-05</v>
+        <v>-6.1086821669755975e-05</v>
       </c>
       <c r="Y9">
-        <v>-2.4925453487590297e-05</v>
+        <v>-6.0210898848725486e-05</v>
       </c>
       <c r="Z9">
-        <v>7.113626159366366e-06</v>
+        <v>8.5311790844845093e-06</v>
       </c>
       <c r="AA9">
-        <v>6.5266818568562961e-06</v>
+        <v>7.6920219427976225e-06</v>
       </c>
       <c r="AB9">
-        <v>1.6847673087838663e-06</v>
+        <v>-1.024119070579583e-05</v>
       </c>
       <c r="AC9">
-        <v>7.3527247910234905e-06</v>
+        <v>9.4274848582951993e-06</v>
       </c>
       <c r="AD9">
-        <v>-1.043391205122893e-05</v>
+        <v>-7.4113146721242862e-05</v>
       </c>
       <c r="AE9">
-        <v>7.9098447125638991e-06</v>
+        <v>-3.34843595512793e-06</v>
       </c>
       <c r="AF9">
-        <v>-1.5370353053766594e-06</v>
+        <v>-1.2766501460807108e-06</v>
       </c>
       <c r="AG9">
-        <v>0.00010027052921489057</v>
+        <v>-0.00016867270152082627</v>
+      </c>
+      <c r="AH9">
+        <v>-8.3141777482098215e-05</v>
+      </c>
+      <c r="AI9">
+        <v>0.00037117144109132753</v>
       </c>
     </row>
     <row r="10">
@@ -4922,100 +5400,106 @@
         <v>25</v>
       </c>
       <c r="B10">
-        <v>0.022697258873002099</v>
+        <v>0.019507095327876152</v>
       </c>
       <c r="C10">
-        <v>-1.5474481394921801e-05</v>
+        <v>-2.226764468905269e-05</v>
       </c>
       <c r="D10">
-        <v>-2.3805408801780891e-06</v>
+        <v>-3.0609639437874859e-06</v>
       </c>
       <c r="E10">
-        <v>5.3157982944807594e-09</v>
+        <v>6.937684904624332e-09</v>
       </c>
       <c r="F10">
-        <v>1.3152490895937884e-05</v>
+        <v>1.9796338654559292e-05</v>
       </c>
       <c r="G10">
-        <v>1.2494003102702088e-05</v>
+        <v>1.6986230532526804e-05</v>
       </c>
       <c r="H10">
-        <v>6.8715091231081563e-06</v>
+        <v>1.3464568744444205e-05</v>
       </c>
       <c r="I10">
-        <v>1.7038615665442437e-06</v>
+        <v>6.5553985238626469e-06</v>
       </c>
       <c r="J10">
-        <v>-2.932310522463555e-06</v>
+        <v>-2.2350172380330125e-05</v>
       </c>
       <c r="K10">
-        <v>0.00025070925440420961</v>
+        <v>0.00032887685903156271</v>
       </c>
       <c r="L10">
-        <v>-2.0030502121559094e-05</v>
+        <v>-2.4770403754243677e-05</v>
       </c>
       <c r="M10">
-        <v>-7.5187747691578787e-07</v>
+        <v>9.7229906533740165e-06</v>
       </c>
       <c r="N10">
-        <v>1.3760451635539978e-05</v>
+        <v>1.9103405061938144e-05</v>
       </c>
       <c r="O10">
-        <v>3.1596256065994852e-06</v>
+        <v>2.2991581508446522e-05</v>
       </c>
       <c r="P10">
-        <v>6.7808597837643253e-07</v>
+        <v>-8.8130101792035479e-06</v>
       </c>
       <c r="Q10">
-        <v>8.9025031551175473e-05</v>
+        <v>0.00011345800635159751</v>
       </c>
       <c r="R10">
-        <v>6.4639160226439662e-05</v>
+        <v>8.5593527860833296e-05</v>
       </c>
       <c r="S10">
-        <v>1.0556010034055508e-05</v>
+        <v>1.4060996713626765e-05</v>
       </c>
       <c r="T10">
-        <v>0.0018605517103708583</v>
+        <v>0.0024487103081431687</v>
       </c>
       <c r="U10">
-        <v>0.0018954827188694323</v>
+        <v>0.0024932705477126752</v>
       </c>
       <c r="V10">
-        <v>0.0019154924101912867</v>
+        <v>0.0025184652257739613</v>
       </c>
       <c r="W10">
-        <v>-2.0060586050050185e-05</v>
+        <v>-2.956393193700654e-05</v>
       </c>
       <c r="X10">
-        <v>6.3031171327357317e-06</v>
+        <v>1.522582992835868e-06</v>
       </c>
       <c r="Y10">
-        <v>5.3595193619314949e-05</v>
+        <v>4.4895728899750978e-05</v>
       </c>
       <c r="Z10">
-        <v>2.0529081635585478e-05</v>
+        <v>9.5288826796151305e-06</v>
       </c>
       <c r="AA10">
-        <v>2.8023596746982191e-06</v>
+        <v>-1.9570131783865075e-05</v>
       </c>
       <c r="AB10">
-        <v>-2.9381163177773142e-06</v>
+        <v>-2.6616656722436446e-05</v>
       </c>
       <c r="AC10">
-        <v>2.1275909058952858e-05</v>
+        <v>8.045076416849338e-06</v>
       </c>
       <c r="AD10">
-        <v>3.6484657821675859e-06</v>
+        <v>-1.6211091124791006e-05</v>
       </c>
       <c r="AE10">
-        <v>1.2841854113162447e-05</v>
+        <v>1.2277340705570843e-05</v>
       </c>
       <c r="AF10">
-        <v>1.114564633412457e-06</v>
+        <v>7.6871471711810675e-07</v>
       </c>
       <c r="AG10">
-        <v>-0.0018496775650005404</v>
+        <v>1.6656694351073042e-05</v>
+      </c>
+      <c r="AH10">
+        <v>3.2264897530520989e-05</v>
+      </c>
+      <c r="AI10">
+        <v>-0.002408534962640044</v>
       </c>
     </row>
     <row r="11">
@@ -5023,201 +5507,213 @@
         <v>26</v>
       </c>
       <c r="B11">
-        <v>0.0072378692847669835</v>
+        <v>0.0067365302942258513</v>
       </c>
       <c r="C11">
-        <v>-6.1491109097676031e-07</v>
+        <v>-5.8287437428686758e-07</v>
       </c>
       <c r="D11">
-        <v>-8.6606786674804546e-07</v>
+        <v>-6.4280215891314599e-07</v>
       </c>
       <c r="E11">
-        <v>9.5353104650458061e-09</v>
+        <v>8.3378763345040892e-09</v>
       </c>
       <c r="F11">
-        <v>-4.1695182500271283e-06</v>
+        <v>-5.7405188505130732e-06</v>
       </c>
       <c r="G11">
-        <v>-4.2522590666086596e-06</v>
+        <v>-6.3799710366713535e-06</v>
       </c>
       <c r="H11">
-        <v>-2.4508328212608259e-06</v>
+        <v>-4.661062151143344e-06</v>
       </c>
       <c r="I11">
-        <v>-1.0334265039564832e-05</v>
+        <v>-1.7084432362418025e-05</v>
       </c>
       <c r="J11">
-        <v>-1.008236735213733e-06</v>
+        <v>7.4984738807742944e-06</v>
       </c>
       <c r="K11">
-        <v>-2.0030502121559094e-05</v>
+        <v>-2.4770403754243677e-05</v>
       </c>
       <c r="L11">
-        <v>1.7300285242636376e-05</v>
+        <v>2.175116941829289e-05</v>
       </c>
       <c r="M11">
-        <v>1.9321673857553294e-06</v>
+        <v>-4.2656021039700153e-06</v>
       </c>
       <c r="N11">
-        <v>7.7830917832707825e-07</v>
+        <v>7.0522282635133661e-07</v>
       </c>
       <c r="O11">
-        <v>8.7532994417048158e-07</v>
+        <v>-8.5357450856608926e-06</v>
       </c>
       <c r="P11">
-        <v>-1.8309190480761078e-06</v>
+        <v>4.8322519843575747e-06</v>
       </c>
       <c r="Q11">
-        <v>-5.8565788806541657e-06</v>
+        <v>-9.1853752335519542e-06</v>
       </c>
       <c r="R11">
-        <v>-1.834383022346386e-05</v>
+        <v>-2.5537299756361466e-05</v>
       </c>
       <c r="S11">
-        <v>-6.7301486291642315e-06</v>
+        <v>-1.2851763871653474e-05</v>
       </c>
       <c r="T11">
-        <v>-4.1037722728565702e-05</v>
+        <v>-4.5785419642202534e-05</v>
       </c>
       <c r="U11">
-        <v>-4.866778028618133e-05</v>
+        <v>-6.2587876562417014e-05</v>
       </c>
       <c r="V11">
-        <v>-4.5567818225643035e-05</v>
+        <v>-5.4942421264625129e-05</v>
       </c>
       <c r="W11">
-        <v>1.4519148175705456e-07</v>
+        <v>3.9323988728646681e-07</v>
       </c>
       <c r="X11">
-        <v>3.3062321293020559e-06</v>
+        <v>2.8840996153256368e-06</v>
       </c>
       <c r="Y11">
-        <v>4.8908047596068295e-06</v>
+        <v>9.6987525820311322e-06</v>
       </c>
       <c r="Z11">
-        <v>-9.0823849218972318e-06</v>
+        <v>-6.0049578820980547e-06</v>
       </c>
       <c r="AA11">
-        <v>-1.1126898249002362e-05</v>
+        <v>-8.3258245848905986e-06</v>
       </c>
       <c r="AB11">
-        <v>-8.3157441435049803e-06</v>
+        <v>-4.5104831088476339e-06</v>
       </c>
       <c r="AC11">
-        <v>-9.9556821724918097e-06</v>
+        <v>-7.3148628605913319e-06</v>
       </c>
       <c r="AD11">
-        <v>-1.2031140510936847e-05</v>
+        <v>-1.1032005505418663e-05</v>
       </c>
       <c r="AE11">
-        <v>-8.7974991603492583e-06</v>
+        <v>-5.3927727825969897e-06</v>
       </c>
       <c r="AF11">
-        <v>-2.1870100858353579e-07</v>
+        <v>-2.8400275670942545e-07</v>
       </c>
       <c r="AG11">
-        <v>7.2099035883625066e-05</v>
+        <v>-4.7572744028242836e-06</v>
+      </c>
+      <c r="AH11">
+        <v>-7.4010554880799231e-06</v>
+      </c>
+      <c r="AI11">
+        <v>7.7037032292740965e-05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B12">
-        <v>0.23628660407834953</v>
+        <v>0.65327016067453847</v>
       </c>
       <c r="C12">
-        <v>-4.3113017440064528e-06</v>
+        <v>-3.1723494920810533e-05</v>
       </c>
       <c r="D12">
-        <v>-2.7555205775670662e-07</v>
+        <v>1.6638624846267825e-06</v>
       </c>
       <c r="E12">
-        <v>1.8071073194478636e-09</v>
+        <v>-2.1655739911599938e-08</v>
       </c>
       <c r="F12">
-        <v>-1.6138216965445515e-05</v>
+        <v>-6.8646367053233843e-05</v>
       </c>
       <c r="G12">
-        <v>4.7714268274553096e-08</v>
+        <v>-2.4006494258163938e-05</v>
       </c>
       <c r="H12">
-        <v>7.4801339880340226e-06</v>
+        <v>-5.4427010099697242e-06</v>
       </c>
       <c r="I12">
-        <v>2.3447892628289651e-05</v>
+        <v>8.2796029395649866e-05</v>
       </c>
       <c r="J12">
-        <v>-6.4742447803613077e-05</v>
+        <v>-0.00045996963522548811</v>
       </c>
       <c r="K12">
-        <v>-7.5187747691578787e-07</v>
+        <v>9.7229906533740165e-06</v>
       </c>
       <c r="L12">
-        <v>1.9321673857553294e-06</v>
+        <v>-4.2656021039700153e-06</v>
       </c>
       <c r="M12">
-        <v>7.4984025355989849e-05</v>
+        <v>0.00063890354726480261</v>
       </c>
       <c r="N12">
-        <v>-2.6015459680644409e-07</v>
+        <v>8.9759368205663441e-06</v>
       </c>
       <c r="O12">
-        <v>6.3510283491509341e-05</v>
+        <v>0.00045450976423457522</v>
       </c>
       <c r="P12">
-        <v>-7.2918983784428604e-05</v>
+        <v>-0.00061150762929524315</v>
       </c>
       <c r="Q12">
-        <v>-3.0778834246309142e-05</v>
+        <v>-0.00019879542569420361</v>
       </c>
       <c r="R12">
-        <v>-3.2382250607231259e-05</v>
+        <v>-0.00018439082620359744</v>
       </c>
       <c r="S12">
-        <v>-3.2442179673281772e-05</v>
+        <v>-0.0002258836783469497</v>
       </c>
       <c r="T12">
-        <v>-2.595979210691195e-06</v>
+        <v>-4.0859574182594242e-05</v>
       </c>
       <c r="U12">
-        <v>7.4391143985481646e-06</v>
+        <v>1.5597952882382601e-05</v>
       </c>
       <c r="V12">
-        <v>4.5135328584244114e-06</v>
+        <v>3.051233833794083e-05</v>
       </c>
       <c r="W12">
-        <v>-1.8141988435718015e-06</v>
+        <v>-1.8682077194645524e-05</v>
       </c>
       <c r="X12">
-        <v>1.0476244968268607e-05</v>
+        <v>3.8780828261938898e-05</v>
       </c>
       <c r="Y12">
-        <v>-3.1247008213823618e-05</v>
+        <v>-0.00018981797359741528</v>
       </c>
       <c r="Z12">
-        <v>-9.9475852460585566e-06</v>
+        <v>-5.2738991774779885e-05</v>
       </c>
       <c r="AA12">
-        <v>-1.4895073867319593e-05</v>
+        <v>-8.1565824726875994e-05</v>
       </c>
       <c r="AB12">
-        <v>-1.7391891510250446e-05</v>
+        <v>-7.4531000168357822e-05</v>
       </c>
       <c r="AC12">
-        <v>-1.2703353865582253e-05</v>
+        <v>-6.6399652958953561e-05</v>
       </c>
       <c r="AD12">
-        <v>-1.0578123565384703e-05</v>
+        <v>-5.2142528327796093e-05</v>
       </c>
       <c r="AE12">
-        <v>-1.2087935056753014e-05</v>
+        <v>-5.4684359378744815e-05</v>
       </c>
       <c r="AF12">
-        <v>1.4554320829353008e-06</v>
+        <v>4.5341083384152171e-06</v>
       </c>
       <c r="AG12">
-        <v>-3.1354179638707811e-05</v>
+        <v>7.9370531799451678e-05</v>
+      </c>
+      <c r="AH12">
+        <v>5.013149121636935e-05</v>
+      </c>
+      <c r="AI12">
+        <v>-0.00010796927102515791</v>
       </c>
     </row>
     <row r="13">
@@ -5225,302 +5721,320 @@
         <v>28</v>
       </c>
       <c r="B13">
-        <v>0.046344716958013572</v>
+        <v>0.076266537637629681</v>
       </c>
       <c r="C13">
-        <v>-0.00024019820742180766</v>
+        <v>-0.00032721101553160996</v>
       </c>
       <c r="D13">
-        <v>8.1266654860760729e-08</v>
+        <v>1.6105749166989508e-06</v>
       </c>
       <c r="E13">
-        <v>-1.5654567780587191e-08</v>
+        <v>-3.5207519034754194e-08</v>
       </c>
       <c r="F13">
-        <v>-1.6269787054758731e-05</v>
+        <v>-2.2211741921381923e-05</v>
       </c>
       <c r="G13">
-        <v>9.601122841489129e-06</v>
+        <v>1.2710445295975419e-05</v>
       </c>
       <c r="H13">
-        <v>5.3468363539406244e-06</v>
+        <v>1.7016537144485373e-05</v>
       </c>
       <c r="I13">
-        <v>4.1048973395538615e-05</v>
+        <v>6.0961084983034175e-05</v>
       </c>
       <c r="J13">
-        <v>-3.225826560839141e-06</v>
+        <v>-2.2946718541055334e-05</v>
       </c>
       <c r="K13">
-        <v>1.3760451635539978e-05</v>
+        <v>1.9103405061938144e-05</v>
       </c>
       <c r="L13">
-        <v>7.7830917832707825e-07</v>
+        <v>7.0522282635133661e-07</v>
       </c>
       <c r="M13">
-        <v>-2.6015459680644409e-07</v>
+        <v>8.9759368205663441e-06</v>
       </c>
       <c r="N13">
-        <v>0.0053985998612576863</v>
+        <v>0.0074391994945310841</v>
       </c>
       <c r="O13">
-        <v>-0.00012742007941077315</v>
+        <v>0.00012093042132118714</v>
       </c>
       <c r="P13">
-        <v>0.00023518842262033521</v>
+        <v>0.00057843243999440694</v>
       </c>
       <c r="Q13">
-        <v>0.0029959590540514056</v>
+        <v>0.0044503371439920062</v>
       </c>
       <c r="R13">
-        <v>0.0029882236154351108</v>
+        <v>0.0044446210162897761</v>
       </c>
       <c r="S13">
-        <v>0.0029673587473815844</v>
+        <v>0.0044155113288065658</v>
       </c>
       <c r="T13">
-        <v>0.00014003549456308986</v>
+        <v>0.0001269330852393532</v>
       </c>
       <c r="U13">
-        <v>2.6630746857018647e-05</v>
+        <v>4.2134927435865614e-05</v>
       </c>
       <c r="V13">
-        <v>0.00013667950602798754</v>
+        <v>0.00019110709000858057</v>
       </c>
       <c r="W13">
-        <v>-3.2582206665644444e-05</v>
+        <v>-4.1771402812106916e-05</v>
       </c>
       <c r="X13">
-        <v>-9.9831334759697271e-06</v>
+        <v>1.1926379245470742e-07</v>
       </c>
       <c r="Y13">
-        <v>-9.894796143190593e-05</v>
+        <v>-0.00012504007718881338</v>
       </c>
       <c r="Z13">
-        <v>0.00012443407783389133</v>
+        <v>6.3903171694334451e-05</v>
       </c>
       <c r="AA13">
-        <v>0.00016002541178001314</v>
+        <v>0.00011456175015991151</v>
       </c>
       <c r="AB13">
-        <v>0.00019690878900844965</v>
+        <v>0.00013430757200705204</v>
       </c>
       <c r="AC13">
-        <v>0.00014719297904257009</v>
+        <v>9.8039917483482919e-05</v>
       </c>
       <c r="AD13">
-        <v>0.00012940082653870814</v>
+        <v>7.1475371197587522e-05</v>
       </c>
       <c r="AE13">
-        <v>0.00018590963167223012</v>
+        <v>0.00012324085976339047</v>
       </c>
       <c r="AF13">
-        <v>6.7391443724539919e-07</v>
+        <v>-1.6854814070528881e-06</v>
       </c>
       <c r="AG13">
-        <v>-0.0030707085921171592</v>
+        <v>6.7198161181713026e-05</v>
+      </c>
+      <c r="AH13">
+        <v>3.4162190225686239e-05</v>
+      </c>
+      <c r="AI13">
+        <v>-0.004452135442681469</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B14">
-        <v>-0.022004001322487473</v>
+        <v>-0.13691387330468932</v>
       </c>
       <c r="C14">
-        <v>-1.0288408450762515e-05</v>
+        <v>-5.2190345536982111e-05</v>
       </c>
       <c r="D14">
-        <v>1.3278797462765355e-07</v>
+        <v>4.7435608756717042e-06</v>
       </c>
       <c r="E14">
-        <v>8.3366516590246226e-10</v>
+        <v>-3.8195828957995975e-08</v>
       </c>
       <c r="F14">
-        <v>-9.8142529099163418e-06</v>
+        <v>-2.542835841340494e-06</v>
       </c>
       <c r="G14">
-        <v>4.8722524336313475e-06</v>
+        <v>2.7578659373188319e-05</v>
       </c>
       <c r="H14">
-        <v>2.1096058993988801e-05</v>
+        <v>5.8140799589011683e-05</v>
       </c>
       <c r="I14">
-        <v>3.9245238564457829e-05</v>
+        <v>0.00019340393619652913</v>
       </c>
       <c r="J14">
-        <v>-7.5867268212224915e-05</v>
+        <v>-0.00063948629735780839</v>
       </c>
       <c r="K14">
-        <v>3.1596256065994852e-06</v>
+        <v>2.2991581508446522e-05</v>
       </c>
       <c r="L14">
-        <v>8.7532994417048158e-07</v>
+        <v>-8.5357450856608926e-06</v>
       </c>
       <c r="M14">
-        <v>6.3510283491509341e-05</v>
+        <v>0.00045450976423457522</v>
       </c>
       <c r="N14">
-        <v>-0.00012742007941077315</v>
+        <v>0.00012093042132118714</v>
       </c>
       <c r="O14">
-        <v>0.0012557026596516439</v>
+        <v>0.010574454106923811</v>
       </c>
       <c r="P14">
-        <v>-0.0010175137244134932</v>
+        <v>-0.0074843242081282972</v>
       </c>
       <c r="Q14">
-        <v>0.00071743148755479161</v>
+        <v>0.003772712901295393</v>
       </c>
       <c r="R14">
-        <v>0.00071803700257074021</v>
+        <v>0.0037718232656827151</v>
       </c>
       <c r="S14">
-        <v>0.00071796054298879414</v>
+        <v>0.0037332183932664458</v>
       </c>
       <c r="T14">
-        <v>2.3166075228149151e-05</v>
+        <v>6.3569120295488822e-05</v>
       </c>
       <c r="U14">
-        <v>2.7198761180284147e-05</v>
+        <v>7.7539521417399929e-05</v>
       </c>
       <c r="V14">
-        <v>2.8145886120179494e-05</v>
+        <v>0.00010938102572210823</v>
       </c>
       <c r="W14">
-        <v>-1.6648805997233284e-06</v>
+        <v>-2.182191783004425e-05</v>
       </c>
       <c r="X14">
-        <v>1.7857557763969738e-05</v>
+        <v>6.1591036288373402e-05</v>
       </c>
       <c r="Y14">
-        <v>2.592070187650388e-05</v>
+        <v>6.0157633434816129e-05</v>
       </c>
       <c r="Z14">
-        <v>-4.111867761025581e-05</v>
+        <v>-0.00011543975939217192</v>
       </c>
       <c r="AA14">
-        <v>-3.6374920994950376e-05</v>
+        <v>-9.5444848122407241e-05</v>
       </c>
       <c r="AB14">
-        <v>-3.755046210642095e-05</v>
+        <v>-9.9987714929009334e-05</v>
       </c>
       <c r="AC14">
-        <v>-4.480835318752699e-05</v>
+        <v>-0.00012832431907419813</v>
       </c>
       <c r="AD14">
-        <v>-3.7254365094515377e-05</v>
+        <v>-4.7235486771416541e-05</v>
       </c>
       <c r="AE14">
-        <v>-4.3357434046430605e-05</v>
+        <v>-9.5000747710684023e-05</v>
       </c>
       <c r="AF14">
-        <v>2.2138589919915682e-07</v>
+        <v>-2.9715070134869425e-06</v>
       </c>
       <c r="AG14">
-        <v>-0.00070074022067162707</v>
+        <v>0.0001750698952145773</v>
+      </c>
+      <c r="AH14">
+        <v>0.00022189868718456023</v>
+      </c>
+      <c r="AI14">
+        <v>-0.0037005242288102864</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B15">
-        <v>0.040890787183952212</v>
+        <v>0.042525396567240963</v>
       </c>
       <c r="C15">
-        <v>4.6918486669518108e-06</v>
+        <v>3.3053013638421755e-05</v>
       </c>
       <c r="D15">
-        <v>1.1797481650982711e-07</v>
+        <v>-2.2758995772888545e-06</v>
       </c>
       <c r="E15">
-        <v>-8.7617767856733949e-10</v>
+        <v>2.457048710279807e-08</v>
       </c>
       <c r="F15">
-        <v>1.5416105629659563e-05</v>
+        <v>6.2499291838728137e-05</v>
       </c>
       <c r="G15">
-        <v>1.6045205627177083e-06</v>
+        <v>3.0300963965835246e-05</v>
       </c>
       <c r="H15">
-        <v>-1.0385885076641036e-05</v>
+        <v>-6.9123038476550216e-06</v>
       </c>
       <c r="I15">
-        <v>-2.3651249507488585e-05</v>
+        <v>-0.00010385536595319497</v>
       </c>
       <c r="J15">
-        <v>6.3154889599536246e-05</v>
+        <v>0.00044001378139978126</v>
       </c>
       <c r="K15">
-        <v>6.7808597837643253e-07</v>
+        <v>-8.8130101792035479e-06</v>
       </c>
       <c r="L15">
-        <v>-1.8309190480761078e-06</v>
+        <v>4.8322519843575747e-06</v>
       </c>
       <c r="M15">
-        <v>-7.2918983784428604e-05</v>
+        <v>-0.00061150762929524315</v>
       </c>
       <c r="N15">
-        <v>0.00023518842262033521</v>
+        <v>0.00057843243999440694</v>
       </c>
       <c r="O15">
-        <v>-0.0010175137244134932</v>
+        <v>-0.0074843242081282972</v>
       </c>
       <c r="P15">
-        <v>0.0012270350749420797</v>
+        <v>0.0096880455925068675</v>
       </c>
       <c r="Q15">
-        <v>0.0010058804348796507</v>
+        <v>0.0034901810177060716</v>
       </c>
       <c r="R15">
-        <v>0.0010083390794696219</v>
+        <v>0.0034801524514338385</v>
       </c>
       <c r="S15">
-        <v>0.0010071662686694616</v>
+        <v>0.0035208298416822166</v>
       </c>
       <c r="T15">
-        <v>-2.2676424316012134e-05</v>
+        <v>-2.4394633965528793e-05</v>
       </c>
       <c r="U15">
-        <v>-7.1175939865589471e-06</v>
+        <v>-4.4100356099130694e-06</v>
       </c>
       <c r="V15">
-        <v>-4.649296344547279e-06</v>
+        <v>-1.8891590283882259e-05</v>
       </c>
       <c r="W15">
-        <v>1.6260607281493305e-06</v>
+        <v>1.8707009413747772e-05</v>
       </c>
       <c r="X15">
-        <v>-1.0304127086822201e-05</v>
+        <v>-3.9132342708521708e-05</v>
       </c>
       <c r="Y15">
-        <v>1.9935133595597968e-05</v>
+        <v>0.00015936702076296003</v>
       </c>
       <c r="Z15">
-        <v>3.0076837371328068e-05</v>
+        <v>8.6421126252416661e-05</v>
       </c>
       <c r="AA15">
-        <v>3.2413127683596731e-05</v>
+        <v>0.00010814157455045134</v>
       </c>
       <c r="AB15">
-        <v>3.6912521479181914e-05</v>
+        <v>8.854105528242098e-05</v>
       </c>
       <c r="AC15">
-        <v>3.3099817879172567e-05</v>
+        <v>0.00010920062210723416</v>
       </c>
       <c r="AD15">
-        <v>3.1536699458196743e-05</v>
+        <v>6.8460209244772773e-05</v>
       </c>
       <c r="AE15">
-        <v>2.8392876978894691e-05</v>
+        <v>5.8168987783405678e-05</v>
       </c>
       <c r="AF15">
-        <v>-1.6227347779727098e-06</v>
+        <v>-4.8550016487323321e-06</v>
       </c>
       <c r="AG15">
-        <v>-0.00095467605227211806</v>
+        <v>-4.5373912749079905e-05</v>
+      </c>
+      <c r="AH15">
+        <v>-0.00015097457733100018</v>
+      </c>
+      <c r="AI15">
+        <v>-0.0031854452860888309</v>
       </c>
     </row>
     <row r="16">
@@ -5528,100 +6042,106 @@
         <v>32</v>
       </c>
       <c r="B16">
-        <v>-0.03415828864287343</v>
+        <v>-0.27907468457175877</v>
       </c>
       <c r="C16">
-        <v>-0.00018588921021277688</v>
+        <v>-0.0002335383041085244</v>
       </c>
       <c r="D16">
-        <v>-2.1407780739264993e-05</v>
+        <v>-2.4673197894813532e-05</v>
       </c>
       <c r="E16">
-        <v>1.4119886020460961e-07</v>
+        <v>1.5643170299260902e-07</v>
       </c>
       <c r="F16">
-        <v>-1.1249784006980932e-05</v>
+        <v>3.4178594085720882e-05</v>
       </c>
       <c r="G16">
-        <v>4.9168630931017109e-05</v>
+        <v>0.00011240303205274291</v>
       </c>
       <c r="H16">
-        <v>7.3815426198823707e-05</v>
+        <v>0.00012205513947016397</v>
       </c>
       <c r="I16">
-        <v>0.0001408563208576412</v>
+        <v>0.00022570642505646658</v>
       </c>
       <c r="J16">
-        <v>-4.6086554464684485e-05</v>
+        <v>-0.00028142695421273859</v>
       </c>
       <c r="K16">
-        <v>8.9025031551175473e-05</v>
+        <v>0.00011345800635159751</v>
       </c>
       <c r="L16">
-        <v>-5.8565788806541657e-06</v>
+        <v>-9.1853752335519542e-06</v>
       </c>
       <c r="M16">
-        <v>-3.0778834246309142e-05</v>
+        <v>-0.00019879542569420361</v>
       </c>
       <c r="N16">
-        <v>0.0029959590540514056</v>
+        <v>0.0044503371439920062</v>
       </c>
       <c r="O16">
-        <v>0.00071743148755479161</v>
+        <v>0.003772712901295393</v>
       </c>
       <c r="P16">
-        <v>0.0010058804348796507</v>
+        <v>0.0034901810177060716</v>
       </c>
       <c r="Q16">
-        <v>0.011950211898996045</v>
+        <v>0.016758042712536586</v>
       </c>
       <c r="R16">
-        <v>0.011639968079113043</v>
+        <v>0.016323141568697592</v>
       </c>
       <c r="S16">
-        <v>0.011616885271847935</v>
+        <v>0.016302657286524705</v>
       </c>
       <c r="T16">
-        <v>0.0029829488542857442</v>
+        <v>0.0036031776442228642</v>
       </c>
       <c r="U16">
-        <v>0.00054507977568107706</v>
+        <v>0.00067996828917176746</v>
       </c>
       <c r="V16">
-        <v>0.00066306631186454279</v>
+        <v>0.0008445104196873538</v>
       </c>
       <c r="W16">
-        <v>-3.785896107794893e-05</v>
+        <v>-4.6238094873402381e-05</v>
       </c>
       <c r="X16">
-        <v>1.645607298874697e-05</v>
+        <v>2.9497718223016941e-05</v>
       </c>
       <c r="Y16">
-        <v>0.00011849889305156399</v>
+        <v>0.00021911050133918177</v>
       </c>
       <c r="Z16">
-        <v>7.8370239379261554e-05</v>
+        <v>-1.4042573154109811e-05</v>
       </c>
       <c r="AA16">
-        <v>0.00010370438898322371</v>
+        <v>4.6668522205139517e-05</v>
       </c>
       <c r="AB16">
-        <v>0.00016643072961185397</v>
+        <v>9.9448226390481693e-05</v>
       </c>
       <c r="AC16">
-        <v>4.4590480214139888e-05</v>
+        <v>-3.4255856849454633e-05</v>
       </c>
       <c r="AD16">
-        <v>0.00012793408227820694</v>
+        <v>6.6467335825516442e-05</v>
       </c>
       <c r="AE16">
-        <v>8.6163876814509015e-05</v>
+        <v>-5.7145689075200311e-07</v>
       </c>
       <c r="AF16">
-        <v>3.4382323716401623e-06</v>
+        <v>-4.2520489844773894e-06</v>
       </c>
       <c r="AG16">
-        <v>-0.011541645251482602</v>
+        <v>0.00031607126843852251</v>
+      </c>
+      <c r="AH16">
+        <v>0.00019648143661476526</v>
+      </c>
+      <c r="AI16">
+        <v>-0.015830166702359098</v>
       </c>
     </row>
     <row r="17">
@@ -5629,100 +6149,106 @@
         <v>33</v>
       </c>
       <c r="B17">
-        <v>-0.0024440366939254615</v>
+        <v>-0.21399226506175684</v>
       </c>
       <c r="C17">
-        <v>-0.00018033001386842074</v>
+        <v>-0.0002303058251058735</v>
       </c>
       <c r="D17">
-        <v>-2.9710612782519373e-05</v>
+        <v>-3.6716647217242154e-05</v>
       </c>
       <c r="E17">
-        <v>2.3314111540483845e-07</v>
+        <v>2.9063490963525747e-07</v>
       </c>
       <c r="F17">
-        <v>3.0418839046161047e-05</v>
+        <v>9.2978855768374204e-05</v>
       </c>
       <c r="G17">
-        <v>3.9121108881171041e-05</v>
+        <v>0.00010714980149372465</v>
       </c>
       <c r="H17">
-        <v>4.8715742661558075e-05</v>
+        <v>9.5082755675074404e-05</v>
       </c>
       <c r="I17">
-        <v>0.00013397533207149329</v>
+        <v>0.00022836685530649645</v>
       </c>
       <c r="J17">
-        <v>-4.5781852662590803e-05</v>
+        <v>-0.00028114959275801315</v>
       </c>
       <c r="K17">
-        <v>6.4639160226439662e-05</v>
+        <v>8.5593527860833296e-05</v>
       </c>
       <c r="L17">
-        <v>-1.834383022346386e-05</v>
+        <v>-2.5537299756361466e-05</v>
       </c>
       <c r="M17">
-        <v>-3.2382250607231259e-05</v>
+        <v>-0.00018439082620359744</v>
       </c>
       <c r="N17">
-        <v>0.0029882236154351108</v>
+        <v>0.0044446210162897761</v>
       </c>
       <c r="O17">
-        <v>0.00071803700257074021</v>
+        <v>0.0037718232656827151</v>
       </c>
       <c r="P17">
-        <v>0.0010083390794696219</v>
+        <v>0.0034801524514338385</v>
       </c>
       <c r="Q17">
-        <v>0.011639968079113043</v>
+        <v>0.016323141568697592</v>
       </c>
       <c r="R17">
-        <v>0.011837510872904335</v>
+        <v>0.016585533691270422</v>
       </c>
       <c r="S17">
-        <v>0.011526239557870951</v>
+        <v>0.016168166483734661</v>
       </c>
       <c r="T17">
-        <v>0.0025724603290250628</v>
+        <v>0.0031028692919028824</v>
       </c>
       <c r="U17">
-        <v>0.0003025909530322197</v>
+        <v>0.00040633665604698299</v>
       </c>
       <c r="V17">
-        <v>0.00040218269014782393</v>
+        <v>0.00052868522768988624</v>
       </c>
       <c r="W17">
-        <v>-5.0787013047568993e-05</v>
+        <v>-6.2072318204642253e-05</v>
       </c>
       <c r="X17">
-        <v>-1.5647959112147485e-05</v>
+        <v>-5.0913165239407747e-06</v>
       </c>
       <c r="Y17">
-        <v>5.1045829180399252e-06</v>
+        <v>8.2035876236467332e-05</v>
       </c>
       <c r="Z17">
-        <v>8.005698389369504e-05</v>
+        <v>9.9292650511473638e-06</v>
       </c>
       <c r="AA17">
-        <v>0.00011048888750356776</v>
+        <v>6.579859296115256e-05</v>
       </c>
       <c r="AB17">
-        <v>0.00014151696742741027</v>
+        <v>7.9745894430414922e-05</v>
       </c>
       <c r="AC17">
-        <v>6.8886509464106092e-05</v>
+        <v>1.0732254452152333e-05</v>
       </c>
       <c r="AD17">
-        <v>0.00013270359470377957</v>
+        <v>8.7401855542785893e-05</v>
       </c>
       <c r="AE17">
-        <v>0.00010845629984538121</v>
+        <v>3.5825910529381022e-05</v>
       </c>
       <c r="AF17">
-        <v>-2.5388167044774926e-07</v>
+        <v>-8.6593109527509067e-06</v>
       </c>
       <c r="AG17">
-        <v>-0.010890448498852215</v>
+        <v>0.00028715676090059969</v>
+      </c>
+      <c r="AH17">
+        <v>0.00018711060073023714</v>
+      </c>
+      <c r="AI17">
+        <v>-0.015025821244958616</v>
       </c>
     </row>
     <row r="18">
@@ -5730,100 +6256,106 @@
         <v>34</v>
       </c>
       <c r="B18">
-        <v>0.053612609893776461</v>
+        <v>-0.12513703312581384</v>
       </c>
       <c r="C18">
-        <v>-0.00015615417739911936</v>
+        <v>-0.00019378965804275452</v>
       </c>
       <c r="D18">
-        <v>-2.1951774781963339e-05</v>
+        <v>-2.7617825972556318e-05</v>
       </c>
       <c r="E18">
-        <v>1.8096306399121193e-07</v>
+        <v>2.294840276284424e-07</v>
       </c>
       <c r="F18">
-        <v>1.7181464922683912e-05</v>
+        <v>7.2527720131985041e-05</v>
       </c>
       <c r="G18">
-        <v>4.5106865196108386e-05</v>
+        <v>0.00010556458696630135</v>
       </c>
       <c r="H18">
-        <v>4.0443525073821044e-05</v>
+        <v>7.4378963457746687e-05</v>
       </c>
       <c r="I18">
-        <v>7.3717243789573218e-05</v>
+        <v>0.0001324128404685404</v>
       </c>
       <c r="J18">
-        <v>-4.4132819116729377e-05</v>
+        <v>-0.00024195772820361438</v>
       </c>
       <c r="K18">
-        <v>1.0556010034055508e-05</v>
+        <v>1.4060996713626765e-05</v>
       </c>
       <c r="L18">
-        <v>-6.7301486291642315e-06</v>
+        <v>-1.2851763871653474e-05</v>
       </c>
       <c r="M18">
-        <v>-3.2442179673281772e-05</v>
+        <v>-0.0002258836783469497</v>
       </c>
       <c r="N18">
-        <v>0.0029673587473815844</v>
+        <v>0.0044155113288065658</v>
       </c>
       <c r="O18">
-        <v>0.00071796054298879414</v>
+        <v>0.0037332183932664458</v>
       </c>
       <c r="P18">
-        <v>0.0010071662686694616</v>
+        <v>0.0035208298416822166</v>
       </c>
       <c r="Q18">
-        <v>0.011616885271847935</v>
+        <v>0.016302657286524705</v>
       </c>
       <c r="R18">
-        <v>0.011526239557870951</v>
+        <v>0.016168166483734661</v>
       </c>
       <c r="S18">
-        <v>0.011698243305008439</v>
+        <v>0.016411463768413431</v>
       </c>
       <c r="T18">
-        <v>0.0023784408503682002</v>
+        <v>0.002830381218431534</v>
       </c>
       <c r="U18">
-        <v>-3.0646796768570017e-06</v>
+        <v>-1.3807853405045645e-05</v>
       </c>
       <c r="V18">
-        <v>4.3199190173644469e-05</v>
+        <v>4.3320037314492762e-05</v>
       </c>
       <c r="W18">
-        <v>-5.7223854230534525e-05</v>
+        <v>-6.9648624537904256e-05</v>
       </c>
       <c r="X18">
-        <v>-1.5720243553254487e-05</v>
+        <v>-2.2127136224194943e-05</v>
       </c>
       <c r="Y18">
-        <v>0.00010042533029580841</v>
+        <v>0.0002056334237344401</v>
       </c>
       <c r="Z18">
-        <v>2.6445192924559081e-05</v>
+        <v>-1.6775914302801127e-05</v>
       </c>
       <c r="AA18">
-        <v>5.8156844814681932e-05</v>
+        <v>4.3098241443089141e-05</v>
       </c>
       <c r="AB18">
-        <v>9.47806128909481e-05</v>
+        <v>7.1132001372349076e-05</v>
       </c>
       <c r="AC18">
-        <v>1.7733500546512036e-05</v>
+        <v>-6.5461614596439011e-06</v>
       </c>
       <c r="AD18">
-        <v>7.3752860993755521e-05</v>
+        <v>5.932915766124116e-05</v>
       </c>
       <c r="AE18">
-        <v>5.5914348687922727e-05</v>
+        <v>1.7578409182146797e-05</v>
       </c>
       <c r="AF18">
-        <v>-3.7297443935173445e-06</v>
+        <v>-1.1463604557539225e-05</v>
       </c>
       <c r="AG18">
-        <v>-0.010699410321673423</v>
+        <v>0.00020059819423439221</v>
+      </c>
+      <c r="AH18">
+        <v>0.00014551465158310021</v>
+      </c>
+      <c r="AI18">
+        <v>-0.014774351112696028</v>
       </c>
     </row>
     <row r="19">
@@ -5831,100 +6363,106 @@
         <v>35</v>
       </c>
       <c r="B19">
-        <v>0.24152667921630172</v>
+        <v>0.30175223928742079</v>
       </c>
       <c r="C19">
-        <v>-0.00010149179620665957</v>
+        <v>-0.00011173905231292986</v>
       </c>
       <c r="D19">
-        <v>3.8033274340980888e-05</v>
+        <v>5.5278619335626046e-05</v>
       </c>
       <c r="E19">
-        <v>-3.6361981013645856e-07</v>
+        <v>-5.2139548909216559e-07</v>
       </c>
       <c r="F19">
-        <v>7.4266916942861833e-05</v>
+        <v>0.0001052124654547246</v>
       </c>
       <c r="G19">
-        <v>6.2197105422482322e-05</v>
+        <v>7.074332874305346e-05</v>
       </c>
       <c r="H19">
-        <v>1.8095212749575859e-05</v>
+        <v>6.3200722583111636e-05</v>
       </c>
       <c r="I19">
-        <v>-7.7953591892699747e-05</v>
+        <v>-0.00012814723418749568</v>
       </c>
       <c r="J19">
-        <v>-1.6236028211765117e-05</v>
+        <v>-5.427711514046656e-05</v>
       </c>
       <c r="K19">
-        <v>0.0018605517103708583</v>
+        <v>0.0024487103081431687</v>
       </c>
       <c r="L19">
-        <v>-4.1037722728565702e-05</v>
+        <v>-4.5785419642202534e-05</v>
       </c>
       <c r="M19">
-        <v>-2.595979210691195e-06</v>
+        <v>-4.0859574182594242e-05</v>
       </c>
       <c r="N19">
-        <v>0.00014003549456308986</v>
+        <v>0.0001269330852393532</v>
       </c>
       <c r="O19">
-        <v>2.3166075228149151e-05</v>
+        <v>6.3569120295488822e-05</v>
       </c>
       <c r="P19">
-        <v>-2.2676424316012134e-05</v>
+        <v>-2.4394633965528793e-05</v>
       </c>
       <c r="Q19">
-        <v>0.0029829488542857442</v>
+        <v>0.0036031776442228642</v>
       </c>
       <c r="R19">
-        <v>0.0025724603290250628</v>
+        <v>0.0031028692919028824</v>
       </c>
       <c r="S19">
-        <v>0.0023784408503682002</v>
+        <v>0.002830381218431534</v>
       </c>
       <c r="T19">
-        <v>0.017834473325615663</v>
+        <v>0.023335704424347504</v>
       </c>
       <c r="U19">
-        <v>0.014887615487547013</v>
+        <v>0.019628108190124963</v>
       </c>
       <c r="V19">
-        <v>0.014991669923725416</v>
+        <v>0.019757722921737629</v>
       </c>
       <c r="W19">
-        <v>6.0207210732806803e-05</v>
+        <v>2.1100730272364903e-05</v>
       </c>
       <c r="X19">
-        <v>8.2725801491395027e-05</v>
+        <v>1.2912768528288224e-05</v>
       </c>
       <c r="Y19">
-        <v>0.00068664896546850613</v>
+        <v>0.00072054389331477169</v>
       </c>
       <c r="Z19">
-        <v>8.5609147356592585e-05</v>
+        <v>-1.7703820299388301e-06</v>
       </c>
       <c r="AA19">
-        <v>-6.7232512064425987e-05</v>
+        <v>-0.0002391107342234371</v>
       </c>
       <c r="AB19">
-        <v>-7.5683183965416685e-05</v>
+        <v>-0.00023331829453876549</v>
       </c>
       <c r="AC19">
-        <v>5.8530405087612106e-05</v>
+        <v>-4.9629513844086891e-05</v>
       </c>
       <c r="AD19">
-        <v>-8.7427247758829676e-05</v>
+        <v>-0.00028632919040400863</v>
       </c>
       <c r="AE19">
-        <v>-7.8777702720571764e-05</v>
+        <v>-6.6982911648969141e-05</v>
       </c>
       <c r="AF19">
-        <v>2.8996886032412687e-06</v>
+        <v>-2.9561829437222678e-07</v>
       </c>
       <c r="AG19">
-        <v>-0.018521867812695998</v>
+        <v>-4.8286190883990721e-05</v>
+      </c>
+      <c r="AH19">
+        <v>0.00016431300235473373</v>
+      </c>
+      <c r="AI19">
+        <v>-0.024007797661731684</v>
       </c>
     </row>
     <row r="20">
@@ -5932,100 +6470,106 @@
         <v>36</v>
       </c>
       <c r="B20">
-        <v>0.25457763409553291</v>
+        <v>0.25746884824837424</v>
       </c>
       <c r="C20">
-        <v>-3.5238291414956995e-05</v>
+        <v>-6.1625668049730789e-05</v>
       </c>
       <c r="D20">
-        <v>-2.6751340245998614e-05</v>
+        <v>-2.9886890183150925e-05</v>
       </c>
       <c r="E20">
-        <v>1.0661295843582858e-07</v>
+        <v>1.0555085868033711e-07</v>
       </c>
       <c r="F20">
-        <v>8.8792500542317961e-05</v>
+        <v>0.00013217582648960798</v>
       </c>
       <c r="G20">
-        <v>0.000101760397985971</v>
+        <v>0.0001212270011351161</v>
       </c>
       <c r="H20">
-        <v>0.00010180836593608428</v>
+        <v>0.0001504576395539274</v>
       </c>
       <c r="I20">
-        <v>-4.5988627532732654e-05</v>
+        <v>-5.159543964531753e-05</v>
       </c>
       <c r="J20">
-        <v>-2.9049290787453615e-05</v>
+        <v>-8.684763448134892e-05</v>
       </c>
       <c r="K20">
-        <v>0.0018954827188694323</v>
+        <v>0.0024932705477126752</v>
       </c>
       <c r="L20">
-        <v>-4.866778028618133e-05</v>
+        <v>-6.2587876562417014e-05</v>
       </c>
       <c r="M20">
-        <v>7.4391143985481646e-06</v>
+        <v>1.5597952882382601e-05</v>
       </c>
       <c r="N20">
-        <v>2.6630746857018647e-05</v>
+        <v>4.2134927435865614e-05</v>
       </c>
       <c r="O20">
-        <v>2.7198761180284147e-05</v>
+        <v>7.7539521417399929e-05</v>
       </c>
       <c r="P20">
-        <v>-7.1175939865589471e-06</v>
+        <v>-4.4100356099130694e-06</v>
       </c>
       <c r="Q20">
-        <v>0.00054507977568107706</v>
+        <v>0.00067996828917176746</v>
       </c>
       <c r="R20">
-        <v>0.0003025909530322197</v>
+        <v>0.00040633665604698299</v>
       </c>
       <c r="S20">
-        <v>-3.0646796768570017e-06</v>
+        <v>-1.3807853405045645e-05</v>
       </c>
       <c r="T20">
-        <v>0.014887615487547013</v>
+        <v>0.019628108190124963</v>
       </c>
       <c r="U20">
-        <v>0.015498240896026132</v>
+        <v>0.020330161876498044</v>
       </c>
       <c r="V20">
-        <v>0.01544547620080625</v>
+        <v>0.020263020209561857</v>
       </c>
       <c r="W20">
-        <v>-7.6738343130027344e-05</v>
+        <v>-0.00013911405428177116</v>
       </c>
       <c r="X20">
-        <v>7.9709506529911621e-05</v>
+        <v>2.0679287143843435e-05</v>
       </c>
       <c r="Y20">
-        <v>0.00056641884096285833</v>
+        <v>0.00051600613871761233</v>
       </c>
       <c r="Z20">
-        <v>0.00017904404506962658</v>
+        <v>6.6596775726588363e-05</v>
       </c>
       <c r="AA20">
-        <v>4.0388758760768334e-05</v>
+        <v>-0.0001612216177934913</v>
       </c>
       <c r="AB20">
-        <v>-4.5198774517446472e-06</v>
+        <v>-0.000213103502907863</v>
       </c>
       <c r="AC20">
-        <v>0.00018975146506003231</v>
+        <v>5.6877917379005542e-05</v>
       </c>
       <c r="AD20">
-        <v>1.1739242101864358e-05</v>
+        <v>-0.00019822358007756495</v>
       </c>
       <c r="AE20">
-        <v>9.4348963746079643e-05</v>
+        <v>6.8994809937670707e-05</v>
       </c>
       <c r="AF20">
-        <v>8.7478830651788718e-06</v>
+        <v>6.434105305371939e-06</v>
       </c>
       <c r="AG20">
-        <v>-0.014676313792467369</v>
+        <v>3.5529327898728424e-05</v>
+      </c>
+      <c r="AH20">
+        <v>0.00016931722591211236</v>
+      </c>
+      <c r="AI20">
+        <v>-0.019144972698791899</v>
       </c>
     </row>
     <row r="21">
@@ -6033,100 +6577,106 @@
         <v>37</v>
       </c>
       <c r="B21">
-        <v>0.29290071033697601</v>
+        <v>0.31264245698831505</v>
       </c>
       <c r="C21">
-        <v>-0.00014666270436385764</v>
+        <v>-0.00021239483960761732</v>
       </c>
       <c r="D21">
-        <v>-1.0460529573620136e-05</v>
+        <v>-4.4623759993101366e-06</v>
       </c>
       <c r="E21">
-        <v>-1.6168915785791999e-07</v>
+        <v>-2.9672922183350712e-07</v>
       </c>
       <c r="F21">
-        <v>4.6188856845626094e-05</v>
+        <v>3.4050800023753395e-05</v>
       </c>
       <c r="G21">
-        <v>8.7680816693028012e-05</v>
+        <v>7.4130549102363239e-05</v>
       </c>
       <c r="H21">
-        <v>4.3515158044219685e-05</v>
+        <v>6.15511025975745e-05</v>
       </c>
       <c r="I21">
-        <v>-8.2820324649471311e-05</v>
+        <v>-0.00011983592278242523</v>
       </c>
       <c r="J21">
-        <v>-2.9113971377562904e-05</v>
+        <v>-0.00011456626608425207</v>
       </c>
       <c r="K21">
-        <v>0.0019154924101912867</v>
+        <v>0.0025184652257739613</v>
       </c>
       <c r="L21">
-        <v>-4.5567818225643035e-05</v>
+        <v>-5.4942421264625129e-05</v>
       </c>
       <c r="M21">
-        <v>4.5135328584244114e-06</v>
+        <v>3.051233833794083e-05</v>
       </c>
       <c r="N21">
-        <v>0.00013667950602798754</v>
+        <v>0.00019110709000858057</v>
       </c>
       <c r="O21">
-        <v>2.8145886120179494e-05</v>
+        <v>0.00010938102572210823</v>
       </c>
       <c r="P21">
-        <v>-4.649296344547279e-06</v>
+        <v>-1.8891590283882259e-05</v>
       </c>
       <c r="Q21">
-        <v>0.00066306631186454279</v>
+        <v>0.0008445104196873538</v>
       </c>
       <c r="R21">
-        <v>0.00040218269014782393</v>
+        <v>0.00052868522768988624</v>
       </c>
       <c r="S21">
-        <v>4.3199190173644469e-05</v>
+        <v>4.3320037314492762e-05</v>
       </c>
       <c r="T21">
-        <v>0.014991669923725416</v>
+        <v>0.019757722921737629</v>
       </c>
       <c r="U21">
-        <v>0.01544547620080625</v>
+        <v>0.020263020209561857</v>
       </c>
       <c r="V21">
-        <v>0.016182635129747183</v>
+        <v>0.021314650250681227</v>
       </c>
       <c r="W21">
-        <v>-0.00011340972255222169</v>
+        <v>-0.00017066564095262157</v>
       </c>
       <c r="X21">
-        <v>4.7857481138262152e-05</v>
+        <v>1.6094479887793483e-05</v>
       </c>
       <c r="Y21">
-        <v>0.00052358466533746276</v>
+        <v>0.00048255718139797454</v>
       </c>
       <c r="Z21">
-        <v>0.00019498703200088521</v>
+        <v>3.234588801504304e-05</v>
       </c>
       <c r="AA21">
-        <v>6.9679719341041169e-05</v>
+        <v>-0.00019776480947328486</v>
       </c>
       <c r="AB21">
-        <v>3.561173431261425e-05</v>
+        <v>-0.000228015592020864</v>
       </c>
       <c r="AC21">
-        <v>0.0002295639778916083</v>
+        <v>5.064178824815916e-05</v>
       </c>
       <c r="AD21">
-        <v>3.2942630155763288e-05</v>
+        <v>-0.00022346204295744382</v>
       </c>
       <c r="AE21">
-        <v>0.00013364260780112107</v>
+        <v>6.0863052053493219e-05</v>
       </c>
       <c r="AF21">
-        <v>9.7024294156043895e-06</v>
+        <v>6.5462480586167397e-06</v>
       </c>
       <c r="AG21">
-        <v>-0.014979031873911988</v>
+        <v>0.00010284722603032259</v>
+      </c>
+      <c r="AH21">
+        <v>0.00021353528251407371</v>
+      </c>
+      <c r="AI21">
+        <v>-0.019555278136735209</v>
       </c>
     </row>
     <row r="22">
@@ -6134,100 +6684,106 @@
         <v>38</v>
       </c>
       <c r="B22">
-        <v>-0.0050669037175389755</v>
+        <v>0.0054815085061861984</v>
       </c>
       <c r="C22">
-        <v>2.8452502558465828e-05</v>
+        <v>3.9564821483017843e-05</v>
       </c>
       <c r="D22">
-        <v>1.0216310574711063e-05</v>
+        <v>8.9429306130692885e-06</v>
       </c>
       <c r="E22">
-        <v>-4.7657272907616299e-08</v>
+        <v>-2.5885828971758204e-08</v>
       </c>
       <c r="F22">
-        <v>-2.2435390006407253e-05</v>
+        <v>2.3762492316839416e-06</v>
       </c>
       <c r="G22">
-        <v>7.5493809545012125e-06</v>
+        <v>2.933742301836893e-05</v>
       </c>
       <c r="H22">
-        <v>-9.1081904446003515e-06</v>
+        <v>1.1349132512395238e-05</v>
       </c>
       <c r="I22">
-        <v>-1.0276551325011395e-05</v>
+        <v>-1.2675792881725387e-07</v>
       </c>
       <c r="J22">
-        <v>3.9206455833612448e-07</v>
+        <v>1.8842634774256128e-05</v>
       </c>
       <c r="K22">
-        <v>-2.0060586050050185e-05</v>
+        <v>-2.956393193700654e-05</v>
       </c>
       <c r="L22">
-        <v>1.4519148175705456e-07</v>
+        <v>3.9323988728646681e-07</v>
       </c>
       <c r="M22">
-        <v>-1.8141988435718015e-06</v>
+        <v>-1.8682077194645524e-05</v>
       </c>
       <c r="N22">
-        <v>-3.2582206665644444e-05</v>
+        <v>-4.1771402812106916e-05</v>
       </c>
       <c r="O22">
-        <v>-1.6648805997233284e-06</v>
+        <v>-2.182191783004425e-05</v>
       </c>
       <c r="P22">
-        <v>1.6260607281493305e-06</v>
+        <v>1.8707009413747772e-05</v>
       </c>
       <c r="Q22">
-        <v>-3.785896107794893e-05</v>
+        <v>-4.6238094873402381e-05</v>
       </c>
       <c r="R22">
-        <v>-5.0787013047568993e-05</v>
+        <v>-6.2072318204642253e-05</v>
       </c>
       <c r="S22">
-        <v>-5.7223854230534525e-05</v>
+        <v>-6.9648624537904256e-05</v>
       </c>
       <c r="T22">
-        <v>6.0207210732806803e-05</v>
+        <v>2.1100730272364903e-05</v>
       </c>
       <c r="U22">
-        <v>-7.6738343130027344e-05</v>
+        <v>-0.00013911405428177116</v>
       </c>
       <c r="V22">
-        <v>-0.00011340972255222169</v>
+        <v>-0.00017066564095262157</v>
       </c>
       <c r="W22">
-        <v>0.00047622575856370912</v>
+        <v>0.00063084839585771145</v>
       </c>
       <c r="X22">
-        <v>0.0001645760360801522</v>
+        <v>0.00020733605832726429</v>
       </c>
       <c r="Y22">
-        <v>0.00024735304098880042</v>
+        <v>0.00031608076664480216</v>
       </c>
       <c r="Z22">
-        <v>1.1046440640983434e-05</v>
+        <v>-3.0080707959581621e-07</v>
       </c>
       <c r="AA22">
-        <v>2.5488095709870473e-06</v>
+        <v>-1.2805140901900563e-05</v>
       </c>
       <c r="AB22">
-        <v>1.5095500511921934e-05</v>
+        <v>1.2864131794275286e-06</v>
       </c>
       <c r="AC22">
-        <v>8.4272525953695536e-06</v>
+        <v>-6.3322716246603925e-06</v>
       </c>
       <c r="AD22">
-        <v>1.9232827080719784e-05</v>
+        <v>7.5633144020334964e-06</v>
       </c>
       <c r="AE22">
-        <v>-4.6446445691187226e-05</v>
+        <v>-4.9954516738316636e-05</v>
       </c>
       <c r="AF22">
-        <v>5.912035099158284e-08</v>
+        <v>2.6429877657229862e-07</v>
       </c>
       <c r="AG22">
-        <v>-0.00041274289625724552</v>
+        <v>3.383842085780478e-05</v>
+      </c>
+      <c r="AH22">
+        <v>-1.1683104600936545e-05</v>
+      </c>
+      <c r="AI22">
+        <v>-0.00041100116851545585</v>
       </c>
     </row>
     <row r="23">
@@ -6235,100 +6791,106 @@
         <v>39</v>
       </c>
       <c r="B23">
-        <v>0.041333434976749295</v>
+        <v>0.075606241716321951</v>
       </c>
       <c r="C23">
-        <v>6.5652393812434846e-06</v>
+        <v>-8.9443228905280233e-07</v>
       </c>
       <c r="D23">
-        <v>2.6522687314115122e-05</v>
+        <v>3.4881524734780984e-05</v>
       </c>
       <c r="E23">
-        <v>-2.0691183931877857e-07</v>
+        <v>-2.8117749342473678e-07</v>
       </c>
       <c r="F23">
-        <v>-3.2441540281280242e-05</v>
+        <v>-1.119198441620786e-05</v>
       </c>
       <c r="G23">
-        <v>1.0432826523100718e-05</v>
+        <v>3.5010963706506772e-05</v>
       </c>
       <c r="H23">
-        <v>7.7039305647939134e-06</v>
+        <v>2.826723158468286e-05</v>
       </c>
       <c r="I23">
-        <v>4.7409652537944678e-05</v>
+        <v>7.4293942289223444e-05</v>
       </c>
       <c r="J23">
-        <v>-1.8946519835451321e-05</v>
+        <v>-6.1086821669755975e-05</v>
       </c>
       <c r="K23">
-        <v>6.3031171327357317e-06</v>
+        <v>1.522582992835868e-06</v>
       </c>
       <c r="L23">
-        <v>3.3062321293020559e-06</v>
+        <v>2.8840996153256368e-06</v>
       </c>
       <c r="M23">
-        <v>1.0476244968268607e-05</v>
+        <v>3.8780828261938898e-05</v>
       </c>
       <c r="N23">
-        <v>-9.9831334759697271e-06</v>
+        <v>1.1926379245470742e-07</v>
       </c>
       <c r="O23">
-        <v>1.7857557763969738e-05</v>
+        <v>6.1591036288373402e-05</v>
       </c>
       <c r="P23">
-        <v>-1.0304127086822201e-05</v>
+        <v>-3.9132342708521708e-05</v>
       </c>
       <c r="Q23">
-        <v>1.645607298874697e-05</v>
+        <v>2.9497718223016941e-05</v>
       </c>
       <c r="R23">
-        <v>-1.5647959112147485e-05</v>
+        <v>-5.0913165239407747e-06</v>
       </c>
       <c r="S23">
-        <v>-1.5720243553254487e-05</v>
+        <v>-2.2127136224194943e-05</v>
       </c>
       <c r="T23">
-        <v>8.2725801491395027e-05</v>
+        <v>1.2912768528288224e-05</v>
       </c>
       <c r="U23">
-        <v>7.9709506529911621e-05</v>
+        <v>2.0679287143843435e-05</v>
       </c>
       <c r="V23">
-        <v>4.7857481138262152e-05</v>
+        <v>1.6094479887793483e-05</v>
       </c>
       <c r="W23">
-        <v>0.0001645760360801522</v>
+        <v>0.00020733605832726429</v>
       </c>
       <c r="X23">
-        <v>0.0003990050599759113</v>
+        <v>0.00053786741536874085</v>
       </c>
       <c r="Y23">
-        <v>0.00018317449458446115</v>
+        <v>0.00022308529666843194</v>
       </c>
       <c r="Z23">
-        <v>-1.2757695637534731e-05</v>
+        <v>9.9461068469423614e-06</v>
       </c>
       <c r="AA23">
-        <v>-1.3153728805381944e-05</v>
+        <v>1.5265079848251746e-05</v>
       </c>
       <c r="AB23">
-        <v>-2.3117710078388574e-07</v>
+        <v>2.4269044024923377e-05</v>
       </c>
       <c r="AC23">
-        <v>-3.0538695615703586e-06</v>
+        <v>1.8885996400031121e-05</v>
       </c>
       <c r="AD23">
-        <v>2.2398552687026541e-05</v>
+        <v>5.9731947545477453e-05</v>
       </c>
       <c r="AE23">
-        <v>-2.6679733562360656e-05</v>
+        <v>1.2268955093169197e-05</v>
       </c>
       <c r="AF23">
-        <v>9.721238783416431e-07</v>
+        <v>-1.2264595303643813e-07</v>
       </c>
       <c r="AG23">
-        <v>-0.0010035270209452747</v>
+        <v>0.00011583449999951964</v>
+      </c>
+      <c r="AH23">
+        <v>1.5224501182161082e-05</v>
+      </c>
+      <c r="AI23">
+        <v>-0.0012675766661341425</v>
       </c>
     </row>
     <row r="24">
@@ -6336,100 +6898,106 @@
         <v>40</v>
       </c>
       <c r="B24">
-        <v>0.19741793888614137</v>
+        <v>0.58030121769813392</v>
       </c>
       <c r="C24">
-        <v>0.000102507548319959</v>
+        <v>0.00013778405085550639</v>
       </c>
       <c r="D24">
-        <v>1.0112087376620995e-05</v>
+        <v>1.0546391990252503e-05</v>
       </c>
       <c r="E24">
-        <v>-3.8040347883048606e-08</v>
+        <v>-1.9302764471890355e-08</v>
       </c>
       <c r="F24">
-        <v>3.1618796387728734e-05</v>
+        <v>5.7622309281317365e-05</v>
       </c>
       <c r="G24">
-        <v>8.1664137176609653e-05</v>
+        <v>0.00011082359073710498</v>
       </c>
       <c r="H24">
-        <v>0.00010051261800222392</v>
+        <v>0.00014103812543211003</v>
       </c>
       <c r="I24">
-        <v>0.00010989618229234458</v>
+        <v>0.00013772907671989266</v>
       </c>
       <c r="J24">
-        <v>-2.4925453487590297e-05</v>
+        <v>-6.0210898848725486e-05</v>
       </c>
       <c r="K24">
-        <v>5.3595193619314949e-05</v>
+        <v>4.4895728899750978e-05</v>
       </c>
       <c r="L24">
-        <v>4.8908047596068295e-06</v>
+        <v>9.6987525820311322e-06</v>
       </c>
       <c r="M24">
-        <v>-3.1247008213823618e-05</v>
+        <v>-0.00018981797359741528</v>
       </c>
       <c r="N24">
-        <v>-9.894796143190593e-05</v>
+        <v>-0.00012504007718881338</v>
       </c>
       <c r="O24">
-        <v>2.592070187650388e-05</v>
+        <v>6.0157633434816129e-05</v>
       </c>
       <c r="P24">
-        <v>1.9935133595597968e-05</v>
+        <v>0.00015936702076296003</v>
       </c>
       <c r="Q24">
-        <v>0.00011849889305156399</v>
+        <v>0.00021911050133918177</v>
       </c>
       <c r="R24">
-        <v>5.1045829180399252e-06</v>
+        <v>8.2035876236467332e-05</v>
       </c>
       <c r="S24">
-        <v>0.00010042533029580841</v>
+        <v>0.0002056334237344401</v>
       </c>
       <c r="T24">
-        <v>0.00068664896546850613</v>
+        <v>0.00072054389331477169</v>
       </c>
       <c r="U24">
-        <v>0.00056641884096285833</v>
+        <v>0.00051600613871761233</v>
       </c>
       <c r="V24">
-        <v>0.00052358466533746276</v>
+        <v>0.00048255718139797454</v>
       </c>
       <c r="W24">
-        <v>0.00024735304098880042</v>
+        <v>0.00031608076664480216</v>
       </c>
       <c r="X24">
-        <v>0.00018317449458446115</v>
+        <v>0.00022308529666843194</v>
       </c>
       <c r="Y24">
-        <v>0.0034212038441354129</v>
+        <v>0.0049127713774817644</v>
       </c>
       <c r="Z24">
-        <v>1.0044551303252304e-05</v>
+        <v>4.544531451682553e-05</v>
       </c>
       <c r="AA24">
-        <v>3.0398733317869105e-05</v>
+        <v>6.0082731177777028e-05</v>
       </c>
       <c r="AB24">
-        <v>5.7202697432759371e-05</v>
+        <v>9.2823550993128756e-05</v>
       </c>
       <c r="AC24">
-        <v>8.0919534755876017e-06</v>
+        <v>3.3394181581054242e-05</v>
       </c>
       <c r="AD24">
-        <v>5.0059007667118896e-05</v>
+        <v>9.2201178753770717e-05</v>
       </c>
       <c r="AE24">
-        <v>-5.4425320463299819e-05</v>
+        <v>-2.3088192576370845e-05</v>
       </c>
       <c r="AF24">
-        <v>-3.5096290110600916e-06</v>
+        <v>-9.1016462402966812e-06</v>
       </c>
       <c r="AG24">
-        <v>-0.0011215853421955352</v>
+        <v>7.3739496584565752e-05</v>
+      </c>
+      <c r="AH24">
+        <v>1.185222418444978e-05</v>
+      </c>
+      <c r="AI24">
+        <v>-0.0011978237530955954</v>
       </c>
     </row>
     <row r="25">
@@ -6437,100 +7005,106 @@
         <v>41</v>
       </c>
       <c r="B25">
-        <v>-0.10137318234779459</v>
+        <v>-0.17691015112612518</v>
       </c>
       <c r="C25">
-        <v>-8.877803668276503e-06</v>
+        <v>5.7221913230602833e-06</v>
       </c>
       <c r="D25">
-        <v>1.156960100076414e-06</v>
+        <v>-3.5955745998582085e-07</v>
       </c>
       <c r="E25">
-        <v>-3.7501710989713656e-08</v>
+        <v>-5.5699364489547746e-09</v>
       </c>
       <c r="F25">
-        <v>-5.0134462642295857e-05</v>
+        <v>-5.5970222525287064e-05</v>
       </c>
       <c r="G25">
-        <v>-2.5102434169491962e-05</v>
+        <v>-3.2237887984472476e-05</v>
       </c>
       <c r="H25">
-        <v>-7.3997089550669956e-05</v>
+        <v>-7.1696895795612167e-05</v>
       </c>
       <c r="I25">
-        <v>1.4588222487678729e-05</v>
+        <v>-5.7447948003091359e-06</v>
       </c>
       <c r="J25">
-        <v>7.113626159366366e-06</v>
+        <v>8.5311790844845093e-06</v>
       </c>
       <c r="K25">
-        <v>2.0529081635585478e-05</v>
+        <v>9.5288826796151305e-06</v>
       </c>
       <c r="L25">
-        <v>-9.0823849218972318e-06</v>
+        <v>-6.0049578820980547e-06</v>
       </c>
       <c r="M25">
-        <v>-9.9475852460585566e-06</v>
+        <v>-5.2738991774779885e-05</v>
       </c>
       <c r="N25">
-        <v>0.00012443407783389133</v>
+        <v>6.3903171694334451e-05</v>
       </c>
       <c r="O25">
-        <v>-4.111867761025581e-05</v>
+        <v>-0.00011543975939217192</v>
       </c>
       <c r="P25">
-        <v>3.0076837371328068e-05</v>
+        <v>8.6421126252416661e-05</v>
       </c>
       <c r="Q25">
-        <v>7.8370239379261554e-05</v>
+        <v>-1.4042573154109811e-05</v>
       </c>
       <c r="R25">
-        <v>8.005698389369504e-05</v>
+        <v>9.9292650511473638e-06</v>
       </c>
       <c r="S25">
-        <v>2.6445192924559081e-05</v>
+        <v>-1.6775914302801127e-05</v>
       </c>
       <c r="T25">
-        <v>8.5609147356592585e-05</v>
+        <v>-1.7703820299388301e-06</v>
       </c>
       <c r="U25">
-        <v>0.00017904404506962658</v>
+        <v>6.6596775726588363e-05</v>
       </c>
       <c r="V25">
-        <v>0.00019498703200088521</v>
+        <v>3.234588801504304e-05</v>
       </c>
       <c r="W25">
-        <v>1.1046440640983434e-05</v>
+        <v>-3.0080707959581621e-07</v>
       </c>
       <c r="X25">
-        <v>-1.2757695637534731e-05</v>
+        <v>9.9461068469423614e-06</v>
       </c>
       <c r="Y25">
-        <v>1.0044551303252304e-05</v>
+        <v>4.544531451682553e-05</v>
       </c>
       <c r="Z25">
-        <v>0.0023662454592939192</v>
+        <v>0.0027353329559316282</v>
       </c>
       <c r="AA25">
-        <v>0.0021244110545033217</v>
+        <v>0.0024019470371932561</v>
       </c>
       <c r="AB25">
-        <v>0.0021278383844272396</v>
+        <v>0.0024003706698320004</v>
       </c>
       <c r="AC25">
-        <v>0.0021272513774244651</v>
+        <v>0.0024053124015353117</v>
       </c>
       <c r="AD25">
-        <v>0.0021306519155457303</v>
+        <v>0.0024130635737536028</v>
       </c>
       <c r="AE25">
-        <v>0.0021131702073767331</v>
+        <v>0.0023943327021205148</v>
       </c>
       <c r="AF25">
-        <v>8.4272321518982698e-06</v>
+        <v>6.8855059488431573e-06</v>
       </c>
       <c r="AG25">
-        <v>-0.0023404140812224375</v>
+        <v>3.9008417406748153e-05</v>
+      </c>
+      <c r="AH25">
+        <v>6.6071984716610348e-06</v>
+      </c>
+      <c r="AI25">
+        <v>-0.0024091914813475467</v>
       </c>
     </row>
     <row r="26">
@@ -6538,100 +7112,106 @@
         <v>42</v>
       </c>
       <c r="B26">
-        <v>-0.035314062558909065</v>
+        <v>-0.041780170364350111</v>
       </c>
       <c r="C26">
-        <v>-5.8973248747452438e-06</v>
+        <v>1.0577578694776009e-05</v>
       </c>
       <c r="D26">
-        <v>3.7377401114815629e-06</v>
+        <v>2.7308923763493925e-06</v>
       </c>
       <c r="E26">
-        <v>-6.8936656713701994e-08</v>
+        <v>-4.0956090897983854e-08</v>
       </c>
       <c r="F26">
-        <v>-3.5659616485143918e-05</v>
+        <v>-3.256235592747638e-05</v>
       </c>
       <c r="G26">
-        <v>-2.7779003373911088e-05</v>
+        <v>-3.3365374743733918e-05</v>
       </c>
       <c r="H26">
-        <v>-8.9198778641227635e-05</v>
+        <v>-8.9513114637770463e-05</v>
       </c>
       <c r="I26">
-        <v>-2.7344143241462854e-05</v>
+        <v>-5.5462795353136696e-05</v>
       </c>
       <c r="J26">
-        <v>6.5266818568562961e-06</v>
+        <v>7.6920219427976225e-06</v>
       </c>
       <c r="K26">
-        <v>2.8023596746982191e-06</v>
+        <v>-1.9570131783865075e-05</v>
       </c>
       <c r="L26">
-        <v>-1.1126898249002362e-05</v>
+        <v>-8.3258245848905986e-06</v>
       </c>
       <c r="M26">
-        <v>-1.4895073867319593e-05</v>
+        <v>-8.1565824726875994e-05</v>
       </c>
       <c r="N26">
-        <v>0.00016002541178001314</v>
+        <v>0.00011456175015991151</v>
       </c>
       <c r="O26">
-        <v>-3.6374920994950376e-05</v>
+        <v>-9.5444848122407241e-05</v>
       </c>
       <c r="P26">
-        <v>3.2413127683596731e-05</v>
+        <v>0.00010814157455045134</v>
       </c>
       <c r="Q26">
-        <v>0.00010370438898322371</v>
+        <v>4.6668522205139517e-05</v>
       </c>
       <c r="R26">
-        <v>0.00011048888750356776</v>
+        <v>6.579859296115256e-05</v>
       </c>
       <c r="S26">
-        <v>5.8156844814681932e-05</v>
+        <v>4.3098241443089141e-05</v>
       </c>
       <c r="T26">
-        <v>-6.7232512064425987e-05</v>
+        <v>-0.0002391107342234371</v>
       </c>
       <c r="U26">
-        <v>4.0388758760768334e-05</v>
+        <v>-0.0001612216177934913</v>
       </c>
       <c r="V26">
-        <v>6.9679719341041169e-05</v>
+        <v>-0.00019776480947328486</v>
       </c>
       <c r="W26">
-        <v>2.5488095709870473e-06</v>
+        <v>-1.2805140901900563e-05</v>
       </c>
       <c r="X26">
-        <v>-1.3153728805381944e-05</v>
+        <v>1.5265079848251746e-05</v>
       </c>
       <c r="Y26">
-        <v>3.0398733317869105e-05</v>
+        <v>6.0082731177777028e-05</v>
       </c>
       <c r="Z26">
-        <v>0.0021244110545033217</v>
+        <v>0.0024019470371932561</v>
       </c>
       <c r="AA26">
-        <v>0.0024756239690290342</v>
+        <v>0.0029132641563827297</v>
       </c>
       <c r="AB26">
-        <v>0.0021366268989155444</v>
+        <v>0.0024145795193169753</v>
       </c>
       <c r="AC26">
-        <v>0.0021276330899440677</v>
+        <v>0.002407777320436252</v>
       </c>
       <c r="AD26">
-        <v>0.002131898567389844</v>
+        <v>0.0024183629461501988</v>
       </c>
       <c r="AE26">
-        <v>0.0021142020575477699</v>
+        <v>0.0023961305224088668</v>
       </c>
       <c r="AF26">
-        <v>7.0217618232480057e-06</v>
+        <v>5.0341015421428035e-06</v>
       </c>
       <c r="AG26">
-        <v>-0.0022033836382427344</v>
+        <v>3.5143103445039927e-05</v>
+      </c>
+      <c r="AH26">
+        <v>-2.8320511428704806e-05</v>
+      </c>
+      <c r="AI26">
+        <v>-0.0021972512193771704</v>
       </c>
     </row>
     <row r="27">
@@ -6639,100 +7219,106 @@
         <v>43</v>
       </c>
       <c r="B27">
-        <v>-0.050783832529671558</v>
+        <v>-0.041959917611259147</v>
       </c>
       <c r="C27">
-        <v>-9.8714966054679304e-06</v>
+        <v>7.2822143498292637e-06</v>
       </c>
       <c r="D27">
-        <v>4.6265665702065824e-06</v>
+        <v>2.697070694620193e-06</v>
       </c>
       <c r="E27">
-        <v>-7.5057046272668922e-08</v>
+        <v>-4.0279910068181208e-08</v>
       </c>
       <c r="F27">
-        <v>-3.9655761580559994e-05</v>
+        <v>-4.3692492921836609e-05</v>
       </c>
       <c r="G27">
-        <v>-2.4704014749193145e-05</v>
+        <v>-3.4721204415569468e-05</v>
       </c>
       <c r="H27">
-        <v>-8.7012589759390331e-05</v>
+        <v>-9.6464399529598956e-05</v>
       </c>
       <c r="I27">
-        <v>-3.5443741443949334e-05</v>
+        <v>-7.5872728060489116e-05</v>
       </c>
       <c r="J27">
-        <v>1.6847673087838663e-06</v>
+        <v>-1.024119070579583e-05</v>
       </c>
       <c r="K27">
-        <v>-2.9381163177773142e-06</v>
+        <v>-2.6616656722436446e-05</v>
       </c>
       <c r="L27">
-        <v>-8.3157441435049803e-06</v>
+        <v>-4.5104831088476339e-06</v>
       </c>
       <c r="M27">
-        <v>-1.7391891510250446e-05</v>
+        <v>-7.4531000168357822e-05</v>
       </c>
       <c r="N27">
-        <v>0.00019690878900844965</v>
+        <v>0.00013430757200705204</v>
       </c>
       <c r="O27">
-        <v>-3.755046210642095e-05</v>
+        <v>-9.9987714929009334e-05</v>
       </c>
       <c r="P27">
-        <v>3.6912521479181914e-05</v>
+        <v>8.854105528242098e-05</v>
       </c>
       <c r="Q27">
-        <v>0.00016643072961185397</v>
+        <v>9.9448226390481693e-05</v>
       </c>
       <c r="R27">
-        <v>0.00014151696742741027</v>
+        <v>7.9745894430414922e-05</v>
       </c>
       <c r="S27">
-        <v>9.47806128909481e-05</v>
+        <v>7.1132001372349076e-05</v>
       </c>
       <c r="T27">
-        <v>-7.5683183965416685e-05</v>
+        <v>-0.00023331829453876549</v>
       </c>
       <c r="U27">
-        <v>-4.5198774517446472e-06</v>
+        <v>-0.000213103502907863</v>
       </c>
       <c r="V27">
-        <v>3.561173431261425e-05</v>
+        <v>-0.000228015592020864</v>
       </c>
       <c r="W27">
-        <v>1.5095500511921934e-05</v>
+        <v>1.2864131794275286e-06</v>
       </c>
       <c r="X27">
-        <v>-2.3117710078388574e-07</v>
+        <v>2.4269044024923377e-05</v>
       </c>
       <c r="Y27">
-        <v>5.7202697432759371e-05</v>
+        <v>9.2823550993128756e-05</v>
       </c>
       <c r="Z27">
-        <v>0.0021278383844272396</v>
+        <v>0.0024003706698320004</v>
       </c>
       <c r="AA27">
-        <v>0.0021366268989155444</v>
+        <v>0.0024145795193169753</v>
       </c>
       <c r="AB27">
-        <v>0.0024598407612613617</v>
+        <v>0.0028900449380497972</v>
       </c>
       <c r="AC27">
-        <v>0.0021298492476775014</v>
+        <v>0.0024043897227105974</v>
       </c>
       <c r="AD27">
-        <v>0.0021365454202894253</v>
+        <v>0.0024166781997009002</v>
       </c>
       <c r="AE27">
-        <v>0.0021146631244888846</v>
+        <v>0.0023922319415731258</v>
       </c>
       <c r="AF27">
-        <v>6.9310533764034815e-06</v>
+        <v>3.9761924869891407e-06</v>
       </c>
       <c r="AG27">
-        <v>-0.0022337355730764554</v>
+        <v>8.4925635283048407e-05</v>
+      </c>
+      <c r="AH27">
+        <v>1.8899554389884433e-05</v>
+      </c>
+      <c r="AI27">
+        <v>-0.0021741961383255994</v>
       </c>
     </row>
     <row r="28">
@@ -6740,100 +7326,106 @@
         <v>44</v>
       </c>
       <c r="B28">
-        <v>-0.1048815473685934</v>
+        <v>-0.17308448932077908</v>
       </c>
       <c r="C28">
-        <v>-9.2243777165275349e-06</v>
+        <v>4.2572345110106642e-06</v>
       </c>
       <c r="D28">
-        <v>3.9144467829741868e-06</v>
+        <v>3.3111745535957895e-06</v>
       </c>
       <c r="E28">
-        <v>-6.8818484765936329e-08</v>
+        <v>-4.6066599677972516e-08</v>
       </c>
       <c r="F28">
-        <v>-7.446299160707116e-05</v>
+        <v>-9.425875026856283e-05</v>
       </c>
       <c r="G28">
-        <v>-7.2821221714079645e-05</v>
+        <v>-9.5267496664021333e-05</v>
       </c>
       <c r="H28">
-        <v>-0.0001299171678492226</v>
+        <v>-0.00014677624567278631</v>
       </c>
       <c r="I28">
-        <v>-5.0452409494885792e-05</v>
+        <v>-9.1320964737238216e-05</v>
       </c>
       <c r="J28">
-        <v>7.3527247910234905e-06</v>
+        <v>9.4274848582951993e-06</v>
       </c>
       <c r="K28">
-        <v>2.1275909058952858e-05</v>
+        <v>8.045076416849338e-06</v>
       </c>
       <c r="L28">
-        <v>-9.9556821724918097e-06</v>
+        <v>-7.3148628605913319e-06</v>
       </c>
       <c r="M28">
-        <v>-1.2703353865582253e-05</v>
+        <v>-6.6399652958953561e-05</v>
       </c>
       <c r="N28">
-        <v>0.00014719297904257009</v>
+        <v>9.8039917483482919e-05</v>
       </c>
       <c r="O28">
-        <v>-4.480835318752699e-05</v>
+        <v>-0.00012832431907419813</v>
       </c>
       <c r="P28">
-        <v>3.3099817879172567e-05</v>
+        <v>0.00010920062210723416</v>
       </c>
       <c r="Q28">
-        <v>4.4590480214139888e-05</v>
+        <v>-3.4255856849454633e-05</v>
       </c>
       <c r="R28">
-        <v>6.8886509464106092e-05</v>
+        <v>1.0732254452152333e-05</v>
       </c>
       <c r="S28">
-        <v>1.7733500546512036e-05</v>
+        <v>-6.5461614596439011e-06</v>
       </c>
       <c r="T28">
-        <v>5.8530405087612106e-05</v>
+        <v>-4.9629513844086891e-05</v>
       </c>
       <c r="U28">
-        <v>0.00018975146506003231</v>
+        <v>5.6877917379005542e-05</v>
       </c>
       <c r="V28">
-        <v>0.0002295639778916083</v>
+        <v>5.064178824815916e-05</v>
       </c>
       <c r="W28">
-        <v>8.4272525953695536e-06</v>
+        <v>-6.3322716246603925e-06</v>
       </c>
       <c r="X28">
-        <v>-3.0538695615703586e-06</v>
+        <v>1.8885996400031121e-05</v>
       </c>
       <c r="Y28">
-        <v>8.0919534755876017e-06</v>
+        <v>3.3394181581054242e-05</v>
       </c>
       <c r="Z28">
-        <v>0.0021272513774244651</v>
+        <v>0.0024053124015353117</v>
       </c>
       <c r="AA28">
-        <v>0.0021276330899440677</v>
+        <v>0.002407777320436252</v>
       </c>
       <c r="AB28">
-        <v>0.0021298492476775014</v>
+        <v>0.0024043897227105974</v>
       </c>
       <c r="AC28">
-        <v>0.0023693636478806751</v>
+        <v>0.002736857499425413</v>
       </c>
       <c r="AD28">
-        <v>0.0021327709559643025</v>
+        <v>0.0024153830837603122</v>
       </c>
       <c r="AE28">
-        <v>0.0021153181181380598</v>
+        <v>0.0023988742628119177</v>
       </c>
       <c r="AF28">
-        <v>9.1784161796599204e-06</v>
+        <v>7.3288350495538185e-06</v>
       </c>
       <c r="AG28">
-        <v>-0.0023351606799294905</v>
+        <v>3.0846391880545981e-05</v>
+      </c>
+      <c r="AH28">
+        <v>-1.8176728307583035e-05</v>
+      </c>
+      <c r="AI28">
+        <v>-0.0023874069787615457</v>
       </c>
     </row>
     <row r="29">
@@ -6841,100 +7433,106 @@
         <v>45</v>
       </c>
       <c r="B29">
-        <v>-0.049380617756219353</v>
+        <v>-0.059777586583149328</v>
       </c>
       <c r="C29">
-        <v>-2.4221781435151366e-05</v>
+        <v>-1.8895805004206254e-05</v>
       </c>
       <c r="D29">
-        <v>3.8214061891865504e-06</v>
+        <v>2.7098451452058439e-06</v>
       </c>
       <c r="E29">
-        <v>-6.2548400488715465e-08</v>
+        <v>-3.3901780022848824e-08</v>
       </c>
       <c r="F29">
-        <v>1.3809560856642422e-06</v>
+        <v>1.0258616395554358e-05</v>
       </c>
       <c r="G29">
-        <v>-1.4506514775377449e-05</v>
+        <v>-3.6770110894328648e-07</v>
       </c>
       <c r="H29">
-        <v>-6.1442403194493837e-05</v>
+        <v>-5.7995603966465303e-05</v>
       </c>
       <c r="I29">
-        <v>5.679111209082083e-05</v>
+        <v>4.7570217411091985e-05</v>
       </c>
       <c r="J29">
-        <v>-1.043391205122893e-05</v>
+        <v>-7.4113146721242862e-05</v>
       </c>
       <c r="K29">
-        <v>3.6484657821675859e-06</v>
+        <v>-1.6211091124791006e-05</v>
       </c>
       <c r="L29">
-        <v>-1.2031140510936847e-05</v>
+        <v>-1.1032005505418663e-05</v>
       </c>
       <c r="M29">
-        <v>-1.0578123565384703e-05</v>
+        <v>-5.2142528327796093e-05</v>
       </c>
       <c r="N29">
-        <v>0.00012940082653870814</v>
+        <v>7.1475371197587522e-05</v>
       </c>
       <c r="O29">
-        <v>-3.7254365094515377e-05</v>
+        <v>-4.7235486771416541e-05</v>
       </c>
       <c r="P29">
-        <v>3.1536699458196743e-05</v>
+        <v>6.8460209244772773e-05</v>
       </c>
       <c r="Q29">
-        <v>0.00012793408227820694</v>
+        <v>6.6467335825516442e-05</v>
       </c>
       <c r="R29">
-        <v>0.00013270359470377957</v>
+        <v>8.7401855542785893e-05</v>
       </c>
       <c r="S29">
-        <v>7.3752860993755521e-05</v>
+        <v>5.932915766124116e-05</v>
       </c>
       <c r="T29">
-        <v>-8.7427247758829676e-05</v>
+        <v>-0.00028632919040400863</v>
       </c>
       <c r="U29">
-        <v>1.1739242101864358e-05</v>
+        <v>-0.00019822358007756495</v>
       </c>
       <c r="V29">
-        <v>3.2942630155763288e-05</v>
+        <v>-0.00022346204295744382</v>
       </c>
       <c r="W29">
-        <v>1.9232827080719784e-05</v>
+        <v>7.5633144020334964e-06</v>
       </c>
       <c r="X29">
-        <v>2.2398552687026541e-05</v>
+        <v>5.9731947545477453e-05</v>
       </c>
       <c r="Y29">
-        <v>5.0059007667118896e-05</v>
+        <v>9.2201178753770717e-05</v>
       </c>
       <c r="Z29">
-        <v>0.0021306519155457303</v>
+        <v>0.0024130635737536028</v>
       </c>
       <c r="AA29">
-        <v>0.002131898567389844</v>
+        <v>0.0024183629461501988</v>
       </c>
       <c r="AB29">
-        <v>0.0021365454202894253</v>
+        <v>0.0024166781997009002</v>
       </c>
       <c r="AC29">
-        <v>0.0021327709559643025</v>
+        <v>0.0024153830837603122</v>
       </c>
       <c r="AD29">
-        <v>0.0023624732826171167</v>
+        <v>0.002741044324812615</v>
       </c>
       <c r="AE29">
-        <v>0.0021132352193214991</v>
+        <v>0.002399823517029775</v>
       </c>
       <c r="AF29">
-        <v>1.1857945925722413e-05</v>
+        <v>6.7432536734442293e-06</v>
       </c>
       <c r="AG29">
-        <v>-0.002320178887264668</v>
+        <v>0.0002488530751332714</v>
+      </c>
+      <c r="AH29">
+        <v>-2.8456481678028681e-07</v>
+      </c>
+      <c r="AI29">
+        <v>-0.0022674087277131556</v>
       </c>
     </row>
     <row r="30">
@@ -6942,100 +7540,106 @@
         <v>46</v>
       </c>
       <c r="B30">
-        <v>-0.10830747053401948</v>
+        <v>-0.15103280478580675</v>
       </c>
       <c r="C30">
-        <v>-3.0923984250093275e-06</v>
+        <v>9.3130314107987875e-06</v>
       </c>
       <c r="D30">
-        <v>-3.9748307806056623e-06</v>
+        <v>-3.7182472273433852e-06</v>
       </c>
       <c r="E30">
-        <v>-1.9607169780295065e-10</v>
+        <v>1.8326230847159117e-08</v>
       </c>
       <c r="F30">
-        <v>-1.5600412780258758e-05</v>
+        <v>-5.2922973063558609e-06</v>
       </c>
       <c r="G30">
-        <v>-4.9130978743581392e-06</v>
+        <v>1.7840588211187744e-06</v>
       </c>
       <c r="H30">
-        <v>-4.4432150647458278e-05</v>
+        <v>-4.1755144483655708e-05</v>
       </c>
       <c r="I30">
-        <v>1.0067916064749119e-05</v>
+        <v>-1.0998181087716835e-05</v>
       </c>
       <c r="J30">
-        <v>7.9098447125638991e-06</v>
+        <v>-3.34843595512793e-06</v>
       </c>
       <c r="K30">
-        <v>1.2841854113162447e-05</v>
+        <v>1.2277340705570843e-05</v>
       </c>
       <c r="L30">
-        <v>-8.7974991603492583e-06</v>
+        <v>-5.3927727825969897e-06</v>
       </c>
       <c r="M30">
-        <v>-1.2087935056753014e-05</v>
+        <v>-5.4684359378744815e-05</v>
       </c>
       <c r="N30">
-        <v>0.00018590963167223012</v>
+        <v>0.00012324085976339047</v>
       </c>
       <c r="O30">
-        <v>-4.3357434046430605e-05</v>
+        <v>-9.5000747710684023e-05</v>
       </c>
       <c r="P30">
-        <v>2.8392876978894691e-05</v>
+        <v>5.8168987783405678e-05</v>
       </c>
       <c r="Q30">
-        <v>8.6163876814509015e-05</v>
+        <v>-5.7145689075200311e-07</v>
       </c>
       <c r="R30">
-        <v>0.00010845629984538121</v>
+        <v>3.5825910529381022e-05</v>
       </c>
       <c r="S30">
-        <v>5.5914348687922727e-05</v>
+        <v>1.7578409182146797e-05</v>
       </c>
       <c r="T30">
-        <v>-7.8777702720571764e-05</v>
+        <v>-6.6982911648969141e-05</v>
       </c>
       <c r="U30">
-        <v>9.4348963746079643e-05</v>
+        <v>6.8994809937670707e-05</v>
       </c>
       <c r="V30">
-        <v>0.00013364260780112107</v>
+        <v>6.0863052053493219e-05</v>
       </c>
       <c r="W30">
-        <v>-4.6446445691187226e-05</v>
+        <v>-4.9954516738316636e-05</v>
       </c>
       <c r="X30">
-        <v>-2.6679733562360656e-05</v>
+        <v>1.2268955093169197e-05</v>
       </c>
       <c r="Y30">
-        <v>-5.4425320463299819e-05</v>
+        <v>-2.3088192576370845e-05</v>
       </c>
       <c r="Z30">
-        <v>0.0021131702073767331</v>
+        <v>0.0023943327021205148</v>
       </c>
       <c r="AA30">
-        <v>0.0021142020575477699</v>
+        <v>0.0023961305224088668</v>
       </c>
       <c r="AB30">
-        <v>0.0021146631244888846</v>
+        <v>0.0023922319415731258</v>
       </c>
       <c r="AC30">
-        <v>0.0021153181181380598</v>
+        <v>0.0023988742628119177</v>
       </c>
       <c r="AD30">
-        <v>0.0021132352193214991</v>
+        <v>0.002399823517029775</v>
       </c>
       <c r="AE30">
-        <v>0.0024600845166822954</v>
+        <v>0.0028590045554329315</v>
       </c>
       <c r="AF30">
-        <v>5.2442169749257372e-06</v>
+        <v>4.640559718731578e-06</v>
       </c>
       <c r="AG30">
-        <v>-0.0020692446765736309</v>
+        <v>2.7589194120178871e-05</v>
+      </c>
+      <c r="AH30">
+        <v>-3.89107080160404e-05</v>
+      </c>
+      <c r="AI30">
+        <v>-0.0022996381816512762</v>
       </c>
     </row>
     <row r="31">
@@ -7043,100 +7647,106 @@
         <v>47</v>
       </c>
       <c r="B31">
-        <v>0.0073297059529603467</v>
+        <v>0.022623976220380211</v>
       </c>
       <c r="C31">
-        <v>-1.0539886173293146e-06</v>
+        <v>-1.1801453572122004e-07</v>
       </c>
       <c r="D31">
-        <v>-1.0164325202820428e-07</v>
+        <v>-1.0517234437267577e-07</v>
       </c>
       <c r="E31">
-        <v>-6.9834347979371075e-10</v>
+        <v>-7.9769449682427677e-10</v>
       </c>
       <c r="F31">
-        <v>-1.4390174210012711e-07</v>
+        <v>-2.1242813873393685e-06</v>
       </c>
       <c r="G31">
-        <v>-1.9204040409130673e-06</v>
+        <v>-4.9769320234327978e-06</v>
       </c>
       <c r="H31">
-        <v>-1.8707608751687319e-06</v>
+        <v>-3.812822218944009e-06</v>
       </c>
       <c r="I31">
-        <v>2.3481140046250883e-06</v>
+        <v>-1.5225029826202927e-06</v>
       </c>
       <c r="J31">
-        <v>-1.5370353053766594e-06</v>
+        <v>-1.2766501460807108e-06</v>
       </c>
       <c r="K31">
-        <v>1.114564633412457e-06</v>
+        <v>7.6871471711810675e-07</v>
       </c>
       <c r="L31">
-        <v>-2.1870100858353579e-07</v>
+        <v>-2.8400275670942545e-07</v>
       </c>
       <c r="M31">
-        <v>1.4554320829353008e-06</v>
+        <v>4.5341083384152171e-06</v>
       </c>
       <c r="N31">
-        <v>6.7391443724539919e-07</v>
+        <v>-1.6854814070528881e-06</v>
       </c>
       <c r="O31">
-        <v>2.2138589919915682e-07</v>
+        <v>-2.9715070134869425e-06</v>
       </c>
       <c r="P31">
-        <v>-1.6227347779727098e-06</v>
+        <v>-4.8550016487323321e-06</v>
       </c>
       <c r="Q31">
-        <v>3.4382323716401623e-06</v>
+        <v>-4.2520489844773894e-06</v>
       </c>
       <c r="R31">
-        <v>-2.5388167044774926e-07</v>
+        <v>-8.6593109527509067e-06</v>
       </c>
       <c r="S31">
-        <v>-3.7297443935173445e-06</v>
+        <v>-1.1463604557539225e-05</v>
       </c>
       <c r="T31">
-        <v>2.8996886032412687e-06</v>
+        <v>-2.9561829437222678e-07</v>
       </c>
       <c r="U31">
-        <v>8.7478830651788718e-06</v>
+        <v>6.434105305371939e-06</v>
       </c>
       <c r="V31">
-        <v>9.7024294156043895e-06</v>
+        <v>6.5462480586167397e-06</v>
       </c>
       <c r="W31">
-        <v>5.912035099158284e-08</v>
+        <v>2.6429877657229862e-07</v>
       </c>
       <c r="X31">
-        <v>9.721238783416431e-07</v>
+        <v>-1.2264595303643813e-07</v>
       </c>
       <c r="Y31">
-        <v>-3.5096290110600916e-06</v>
+        <v>-9.1016462402966812e-06</v>
       </c>
       <c r="Z31">
-        <v>8.4272321518982698e-06</v>
+        <v>6.8855059488431573e-06</v>
       </c>
       <c r="AA31">
-        <v>7.0217618232480057e-06</v>
+        <v>5.0341015421428035e-06</v>
       </c>
       <c r="AB31">
-        <v>6.9310533764034815e-06</v>
+        <v>3.9761924869891407e-06</v>
       </c>
       <c r="AC31">
-        <v>9.1784161796599204e-06</v>
+        <v>7.3288350495538185e-06</v>
       </c>
       <c r="AD31">
-        <v>1.1857945925722413e-05</v>
+        <v>6.7432536734442293e-06</v>
       </c>
       <c r="AE31">
-        <v>5.2442169749257372e-06</v>
+        <v>4.640559718731578e-06</v>
       </c>
       <c r="AF31">
-        <v>3.0938552504869883e-06</v>
+        <v>3.8262559738154043e-06</v>
       </c>
       <c r="AG31">
-        <v>-5.9901912604673263e-05</v>
+        <v>-6.0272775925399258e-06</v>
+      </c>
+      <c r="AH31">
+        <v>-1.1944329663813337e-05</v>
+      </c>
+      <c r="AI31">
+        <v>-6.1229541170580211e-05</v>
       </c>
     </row>
     <row r="32">
@@ -7144,100 +7754,320 @@
         <v>48</v>
       </c>
       <c r="B32">
-        <v>-0.26603228404670176</v>
+        <v>-0.20141914495740831</v>
       </c>
       <c r="C32">
-        <v>0.00017151388028960356</v>
+        <v>-7.8303737241919042e-05</v>
       </c>
       <c r="D32">
-        <v>-0.00027447695095998183</v>
+        <v>6.7792657439162902e-07</v>
       </c>
       <c r="E32">
-        <v>2.3688879857051789e-06</v>
+        <v>-2.0616752399827562e-08</v>
       </c>
       <c r="F32">
-        <v>-0.0024249514036422341</v>
+        <v>1.3254611324652228e-05</v>
       </c>
       <c r="G32">
-        <v>-0.0024963187450407738</v>
+        <v>2.3653988487843877e-05</v>
       </c>
       <c r="H32">
-        <v>-0.0024842963424730052</v>
+        <v>-9.4182418717767002e-07</v>
       </c>
       <c r="I32">
-        <v>-0.0030329053243088669</v>
+        <v>0.00017677745986703283</v>
       </c>
       <c r="J32">
-        <v>0.00010027052921489057</v>
+        <v>-0.00016867270152082627</v>
       </c>
       <c r="K32">
-        <v>-0.0018496775650005404</v>
+        <v>1.6656694351073042e-05</v>
       </c>
       <c r="L32">
-        <v>7.2099035883625066e-05</v>
+        <v>-4.7572744028242836e-06</v>
       </c>
       <c r="M32">
-        <v>-3.1354179638707811e-05</v>
+        <v>7.9370531799451678e-05</v>
       </c>
       <c r="N32">
-        <v>-0.0030707085921171592</v>
+        <v>6.7198161181713026e-05</v>
       </c>
       <c r="O32">
-        <v>-0.00070074022067162707</v>
+        <v>0.0001750698952145773</v>
       </c>
       <c r="P32">
-        <v>-0.00095467605227211806</v>
+        <v>-4.5373912749079905e-05</v>
       </c>
       <c r="Q32">
-        <v>-0.011541645251482602</v>
+        <v>0.00031607126843852251</v>
       </c>
       <c r="R32">
-        <v>-0.010890448498852215</v>
+        <v>0.00028715676090059969</v>
       </c>
       <c r="S32">
-        <v>-0.010699410321673423</v>
+        <v>0.00020059819423439221</v>
       </c>
       <c r="T32">
-        <v>-0.018521867812695998</v>
+        <v>-4.8286190883990721e-05</v>
       </c>
       <c r="U32">
-        <v>-0.014676313792467369</v>
+        <v>3.5529327898728424e-05</v>
       </c>
       <c r="V32">
-        <v>-0.014979031873911988</v>
+        <v>0.00010284722603032259</v>
       </c>
       <c r="W32">
-        <v>-0.00041274289625724552</v>
+        <v>3.383842085780478e-05</v>
       </c>
       <c r="X32">
-        <v>-0.0010035270209452747</v>
+        <v>0.00011583449999951964</v>
       </c>
       <c r="Y32">
-        <v>-0.0011215853421955352</v>
+        <v>7.3739496584565752e-05</v>
       </c>
       <c r="Z32">
-        <v>-0.0023404140812224375</v>
+        <v>3.9008417406748153e-05</v>
       </c>
       <c r="AA32">
-        <v>-0.0022033836382427344</v>
+        <v>3.5143103445039927e-05</v>
       </c>
       <c r="AB32">
-        <v>-0.0022337355730764554</v>
+        <v>8.4925635283048407e-05</v>
       </c>
       <c r="AC32">
-        <v>-0.0023351606799294905</v>
+        <v>3.0846391880545981e-05</v>
       </c>
       <c r="AD32">
-        <v>-0.002320178887264668</v>
+        <v>0.0002488530751332714</v>
       </c>
       <c r="AE32">
-        <v>-0.0020692446765736309</v>
+        <v>2.7589194120178871e-05</v>
       </c>
       <c r="AF32">
-        <v>-5.9901912604673263e-05</v>
+        <v>-6.0272775925399258e-06</v>
       </c>
       <c r="AG32">
-        <v>0.038988563307745978</v>
+        <v>0.0017435790274805698</v>
+      </c>
+      <c r="AH32">
+        <v>0.0002839342265336464</v>
+      </c>
+      <c r="AI32">
+        <v>-0.00031764632932575275</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33">
+        <v>-0.12567371101174948</v>
+      </c>
+      <c r="C33">
+        <v>-2.8586673719581114e-05</v>
+      </c>
+      <c r="D33">
+        <v>-2.1025786509196349e-06</v>
+      </c>
+      <c r="E33">
+        <v>9.7628222075587755e-09</v>
+      </c>
+      <c r="F33">
+        <v>-8.3220067583281154e-07</v>
+      </c>
+      <c r="G33">
+        <v>5.0810295743719102e-05</v>
+      </c>
+      <c r="H33">
+        <v>1.1790754280966483e-05</v>
+      </c>
+      <c r="I33">
+        <v>6.4729527955960983e-05</v>
+      </c>
+      <c r="J33">
+        <v>-8.3141777482098215e-05</v>
+      </c>
+      <c r="K33">
+        <v>3.2264897530520989e-05</v>
+      </c>
+      <c r="L33">
+        <v>-7.4010554880799231e-06</v>
+      </c>
+      <c r="M33">
+        <v>5.013149121636935e-05</v>
+      </c>
+      <c r="N33">
+        <v>3.4162190225686239e-05</v>
+      </c>
+      <c r="O33">
+        <v>0.00022189868718456023</v>
+      </c>
+      <c r="P33">
+        <v>-0.00015097457733100018</v>
+      </c>
+      <c r="Q33">
+        <v>0.00019648143661476526</v>
+      </c>
+      <c r="R33">
+        <v>0.00018711060073023714</v>
+      </c>
+      <c r="S33">
+        <v>0.00014551465158310021</v>
+      </c>
+      <c r="T33">
+        <v>0.00016431300235473373</v>
+      </c>
+      <c r="U33">
+        <v>0.00016931722591211236</v>
+      </c>
+      <c r="V33">
+        <v>0.00021353528251407371</v>
+      </c>
+      <c r="W33">
+        <v>-1.1683104600936545e-05</v>
+      </c>
+      <c r="X33">
+        <v>1.5224501182161082e-05</v>
+      </c>
+      <c r="Y33">
+        <v>1.185222418444978e-05</v>
+      </c>
+      <c r="Z33">
+        <v>6.6071984716610348e-06</v>
+      </c>
+      <c r="AA33">
+        <v>-2.8320511428704806e-05</v>
+      </c>
+      <c r="AB33">
+        <v>1.8899554389884433e-05</v>
+      </c>
+      <c r="AC33">
+        <v>-1.8176728307583035e-05</v>
+      </c>
+      <c r="AD33">
+        <v>-2.8456481678028681e-07</v>
+      </c>
+      <c r="AE33">
+        <v>-3.89107080160404e-05</v>
+      </c>
+      <c r="AF33">
+        <v>-1.1944329663813337e-05</v>
+      </c>
+      <c r="AG33">
+        <v>0.0002839342265336464</v>
+      </c>
+      <c r="AH33">
+        <v>0.0014619434463006196</v>
+      </c>
+      <c r="AI33">
+        <v>-0.00011722674572657436</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34">
+        <v>-0.4431631749946896</v>
+      </c>
+      <c r="C34">
+        <v>0.00018030146354133222</v>
+      </c>
+      <c r="D34">
+        <v>-0.00037727989086930693</v>
+      </c>
+      <c r="E34">
+        <v>3.2579248682791623e-06</v>
+      </c>
+      <c r="F34">
+        <v>-0.0031909959915158394</v>
+      </c>
+      <c r="G34">
+        <v>-0.003270466191866302</v>
+      </c>
+      <c r="H34">
+        <v>-0.003381134787782597</v>
+      </c>
+      <c r="I34">
+        <v>-0.0039087046616684516</v>
+      </c>
+      <c r="J34">
+        <v>0.00037117144109132753</v>
+      </c>
+      <c r="K34">
+        <v>-0.002408534962640044</v>
+      </c>
+      <c r="L34">
+        <v>7.7037032292740965e-05</v>
+      </c>
+      <c r="M34">
+        <v>-0.00010796927102515791</v>
+      </c>
+      <c r="N34">
+        <v>-0.004452135442681469</v>
+      </c>
+      <c r="O34">
+        <v>-0.0037005242288102864</v>
+      </c>
+      <c r="P34">
+        <v>-0.0031854452860888309</v>
+      </c>
+      <c r="Q34">
+        <v>-0.015830166702359098</v>
+      </c>
+      <c r="R34">
+        <v>-0.015025821244958616</v>
+      </c>
+      <c r="S34">
+        <v>-0.014774351112696028</v>
+      </c>
+      <c r="T34">
+        <v>-0.024007797661731684</v>
+      </c>
+      <c r="U34">
+        <v>-0.019144972698791899</v>
+      </c>
+      <c r="V34">
+        <v>-0.019555278136735209</v>
+      </c>
+      <c r="W34">
+        <v>-0.00041100116851545585</v>
+      </c>
+      <c r="X34">
+        <v>-0.0012675766661341425</v>
+      </c>
+      <c r="Y34">
+        <v>-0.0011978237530955954</v>
+      </c>
+      <c r="Z34">
+        <v>-0.0024091914813475467</v>
+      </c>
+      <c r="AA34">
+        <v>-0.0021972512193771704</v>
+      </c>
+      <c r="AB34">
+        <v>-0.0021741961383255994</v>
+      </c>
+      <c r="AC34">
+        <v>-0.0023874069787615457</v>
+      </c>
+      <c r="AD34">
+        <v>-0.0022674087277131556</v>
+      </c>
+      <c r="AE34">
+        <v>-0.0022996381816512762</v>
+      </c>
+      <c r="AF34">
+        <v>-6.1229541170580211e-05</v>
+      </c>
+      <c r="AG34">
+        <v>-0.00031764632932575275</v>
+      </c>
+      <c r="AH34">
+        <v>-0.00011722674572657436</v>
+      </c>
+      <c r="AI34">
+        <v>0.051332128838372015</v>
       </c>
     </row>
   </sheetData>
